--- a/apps/backend/src/plans/plans/import-plan-aggregate/__fixtures__/one_fiche_plan.xlsx
+++ b/apps/backend/src/plans/plans/import-plan-aggregate/__fixtures__/one_fiche_plan.xlsx
@@ -616,7 +616,7 @@
     <t xml:space="preserve">Il s’agit alors de permettre aux élus communautaires d’à la fois porter la parole des habitants dans le cadre du CLS mais aussi de pouvoir suivre l’avancée des actions et de se tenir informé de toute son actualité. </t>
   </si>
   <si>
-    <t xml:space="preserve"> Une instance de gouvernance</t>
+    <t xml:space="preserve"> Une instance de gouvernance, Une autre instance</t>
   </si>
   <si>
     <t>Objectif général : L’appropriation du Contrat Local de Santé par les élus

--- a/apps/backend/src/plans/plans/import-plan-aggregate/__fixtures__/one_fiche_plan.xlsx
+++ b/apps/backend/src/plans/plans/import-plan-aggregate/__fixtures__/one_fiche_plan.xlsx
@@ -1,28 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="Mode demploi" sheetId="1" r:id="rId4"/>
-    <sheet name="Fichier dimport" sheetId="2" r:id="rId5"/>
-    <sheet name="Listes déroulantes" sheetId="3" r:id="rId6"/>
+    <sheet sheetId="1" name="Mode demploi" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Fichier dimport" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Listes déroulantes" state="visible" r:id="rId6"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="111">
   <si>
     <t>Importer un plan d'action sur la plateforme Territoires en Transitions</t>
   </si>
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
+        <color indexed="14"/>
         <sz val="12"/>
-        <color indexed="14"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">📺 Consultez une vidéo de présentation de ce fichier </t>
@@ -31,17 +34,17 @@
   <si>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">➜ </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">À savoir :
@@ -49,42 +52,42 @@
     </r>
     <r>
       <rPr>
+        <color indexed="15"/>
         <sz val="12"/>
-        <color indexed="15"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>🟨</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Les colonnes sur fond </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>jaune</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> sont à renseigner en priorité : elles sont recommandées pour un import optimal.</t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -92,42 +95,42 @@
     </r>
     <r>
       <rPr>
+        <color indexed="16"/>
         <sz val="12"/>
-        <color indexed="16"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>🟦</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Les colonnes sur fond </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">bleu </t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">sont facultatives : à compléter si vous disposez des informations. </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -135,33 +138,33 @@
     </r>
     <r>
       <rPr>
+        <color indexed="17"/>
         <sz val="12"/>
-        <color indexed="17"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>🟥</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Les colonnes sur fond </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">rouge </t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">ne sont pas importables techniquement dans la plateforme : elles permettent néanmoins de centraliser les informations utiles, que vous pourrez saisir manuellement après l’import.
@@ -169,9 +172,9 @@
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -179,17 +182,17 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">➜ </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Affichage :
@@ -197,8 +200,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Certaines colonnes sont masquées par défaut. Vous pouvez les afficher en cliquant sur le symbole "+" situé au-dessus de l'en-tête.
@@ -206,8 +209,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -215,18 +218,18 @@
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="9"/>
         <sz val="12"/>
-        <color indexed="9"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Bonnes pratiques : </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">
@@ -234,8 +237,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">➔ Reprenez l’architecture de votre plan : chaque ligne correspond à la création d'une fiche. Ainsi, un même axe peut apparaître sur plusieurs lignes,
@@ -243,25 +246,25 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">➔ Un </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>exemple prérempli est disponible</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> pour vous guider à la ligne 5,
@@ -269,25 +272,25 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>➔ Pensez à lire</t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> les consignes de remplissage</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> indiquées ligne 4 pour bien respecter le format requis,
@@ -295,25 +298,25 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>➔ Conservez</t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> la structure des colonnes telle quelle</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> : n’en ajoutez pas et n’en supprimez pas.</t>
@@ -322,18 +325,18 @@
   <si>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="19"/>
         <sz val="12"/>
-        <color indexed="19"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>🆘</t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> Besoin d’aide ? 
@@ -341,8 +344,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Si vous rencontrez des difficultés à l'utilisation de ce fichier, que vous souhaitez bénéficier d'un accompagnement à l'import, 
@@ -350,42 +353,42 @@
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">faîtes-nous signe en nous écrivant à l'adresse </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>contact@territoiresentransitions.fr</t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve"> ou bien directement sur le </t>
     </r>
     <r>
       <rPr>
-        <b val="1"/>
+        <b/>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Chat </t>
     </r>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="12"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>de la plateforme.</t>
@@ -416,6 +419,9 @@
     <t>Titre de l'action</t>
   </si>
   <si>
+    <t>Titre de la sous-action</t>
+  </si>
+  <si>
     <t>Descriptif</t>
   </si>
   <si>
@@ -506,14 +512,14 @@
     <t xml:space="preserve">Champ texte </t>
   </si>
   <si>
-    <t>Champ texte non importé
+    <t xml:space="preserve">Champ texte non importé
 🟢 Clé pour le pilotage</t>
   </si>
   <si>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="9"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Champ texte
@@ -521,8 +527,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="29"/>
         <sz val="9"/>
-        <color indexed="29"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>(séparateur virgule)</t>
@@ -531,8 +537,8 @@
   <si>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="9"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Champ texte 🟢 Clé pour le pilotage
@@ -540,8 +546,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="29"/>
         <sz val="9"/>
-        <color indexed="29"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>(séparateur virgule)</t>
@@ -550,8 +556,8 @@
   <si>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="9"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Champ liste déroulante 
@@ -559,8 +565,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="29"/>
         <sz val="9"/>
-        <color indexed="29"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>(choix prédéfinis)</t>
@@ -575,8 +581,8 @@
   <si>
     <r>
       <rPr>
+        <color indexed="8"/>
         <sz val="9"/>
-        <color indexed="8"/>
         <rFont val="Calibri"/>
       </rPr>
       <t xml:space="preserve">Champ liste déroulante 🟢 Clé pour le pilotage
@@ -584,8 +590,8 @@
     </r>
     <r>
       <rPr>
+        <color indexed="29"/>
         <sz val="9"/>
-        <color indexed="29"/>
         <rFont val="Calibri"/>
       </rPr>
       <t>(choix prédéfinis)</t>
@@ -619,7 +625,7 @@
     <t xml:space="preserve"> Une instance de gouvernance, Une autre instance</t>
   </si>
   <si>
-    <t>Objectif général : L’appropriation du Contrat Local de Santé par les élus
+    <t xml:space="preserve">Objectif général : L’appropriation du Contrat Local de Santé par les élus
 Objectif spécifique n°1 : Désigner les élus à intégrer la commission de suivi du CLS (Maire de communes avec une dynamique Santé)
 Objectif opérationnel 1.1 : Sensibiliser les élus à la dynamique du CLS
 Objectif opérationnel 1.2 : Interroger sur la place et les attendus du CLS auprès de chaque élu (sondage)
@@ -786,121 +792,86 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <color indexed="9"/>
       <sz val="16"/>
-      <color indexed="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="13"/>
       <sz val="12"/>
-      <color indexed="13"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
+      <color indexed="14"/>
       <sz val="12"/>
-      <color indexed="14"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color indexed="20"/>
       <sz val="12"/>
-      <color indexed="15"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="16"/>
+      <b/>
+      <color indexed="8"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="17"/>
+      <color indexed="8"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="12"/>
-      <color indexed="9"/>
+      <color indexed="27"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="12"/>
-      <color indexed="19"/>
+      <color indexed="8"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="12"/>
-      <color indexed="20"/>
+      <color indexed="30"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="27"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="29"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="30"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <color indexed="12"/>
       <sz val="12"/>
-      <color indexed="12"/>
       <name val="Avenir Roman"/>
     </font>
     <font>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
       <name val="Avenir Roman"/>
     </font>
   </fonts>
@@ -914,65 +885,55 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="10"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="18"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="21"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="23"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="24"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="25"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="26"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="28"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="31"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1032,13 +993,6 @@
       <left style="thin">
         <color indexed="11"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom/>
@@ -1296,222 +1250,218 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="71">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="71">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="10" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="14" fontId="10" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="6" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="6" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="7" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="8" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="9" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="13" fillId="7" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="10" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="12" fillId="11" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="19" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="18" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="3" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="3" borderId="22" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="7" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="14" fontId="17" fillId="7" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="11" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="13" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1519,44 +1469,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ff38761d"/>
-      <rgbColor rgb="ffd9ead3"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ff0563c1"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffff9900"/>
-      <rgbColor rgb="ff1155cc"/>
-      <rgbColor rgb="fff4cccc"/>
-      <rgbColor rgb="fff3f3f3"/>
-      <rgbColor rgb="ffcc0000"/>
-      <rgbColor rgb="fffefffe"/>
-      <rgbColor rgb="ff5e88b1"/>
-      <rgbColor rgb="ff808080"/>
-      <rgbColor rgb="fffff2cc"/>
-      <rgbColor rgb="ffdbe9f6"/>
-      <rgbColor rgb="ffebc3b9"/>
-      <rgbColor rgb="fff0f6fb"/>
-      <rgbColor rgb="ff999999"/>
-      <rgbColor rgb="fffff1f1"/>
-      <rgbColor rgb="ffc00000"/>
-      <rgbColor rgb="ff666666"/>
-      <rgbColor rgb="ff4472c4"/>
-      <rgbColor rgb="ffaeabab"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -2585,89 +2506,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="11.1667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AB10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.1667"/>
   <cols>
     <col min="1" max="1" width="1.67188" style="1" customWidth="1"/>
     <col min="2" max="2" width="152" style="1" customWidth="1"/>
     <col min="3" max="3" width="2.67188" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.1719" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="11.1719" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="11.1719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5" customHeight="1">
+    <row r="1" ht="28.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
-      <c r="B1" t="s" s="3">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5"/>
       <c r="E1" s="6"/>
     </row>
-    <row r="2" ht="25.5" customHeight="1">
+    <row r="2" ht="25.5" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
-      <c r="B2" t="s" s="8">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="5"/>
       <c r="E2" s="6"/>
-    </row>
-    <row r="3" ht="228" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" t="s" s="11">
+      <c r="W2" s="1">
+        <v>666</v>
+      </c>
+      <c r="AB2" s="10">
+        <v>47727</v>
+      </c>
+    </row>
+    <row r="3" ht="228" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="9"/>
       <c r="D3" s="5"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" ht="66.75" customHeight="1">
-      <c r="A4" s="12"/>
-      <c r="B4" t="s" s="13">
+    <row r="4" ht="66.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="5"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15"/>
+    <row r="5" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
       <c r="C5" s="9"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" ht="15.35" customHeight="1">
+    <row r="6" ht="15.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="16"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
     </row>
-    <row r="7" ht="15.35" customHeight="1">
+    <row r="7" ht="15.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" ht="15.35" customHeight="1">
+    <row r="8" ht="15.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" ht="15.35" customHeight="1">
+    <row r="9" ht="15.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
-    <row r="10" ht="15.35" customHeight="1">
+    <row r="10" ht="15.35" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -2676,10 +2602,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="" tooltip="" display="📺 Consultez une vidéo de présentation de ce fichier "/>
+    <hyperlink ref="B2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -2687,43 +2613,42 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ195"/>
-  <sheetFormatPr defaultColWidth="11.1667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.1667"/>
   <cols>
-    <col min="1" max="1" width="24.1719" style="17" customWidth="1"/>
-    <col min="2" max="2" width="22.3516" style="17" customWidth="1"/>
-    <col min="3" max="3" width="24.6719" style="17" customWidth="1"/>
-    <col min="4" max="4" width="22.3516" style="17" customWidth="1"/>
-    <col min="5" max="5" width="74" style="17" customWidth="1"/>
-    <col min="6" max="6" width="36.1719" style="17" customWidth="1"/>
-    <col min="7" max="7" width="56" style="17" customWidth="1"/>
-    <col min="8" max="8" width="20.6719" style="17" customWidth="1"/>
-    <col min="9" max="9" width="28.5" style="17" customWidth="1"/>
-    <col min="10" max="10" width="24.8516" style="17" customWidth="1"/>
-    <col min="11" max="11" width="28.5" style="17" customWidth="1"/>
-    <col min="12" max="12" width="32.6719" style="17" customWidth="1"/>
-    <col min="13" max="13" width="54" style="17" customWidth="1"/>
-    <col min="14" max="14" width="24.1719" style="17" customWidth="1"/>
-    <col min="15" max="15" width="23.6719" style="17" customWidth="1"/>
-    <col min="16" max="16" width="25.5" style="17" customWidth="1"/>
-    <col min="17" max="17" width="32.1719" style="17" customWidth="1"/>
-    <col min="18" max="18" width="15.5" style="17" customWidth="1"/>
-    <col min="19" max="19" width="28.5" style="17" customWidth="1"/>
-    <col min="20" max="20" width="15.5" style="17" customWidth="1"/>
-    <col min="21" max="21" width="28.5" style="17" customWidth="1"/>
-    <col min="22" max="22" width="15.5" style="17" customWidth="1"/>
-    <col min="23" max="23" width="26.1719" style="17" customWidth="1"/>
-    <col min="24" max="24" width="35.1719" style="17" customWidth="1"/>
-    <col min="25" max="25" width="34.6719" style="17" customWidth="1"/>
-    <col min="26" max="27" width="21" style="17" customWidth="1"/>
-    <col min="28" max="35" hidden="1" width="11.1667" style="17" customWidth="1"/>
-    <col min="36" max="36" width="11.1719" style="17" customWidth="1"/>
-    <col min="37" max="16384" width="11.1719" style="17" customWidth="1"/>
+    <col min="1" max="1" width="24.1719" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22.3516" style="1" customWidth="1"/>
+    <col min="3" max="3" width="24.6719" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.3516" style="1" customWidth="1"/>
+    <col min="5" max="5" width="74" style="1" customWidth="1"/>
+    <col min="6" max="6" width="36.1719" style="1" customWidth="1"/>
+    <col min="7" max="7" width="56" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.6719" style="1" customWidth="1"/>
+    <col min="9" max="9" width="28.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.8516" style="1" customWidth="1"/>
+    <col min="11" max="11" width="28.5" style="1" customWidth="1"/>
+    <col min="12" max="12" width="32.6719" style="1" customWidth="1"/>
+    <col min="13" max="13" width="54" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.1719" style="1" customWidth="1"/>
+    <col min="15" max="15" width="23.6719" style="1" customWidth="1"/>
+    <col min="16" max="16" width="25.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="32.1719" style="1" customWidth="1"/>
+    <col min="18" max="18" width="15.5" style="1" customWidth="1"/>
+    <col min="19" max="19" width="28.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="15.5" style="1" customWidth="1"/>
+    <col min="21" max="21" width="28.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.5" style="1" customWidth="1"/>
+    <col min="23" max="23" width="26.1719" style="1" customWidth="1"/>
+    <col min="24" max="24" width="35.1719" style="1" customWidth="1"/>
+    <col min="25" max="25" width="34.6719" style="1" customWidth="1"/>
+    <col min="26" max="27" width="21" style="1" customWidth="1"/>
+    <col min="28" max="35" width="11.1667" style="1" hidden="1" customWidth="1"/>
+    <col min="36" max="16384" width="11.1719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" t="s" s="18">
+    <row r="1" ht="18" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="19"/>
@@ -2731,7 +2656,7 @@
       <c r="D1" s="19"/>
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
-      <c r="G1" t="s" s="21">
+      <c r="G1" s="21" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="22"/>
@@ -2742,10 +2667,10 @@
       <c r="M1" s="25"/>
       <c r="N1" s="25"/>
       <c r="O1" s="26"/>
-      <c r="P1" t="s" s="20">
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="20"/>
       <c r="R1" s="20"/>
       <c r="S1" s="20"/>
       <c r="T1" s="20"/>
@@ -2758,313 +2683,315 @@
       <c r="AA1" s="20"/>
       <c r="AB1" s="20"/>
       <c r="AC1" s="20"/>
-      <c r="AD1" t="s" s="21">
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="21"/>
       <c r="AF1" s="21"/>
       <c r="AG1" s="21"/>
       <c r="AH1" s="19"/>
       <c r="AI1" s="19"/>
       <c r="AJ1" s="5"/>
     </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" t="s" s="27">
+    <row r="2" ht="18.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s" s="28">
+      <c r="B2" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s" s="28">
+      <c r="C2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s" s="28">
+      <c r="D2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s" s="28">
+      <c r="E2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s" s="29">
+      <c r="F2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s" s="28">
+      <c r="G2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s" s="30">
+      <c r="H2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="I2" t="s" s="31">
+      <c r="I2" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s" s="31">
+      <c r="J2" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="K2" t="s" s="31">
+      <c r="K2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s" s="28">
+      <c r="L2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="M2" t="s" s="28">
+      <c r="M2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="N2" t="s" s="31">
+      <c r="N2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="O2" t="s" s="31">
+      <c r="O2" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="P2" t="s" s="31">
+      <c r="P2" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" t="s" s="31">
+      <c r="Q2" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="R2" t="s" s="31">
+      <c r="R2" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="S2" t="s" s="31">
+      <c r="S2" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="T2" t="s" s="31">
-        <v>25</v>
-      </c>
-      <c r="U2" t="s" s="31">
+      <c r="T2" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="V2" t="s" s="31">
-        <v>25</v>
-      </c>
-      <c r="W2" t="s" s="28">
+      <c r="U2" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="V2" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="X2" t="s" s="28">
+      <c r="W2" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="X2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" t="s" s="28">
+      <c r="Y2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" t="s" s="28">
+      <c r="Z2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" t="s" s="28">
+      <c r="AA2" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="AB2" t="s" s="29">
+      <c r="AB2" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="AC2" t="s" s="29">
+      <c r="AC2" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="AD2" t="s" s="30">
+      <c r="AD2" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE2" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="AE2" t="s" s="30">
-        <v>35</v>
-      </c>
-      <c r="AF2" t="s" s="30">
+      <c r="AF2" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="AG2" t="s" s="30">
+      <c r="AG2" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="AH2" t="s" s="32">
+      <c r="AH2" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="AI2" t="s" s="30">
+      <c r="AI2" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AJ2" s="33"/>
-    </row>
-    <row r="3" ht="30.75" customHeight="1">
-      <c r="A3" t="s" s="34">
+      <c r="AJ2" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B3" t="s" s="35">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s" s="35">
-        <v>40</v>
-      </c>
-      <c r="D3" t="s" s="35">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s" s="35">
+    </row>
+    <row r="3" ht="30.75" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F3" t="s" s="36">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s" s="36">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s" s="37">
+      <c r="B3" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="I3" t="s" s="36">
+      <c r="G3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="J3" t="s" s="36">
-        <v>40</v>
-      </c>
-      <c r="K3" t="s" s="36">
-        <v>43</v>
-      </c>
-      <c r="L3" t="s" s="36">
-        <v>43</v>
-      </c>
-      <c r="M3" t="s" s="36">
+      <c r="J3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="N3" t="s" s="36">
+      <c r="K3" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="O3" t="s" s="36">
+      <c r="M3" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="N3" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="P3" t="s" s="36">
+      <c r="O3" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="36" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" t="s" s="36">
-        <v>43</v>
-      </c>
-      <c r="R3" t="s" s="36">
+      <c r="Q3" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="S3" t="s" s="36">
-        <v>43</v>
-      </c>
-      <c r="T3" t="s" s="36">
+      <c r="R3" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="U3" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="V3" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="W3" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="X3" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y3" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z3" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA3" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="AB3" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC3" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD3" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="U3" t="s" s="36">
-        <v>43</v>
-      </c>
-      <c r="V3" t="s" s="36">
-        <v>47</v>
-      </c>
-      <c r="W3" t="s" s="36">
-        <v>47</v>
-      </c>
-      <c r="X3" t="s" s="36">
-        <v>48</v>
-      </c>
-      <c r="Y3" t="s" s="36">
-        <v>48</v>
-      </c>
-      <c r="Z3" t="s" s="36">
-        <v>49</v>
-      </c>
-      <c r="AA3" t="s" s="36">
-        <v>49</v>
-      </c>
-      <c r="AB3" t="s" s="36">
-        <v>50</v>
-      </c>
-      <c r="AC3" t="s" s="36">
-        <v>46</v>
-      </c>
-      <c r="AD3" t="s" s="37">
-        <v>51</v>
-      </c>
-      <c r="AE3" t="s" s="37">
-        <v>51</v>
-      </c>
-      <c r="AF3" t="s" s="37">
-        <v>51</v>
-      </c>
-      <c r="AG3" t="s" s="37">
-        <v>51</v>
-      </c>
-      <c r="AH3" t="s" s="38">
-        <v>40</v>
-      </c>
-      <c r="AI3" t="s" s="37">
-        <v>51</v>
-      </c>
-      <c r="AJ3" s="33"/>
-    </row>
-    <row r="4" ht="230.4" customHeight="1">
-      <c r="A4" t="s" s="39">
+      <c r="AE3" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="B4" t="s" s="40">
+      <c r="AF3" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="AG3" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH3" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="AI3" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ3" s="33" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" ht="230.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C4" t="s" s="41">
+      <c r="B4" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="D4" t="s" s="42">
+      <c r="C4" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="E4" t="s" s="42">
+      <c r="D4" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="F4" t="s" s="43">
+      <c r="E4" s="42"/>
+      <c r="F4" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="G4" t="s" s="44">
+      <c r="G4" s="44" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="45"/>
-      <c r="I4" t="s" s="46">
+      <c r="H4" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="J4" t="s" s="46">
+      <c r="I4" s="46"/>
+      <c r="J4" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="K4" t="s" s="46">
+      <c r="K4" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="L4" t="s" s="46">
+      <c r="L4" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="M4" t="s" s="46">
+      <c r="M4" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="N4" t="s" s="46">
+      <c r="N4" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="O4" t="s" s="47">
+      <c r="O4" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="P4" t="s" s="44">
+      <c r="P4" s="44" t="s">
         <v>66</v>
       </c>
-      <c r="Q4" t="s" s="46">
+      <c r="Q4" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="S4" s="46">
         <v>1000</v>
       </c>
-      <c r="S4" t="s" s="46">
-        <v>68</v>
-      </c>
-      <c r="T4" s="49">
+      <c r="T4" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="U4" s="46">
         <v>25000</v>
       </c>
-      <c r="U4" t="s" s="46">
-        <v>69</v>
-      </c>
-      <c r="V4" s="48">
+      <c r="V4" s="45" t="s">
+        <v>70</v>
+      </c>
+      <c r="W4" s="49">
         <v>666</v>
       </c>
-      <c r="W4" s="48">
+      <c r="X4" s="46">
         <v>5000000</v>
       </c>
-      <c r="X4" t="s" s="46">
-        <v>70</v>
-      </c>
-      <c r="Y4" t="s" s="46">
+      <c r="Y4" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="Z4" s="50">
+      <c r="Z4" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA4" s="50">
         <v>45992</v>
       </c>
-      <c r="AA4" s="50">
+      <c r="AB4" s="51">
         <v>47727</v>
       </c>
-      <c r="AB4" s="45"/>
       <c r="AC4" s="44"/>
       <c r="AD4" s="45"/>
       <c r="AE4" s="45"/>
@@ -3074,45 +3001,45 @@
       <c r="AI4" s="45"/>
       <c r="AJ4" s="33"/>
     </row>
-    <row r="5" ht="100.8" customHeight="1">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="52"/>
-      <c r="Z5" s="52"/>
-      <c r="AA5" s="52"/>
-      <c r="AB5" s="53"/>
-      <c r="AC5" s="54"/>
-      <c r="AD5" s="53"/>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
+    <row r="5" ht="100.8" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="53"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="53"/>
+      <c r="O5" s="53"/>
+      <c r="P5" s="53"/>
+      <c r="Q5" s="53"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="53"/>
+      <c r="T5" s="53"/>
+      <c r="U5" s="53"/>
+      <c r="V5" s="53"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="53"/>
+      <c r="Z5" s="53"/>
+      <c r="AA5" s="53"/>
+      <c r="AB5" s="54"/>
+      <c r="AC5" s="55"/>
+      <c r="AD5" s="54"/>
+      <c r="AE5" s="54"/>
+      <c r="AF5" s="54"/>
+      <c r="AG5" s="54"/>
+      <c r="AH5" s="54"/>
+      <c r="AI5" s="54"/>
       <c r="AJ5" s="6"/>
     </row>
-    <row r="6" ht="288" customHeight="1">
+    <row r="6" ht="288" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -3140,17 +3067,17 @@
       <c r="Y6" s="6"/>
       <c r="Z6" s="6"/>
       <c r="AA6" s="6"/>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="56"/>
-      <c r="AD6" s="55"/>
-      <c r="AE6" s="55"/>
-      <c r="AF6" s="55"/>
-      <c r="AG6" s="55"/>
-      <c r="AH6" s="55"/>
-      <c r="AI6" s="55"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="57"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="56"/>
       <c r="AJ6" s="6"/>
     </row>
-    <row r="7" ht="302.4" customHeight="1">
+    <row r="7" ht="302.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3178,17 +3105,17 @@
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="6"/>
-      <c r="AB7" s="53"/>
-      <c r="AC7" s="54"/>
-      <c r="AD7" s="53"/>
-      <c r="AE7" s="53"/>
-      <c r="AF7" s="53"/>
-      <c r="AG7" s="53"/>
-      <c r="AH7" s="53"/>
-      <c r="AI7" s="53"/>
+      <c r="AB7" s="54"/>
+      <c r="AC7" s="55"/>
+      <c r="AD7" s="54"/>
+      <c r="AE7" s="54"/>
+      <c r="AF7" s="54"/>
+      <c r="AG7" s="54"/>
+      <c r="AH7" s="54"/>
+      <c r="AI7" s="54"/>
       <c r="AJ7" s="6"/>
     </row>
-    <row r="8" ht="144" customHeight="1">
+    <row r="8" ht="144" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -3216,17 +3143,17 @@
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
       <c r="AA8" s="6"/>
-      <c r="AB8" s="55"/>
-      <c r="AC8" s="56"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="55"/>
-      <c r="AG8" s="55"/>
-      <c r="AH8" s="55"/>
-      <c r="AI8" s="55"/>
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="57"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="56"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="56"/>
+      <c r="AH8" s="56"/>
+      <c r="AI8" s="56"/>
       <c r="AJ8" s="6"/>
     </row>
-    <row r="9" ht="172.8" customHeight="1">
+    <row r="9" ht="172.8" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -3254,17 +3181,17 @@
       <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
-      <c r="AB9" s="53"/>
-      <c r="AC9" s="54"/>
-      <c r="AD9" s="53"/>
-      <c r="AE9" s="53"/>
-      <c r="AF9" s="53"/>
-      <c r="AG9" s="53"/>
-      <c r="AH9" s="53"/>
-      <c r="AI9" s="53"/>
+      <c r="AB9" s="54"/>
+      <c r="AC9" s="55"/>
+      <c r="AD9" s="54"/>
+      <c r="AE9" s="54"/>
+      <c r="AF9" s="54"/>
+      <c r="AG9" s="54"/>
+      <c r="AH9" s="54"/>
+      <c r="AI9" s="54"/>
       <c r="AJ9" s="6"/>
     </row>
-    <row r="10" ht="259.2" customHeight="1">
+    <row r="10" ht="259.2" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -3292,17 +3219,17 @@
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
       <c r="AA10" s="6"/>
-      <c r="AB10" s="55"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="55"/>
-      <c r="AE10" s="55"/>
-      <c r="AF10" s="55"/>
-      <c r="AG10" s="55"/>
-      <c r="AH10" s="55"/>
-      <c r="AI10" s="55"/>
+      <c r="AB10" s="56"/>
+      <c r="AC10" s="57"/>
+      <c r="AD10" s="56"/>
+      <c r="AE10" s="56"/>
+      <c r="AF10" s="56"/>
+      <c r="AG10" s="56"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="56"/>
       <c r="AJ10" s="6"/>
     </row>
-    <row r="11" ht="316.8" customHeight="1">
+    <row r="11" ht="316.8" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -3330,17 +3257,17 @@
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
-      <c r="AB11" s="53"/>
-      <c r="AC11" s="54"/>
-      <c r="AD11" s="53"/>
-      <c r="AE11" s="53"/>
-      <c r="AF11" s="53"/>
-      <c r="AG11" s="53"/>
-      <c r="AH11" s="53"/>
-      <c r="AI11" s="53"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="55"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="54"/>
+      <c r="AG11" s="54"/>
+      <c r="AH11" s="54"/>
+      <c r="AI11" s="54"/>
       <c r="AJ11" s="6"/>
     </row>
-    <row r="12" ht="172.8" customHeight="1">
+    <row r="12" ht="172.8" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -3368,17 +3295,17 @@
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
       <c r="AA12" s="6"/>
-      <c r="AB12" s="55"/>
-      <c r="AC12" s="56"/>
-      <c r="AD12" s="55"/>
-      <c r="AE12" s="55"/>
-      <c r="AF12" s="55"/>
-      <c r="AG12" s="55"/>
-      <c r="AH12" s="55"/>
-      <c r="AI12" s="55"/>
+      <c r="AB12" s="56"/>
+      <c r="AC12" s="57"/>
+      <c r="AD12" s="56"/>
+      <c r="AE12" s="56"/>
+      <c r="AF12" s="56"/>
+      <c r="AG12" s="56"/>
+      <c r="AH12" s="56"/>
+      <c r="AI12" s="56"/>
       <c r="AJ12" s="6"/>
     </row>
-    <row r="13" ht="129.6" customHeight="1">
+    <row r="13" ht="129.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -3406,17 +3333,17 @@
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
-      <c r="AB13" s="53"/>
-      <c r="AC13" s="54"/>
-      <c r="AD13" s="53"/>
-      <c r="AE13" s="53"/>
-      <c r="AF13" s="53"/>
-      <c r="AG13" s="53"/>
-      <c r="AH13" s="53"/>
-      <c r="AI13" s="53"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="55"/>
+      <c r="AD13" s="54"/>
+      <c r="AE13" s="54"/>
+      <c r="AF13" s="54"/>
+      <c r="AG13" s="54"/>
+      <c r="AH13" s="54"/>
+      <c r="AI13" s="54"/>
       <c r="AJ13" s="6"/>
     </row>
-    <row r="14" ht="187.2" customHeight="1">
+    <row r="14" ht="187.2" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3444,17 +3371,17 @@
       <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
-      <c r="AB14" s="55"/>
-      <c r="AC14" s="56"/>
-      <c r="AD14" s="55"/>
-      <c r="AE14" s="55"/>
-      <c r="AF14" s="55"/>
-      <c r="AG14" s="55"/>
-      <c r="AH14" s="55"/>
-      <c r="AI14" s="55"/>
+      <c r="AB14" s="56"/>
+      <c r="AC14" s="57"/>
+      <c r="AD14" s="56"/>
+      <c r="AE14" s="56"/>
+      <c r="AF14" s="56"/>
+      <c r="AG14" s="56"/>
+      <c r="AH14" s="56"/>
+      <c r="AI14" s="56"/>
       <c r="AJ14" s="6"/>
     </row>
-    <row r="15" ht="187.2" customHeight="1">
+    <row r="15" ht="187.2" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -3482,17 +3409,17 @@
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
       <c r="AA15" s="6"/>
-      <c r="AB15" s="53"/>
-      <c r="AC15" s="54"/>
-      <c r="AD15" s="53"/>
-      <c r="AE15" s="53"/>
-      <c r="AF15" s="53"/>
-      <c r="AG15" s="53"/>
-      <c r="AH15" s="53"/>
-      <c r="AI15" s="53"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="55"/>
+      <c r="AD15" s="54"/>
+      <c r="AE15" s="54"/>
+      <c r="AF15" s="54"/>
+      <c r="AG15" s="54"/>
+      <c r="AH15" s="54"/>
+      <c r="AI15" s="54"/>
       <c r="AJ15" s="6"/>
     </row>
-    <row r="16" ht="187.2" customHeight="1">
+    <row r="16" ht="187.2" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -3520,17 +3447,17 @@
       <c r="Y16" s="6"/>
       <c r="Z16" s="6"/>
       <c r="AA16" s="6"/>
-      <c r="AB16" s="55"/>
-      <c r="AC16" s="56"/>
-      <c r="AD16" s="55"/>
-      <c r="AE16" s="55"/>
-      <c r="AF16" s="55"/>
-      <c r="AG16" s="55"/>
-      <c r="AH16" s="55"/>
-      <c r="AI16" s="55"/>
+      <c r="AB16" s="56"/>
+      <c r="AC16" s="57"/>
+      <c r="AD16" s="56"/>
+      <c r="AE16" s="56"/>
+      <c r="AF16" s="56"/>
+      <c r="AG16" s="56"/>
+      <c r="AH16" s="56"/>
+      <c r="AI16" s="56"/>
       <c r="AJ16" s="6"/>
     </row>
-    <row r="17" ht="288" customHeight="1">
+    <row r="17" ht="288" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -3558,17 +3485,17 @@
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
-      <c r="AB17" s="53"/>
-      <c r="AC17" s="54"/>
-      <c r="AD17" s="53"/>
-      <c r="AE17" s="53"/>
-      <c r="AF17" s="53"/>
-      <c r="AG17" s="53"/>
-      <c r="AH17" s="53"/>
-      <c r="AI17" s="53"/>
+      <c r="AB17" s="54"/>
+      <c r="AC17" s="55"/>
+      <c r="AD17" s="54"/>
+      <c r="AE17" s="54"/>
+      <c r="AF17" s="54"/>
+      <c r="AG17" s="54"/>
+      <c r="AH17" s="54"/>
+      <c r="AI17" s="54"/>
       <c r="AJ17" s="6"/>
     </row>
-    <row r="18" ht="144" customHeight="1">
+    <row r="18" ht="144" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -3596,17 +3523,17 @@
       <c r="Y18" s="6"/>
       <c r="Z18" s="6"/>
       <c r="AA18" s="6"/>
-      <c r="AB18" s="55"/>
-      <c r="AC18" s="56"/>
-      <c r="AD18" s="55"/>
-      <c r="AE18" s="55"/>
-      <c r="AF18" s="55"/>
-      <c r="AG18" s="55"/>
-      <c r="AH18" s="55"/>
-      <c r="AI18" s="55"/>
+      <c r="AB18" s="56"/>
+      <c r="AC18" s="57"/>
+      <c r="AD18" s="56"/>
+      <c r="AE18" s="56"/>
+      <c r="AF18" s="56"/>
+      <c r="AG18" s="56"/>
+      <c r="AH18" s="56"/>
+      <c r="AI18" s="56"/>
       <c r="AJ18" s="6"/>
     </row>
-    <row r="19" ht="273.6" customHeight="1">
+    <row r="19" ht="273.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -3634,17 +3561,17 @@
       <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
-      <c r="AB19" s="53"/>
-      <c r="AC19" s="54"/>
-      <c r="AD19" s="53"/>
-      <c r="AE19" s="53"/>
-      <c r="AF19" s="53"/>
-      <c r="AG19" s="53"/>
-      <c r="AH19" s="53"/>
-      <c r="AI19" s="53"/>
+      <c r="AB19" s="54"/>
+      <c r="AC19" s="55"/>
+      <c r="AD19" s="54"/>
+      <c r="AE19" s="54"/>
+      <c r="AF19" s="54"/>
+      <c r="AG19" s="54"/>
+      <c r="AH19" s="54"/>
+      <c r="AI19" s="54"/>
       <c r="AJ19" s="6"/>
     </row>
-    <row r="20" ht="144" customHeight="1">
+    <row r="20" ht="144" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -3672,17 +3599,17 @@
       <c r="Y20" s="6"/>
       <c r="Z20" s="6"/>
       <c r="AA20" s="6"/>
-      <c r="AB20" s="55"/>
-      <c r="AC20" s="56"/>
-      <c r="AD20" s="55"/>
-      <c r="AE20" s="55"/>
-      <c r="AF20" s="55"/>
-      <c r="AG20" s="55"/>
-      <c r="AH20" s="55"/>
-      <c r="AI20" s="55"/>
+      <c r="AB20" s="56"/>
+      <c r="AC20" s="57"/>
+      <c r="AD20" s="56"/>
+      <c r="AE20" s="56"/>
+      <c r="AF20" s="56"/>
+      <c r="AG20" s="56"/>
+      <c r="AH20" s="56"/>
+      <c r="AI20" s="56"/>
       <c r="AJ20" s="6"/>
     </row>
-    <row r="21" ht="345.6" customHeight="1">
+    <row r="21" ht="345.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -3710,17 +3637,17 @@
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
       <c r="AA21" s="6"/>
-      <c r="AB21" s="53"/>
-      <c r="AC21" s="54"/>
-      <c r="AD21" s="53"/>
-      <c r="AE21" s="53"/>
-      <c r="AF21" s="53"/>
-      <c r="AG21" s="53"/>
-      <c r="AH21" s="53"/>
-      <c r="AI21" s="53"/>
+      <c r="AB21" s="54"/>
+      <c r="AC21" s="55"/>
+      <c r="AD21" s="54"/>
+      <c r="AE21" s="54"/>
+      <c r="AF21" s="54"/>
+      <c r="AG21" s="54"/>
+      <c r="AH21" s="54"/>
+      <c r="AI21" s="54"/>
       <c r="AJ21" s="6"/>
     </row>
-    <row r="22" ht="230.4" customHeight="1">
+    <row r="22" ht="230.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -3748,17 +3675,17 @@
       <c r="Y22" s="6"/>
       <c r="Z22" s="6"/>
       <c r="AA22" s="6"/>
-      <c r="AB22" s="55"/>
-      <c r="AC22" s="56"/>
-      <c r="AD22" s="55"/>
-      <c r="AE22" s="55"/>
-      <c r="AF22" s="55"/>
-      <c r="AG22" s="55"/>
-      <c r="AH22" s="55"/>
-      <c r="AI22" s="55"/>
+      <c r="AB22" s="56"/>
+      <c r="AC22" s="57"/>
+      <c r="AD22" s="56"/>
+      <c r="AE22" s="56"/>
+      <c r="AF22" s="56"/>
+      <c r="AG22" s="56"/>
+      <c r="AH22" s="56"/>
+      <c r="AI22" s="56"/>
       <c r="AJ22" s="6"/>
     </row>
-    <row r="23" ht="187.2" customHeight="1">
+    <row r="23" ht="187.2" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -3786,17 +3713,17 @@
       <c r="Y23" s="6"/>
       <c r="Z23" s="6"/>
       <c r="AA23" s="6"/>
-      <c r="AB23" s="53"/>
-      <c r="AC23" s="54"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="53"/>
-      <c r="AF23" s="53"/>
-      <c r="AG23" s="53"/>
-      <c r="AH23" s="53"/>
-      <c r="AI23" s="53"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="55"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="54"/>
+      <c r="AG23" s="54"/>
+      <c r="AH23" s="54"/>
+      <c r="AI23" s="54"/>
       <c r="AJ23" s="6"/>
     </row>
-    <row r="24" ht="216" customHeight="1">
+    <row r="24" ht="216" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -3824,17 +3751,17 @@
       <c r="Y24" s="6"/>
       <c r="Z24" s="6"/>
       <c r="AA24" s="6"/>
-      <c r="AB24" s="55"/>
-      <c r="AC24" s="56"/>
-      <c r="AD24" s="55"/>
-      <c r="AE24" s="55"/>
-      <c r="AF24" s="55"/>
-      <c r="AG24" s="55"/>
-      <c r="AH24" s="55"/>
-      <c r="AI24" s="55"/>
+      <c r="AB24" s="56"/>
+      <c r="AC24" s="57"/>
+      <c r="AD24" s="56"/>
+      <c r="AE24" s="56"/>
+      <c r="AF24" s="56"/>
+      <c r="AG24" s="56"/>
+      <c r="AH24" s="56"/>
+      <c r="AI24" s="56"/>
       <c r="AJ24" s="6"/>
     </row>
-    <row r="25" ht="158.4" customHeight="1">
+    <row r="25" ht="158.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -3862,17 +3789,17 @@
       <c r="Y25" s="6"/>
       <c r="Z25" s="6"/>
       <c r="AA25" s="6"/>
-      <c r="AB25" s="53"/>
-      <c r="AC25" s="54"/>
-      <c r="AD25" s="53"/>
-      <c r="AE25" s="53"/>
-      <c r="AF25" s="53"/>
-      <c r="AG25" s="53"/>
-      <c r="AH25" s="53"/>
-      <c r="AI25" s="53"/>
+      <c r="AB25" s="54"/>
+      <c r="AC25" s="55"/>
+      <c r="AD25" s="54"/>
+      <c r="AE25" s="54"/>
+      <c r="AF25" s="54"/>
+      <c r="AG25" s="54"/>
+      <c r="AH25" s="54"/>
+      <c r="AI25" s="54"/>
       <c r="AJ25" s="6"/>
     </row>
-    <row r="26" ht="129.6" customHeight="1">
+    <row r="26" ht="129.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -3900,17 +3827,17 @@
       <c r="Y26" s="6"/>
       <c r="Z26" s="6"/>
       <c r="AA26" s="6"/>
-      <c r="AB26" s="55"/>
-      <c r="AC26" s="56"/>
-      <c r="AD26" s="55"/>
-      <c r="AE26" s="55"/>
-      <c r="AF26" s="55"/>
-      <c r="AG26" s="55"/>
-      <c r="AH26" s="55"/>
-      <c r="AI26" s="55"/>
+      <c r="AB26" s="56"/>
+      <c r="AC26" s="57"/>
+      <c r="AD26" s="56"/>
+      <c r="AE26" s="56"/>
+      <c r="AF26" s="56"/>
+      <c r="AG26" s="56"/>
+      <c r="AH26" s="56"/>
+      <c r="AI26" s="56"/>
       <c r="AJ26" s="6"/>
     </row>
-    <row r="27" ht="216" customHeight="1">
+    <row r="27" ht="216" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -3938,17 +3865,17 @@
       <c r="Y27" s="6"/>
       <c r="Z27" s="6"/>
       <c r="AA27" s="6"/>
-      <c r="AB27" s="53"/>
-      <c r="AC27" s="54"/>
-      <c r="AD27" s="53"/>
-      <c r="AE27" s="53"/>
-      <c r="AF27" s="53"/>
-      <c r="AG27" s="53"/>
-      <c r="AH27" s="53"/>
-      <c r="AI27" s="53"/>
+      <c r="AB27" s="54"/>
+      <c r="AC27" s="55"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="54"/>
+      <c r="AG27" s="54"/>
+      <c r="AH27" s="54"/>
+      <c r="AI27" s="54"/>
       <c r="AJ27" s="6"/>
     </row>
-    <row r="28" ht="244.8" customHeight="1">
+    <row r="28" ht="244.8" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -3976,17 +3903,17 @@
       <c r="Y28" s="6"/>
       <c r="Z28" s="6"/>
       <c r="AA28" s="6"/>
-      <c r="AB28" s="55"/>
-      <c r="AC28" s="56"/>
-      <c r="AD28" s="55"/>
-      <c r="AE28" s="55"/>
-      <c r="AF28" s="55"/>
-      <c r="AG28" s="55"/>
-      <c r="AH28" s="55"/>
-      <c r="AI28" s="55"/>
+      <c r="AB28" s="56"/>
+      <c r="AC28" s="57"/>
+      <c r="AD28" s="56"/>
+      <c r="AE28" s="56"/>
+      <c r="AF28" s="56"/>
+      <c r="AG28" s="56"/>
+      <c r="AH28" s="56"/>
+      <c r="AI28" s="56"/>
       <c r="AJ28" s="6"/>
     </row>
-    <row r="29" ht="187.2" customHeight="1">
+    <row r="29" ht="187.2" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -4014,17 +3941,17 @@
       <c r="Y29" s="6"/>
       <c r="Z29" s="6"/>
       <c r="AA29" s="6"/>
-      <c r="AB29" s="53"/>
-      <c r="AC29" s="54"/>
-      <c r="AD29" s="53"/>
-      <c r="AE29" s="53"/>
-      <c r="AF29" s="53"/>
-      <c r="AG29" s="53"/>
-      <c r="AH29" s="53"/>
-      <c r="AI29" s="53"/>
+      <c r="AB29" s="54"/>
+      <c r="AC29" s="55"/>
+      <c r="AD29" s="54"/>
+      <c r="AE29" s="54"/>
+      <c r="AF29" s="54"/>
+      <c r="AG29" s="54"/>
+      <c r="AH29" s="54"/>
+      <c r="AI29" s="54"/>
       <c r="AJ29" s="6"/>
     </row>
-    <row r="30" ht="158.4" customHeight="1">
+    <row r="30" ht="158.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -4052,17 +3979,17 @@
       <c r="Y30" s="6"/>
       <c r="Z30" s="6"/>
       <c r="AA30" s="6"/>
-      <c r="AB30" s="55"/>
-      <c r="AC30" s="56"/>
-      <c r="AD30" s="55"/>
-      <c r="AE30" s="55"/>
-      <c r="AF30" s="55"/>
-      <c r="AG30" s="55"/>
-      <c r="AH30" s="55"/>
-      <c r="AI30" s="55"/>
+      <c r="AB30" s="56"/>
+      <c r="AC30" s="57"/>
+      <c r="AD30" s="56"/>
+      <c r="AE30" s="56"/>
+      <c r="AF30" s="56"/>
+      <c r="AG30" s="56"/>
+      <c r="AH30" s="56"/>
+      <c r="AI30" s="56"/>
       <c r="AJ30" s="6"/>
     </row>
-    <row r="31" ht="14.4" customHeight="1">
+    <row r="31" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -4090,17 +4017,17 @@
       <c r="Y31" s="6"/>
       <c r="Z31" s="6"/>
       <c r="AA31" s="6"/>
-      <c r="AB31" s="53"/>
-      <c r="AC31" s="54"/>
-      <c r="AD31" s="53"/>
-      <c r="AE31" s="53"/>
-      <c r="AF31" s="53"/>
-      <c r="AG31" s="53"/>
-      <c r="AH31" s="53"/>
-      <c r="AI31" s="53"/>
+      <c r="AB31" s="54"/>
+      <c r="AC31" s="55"/>
+      <c r="AD31" s="54"/>
+      <c r="AE31" s="54"/>
+      <c r="AF31" s="54"/>
+      <c r="AG31" s="54"/>
+      <c r="AH31" s="54"/>
+      <c r="AI31" s="54"/>
       <c r="AJ31" s="6"/>
     </row>
-    <row r="32" ht="14.4" customHeight="1">
+    <row r="32" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -4128,17 +4055,17 @@
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
       <c r="AA32" s="6"/>
-      <c r="AB32" s="55"/>
-      <c r="AC32" s="56"/>
-      <c r="AD32" s="55"/>
-      <c r="AE32" s="55"/>
-      <c r="AF32" s="55"/>
-      <c r="AG32" s="55"/>
-      <c r="AH32" s="55"/>
-      <c r="AI32" s="55"/>
+      <c r="AB32" s="56"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="56"/>
+      <c r="AE32" s="56"/>
+      <c r="AF32" s="56"/>
+      <c r="AG32" s="56"/>
+      <c r="AH32" s="56"/>
+      <c r="AI32" s="56"/>
       <c r="AJ32" s="6"/>
     </row>
-    <row r="33" ht="14.4" customHeight="1">
+    <row r="33" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -4166,17 +4093,17 @@
       <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
-      <c r="AB33" s="53"/>
-      <c r="AC33" s="54"/>
-      <c r="AD33" s="53"/>
-      <c r="AE33" s="53"/>
-      <c r="AF33" s="53"/>
-      <c r="AG33" s="53"/>
-      <c r="AH33" s="53"/>
-      <c r="AI33" s="53"/>
+      <c r="AB33" s="54"/>
+      <c r="AC33" s="55"/>
+      <c r="AD33" s="54"/>
+      <c r="AE33" s="54"/>
+      <c r="AF33" s="54"/>
+      <c r="AG33" s="54"/>
+      <c r="AH33" s="54"/>
+      <c r="AI33" s="54"/>
       <c r="AJ33" s="6"/>
     </row>
-    <row r="34" ht="14.4" customHeight="1">
+    <row r="34" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -4204,17 +4131,17 @@
       <c r="Y34" s="6"/>
       <c r="Z34" s="6"/>
       <c r="AA34" s="6"/>
-      <c r="AB34" s="55"/>
-      <c r="AC34" s="56"/>
-      <c r="AD34" s="55"/>
-      <c r="AE34" s="55"/>
-      <c r="AF34" s="55"/>
-      <c r="AG34" s="55"/>
-      <c r="AH34" s="55"/>
-      <c r="AI34" s="55"/>
+      <c r="AB34" s="56"/>
+      <c r="AC34" s="57"/>
+      <c r="AD34" s="56"/>
+      <c r="AE34" s="56"/>
+      <c r="AF34" s="56"/>
+      <c r="AG34" s="56"/>
+      <c r="AH34" s="56"/>
+      <c r="AI34" s="56"/>
       <c r="AJ34" s="6"/>
     </row>
-    <row r="35" ht="14.4" customHeight="1">
+    <row r="35" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -4242,17 +4169,17 @@
       <c r="Y35" s="6"/>
       <c r="Z35" s="6"/>
       <c r="AA35" s="6"/>
-      <c r="AB35" s="53"/>
-      <c r="AC35" s="54"/>
-      <c r="AD35" s="53"/>
-      <c r="AE35" s="53"/>
-      <c r="AF35" s="53"/>
-      <c r="AG35" s="53"/>
-      <c r="AH35" s="53"/>
-      <c r="AI35" s="53"/>
+      <c r="AB35" s="54"/>
+      <c r="AC35" s="55"/>
+      <c r="AD35" s="54"/>
+      <c r="AE35" s="54"/>
+      <c r="AF35" s="54"/>
+      <c r="AG35" s="54"/>
+      <c r="AH35" s="54"/>
+      <c r="AI35" s="54"/>
       <c r="AJ35" s="6"/>
     </row>
-    <row r="36" ht="14.4" customHeight="1">
+    <row r="36" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -4280,17 +4207,17 @@
       <c r="Y36" s="6"/>
       <c r="Z36" s="6"/>
       <c r="AA36" s="6"/>
-      <c r="AB36" s="55"/>
-      <c r="AC36" s="56"/>
-      <c r="AD36" s="55"/>
-      <c r="AE36" s="55"/>
-      <c r="AF36" s="55"/>
-      <c r="AG36" s="55"/>
-      <c r="AH36" s="55"/>
-      <c r="AI36" s="55"/>
+      <c r="AB36" s="56"/>
+      <c r="AC36" s="57"/>
+      <c r="AD36" s="56"/>
+      <c r="AE36" s="56"/>
+      <c r="AF36" s="56"/>
+      <c r="AG36" s="56"/>
+      <c r="AH36" s="56"/>
+      <c r="AI36" s="56"/>
       <c r="AJ36" s="6"/>
     </row>
-    <row r="37" ht="14.4" customHeight="1">
+    <row r="37" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -4318,17 +4245,17 @@
       <c r="Y37" s="6"/>
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
-      <c r="AB37" s="53"/>
-      <c r="AC37" s="54"/>
-      <c r="AD37" s="53"/>
-      <c r="AE37" s="53"/>
-      <c r="AF37" s="53"/>
-      <c r="AG37" s="53"/>
-      <c r="AH37" s="53"/>
-      <c r="AI37" s="53"/>
+      <c r="AB37" s="54"/>
+      <c r="AC37" s="55"/>
+      <c r="AD37" s="54"/>
+      <c r="AE37" s="54"/>
+      <c r="AF37" s="54"/>
+      <c r="AG37" s="54"/>
+      <c r="AH37" s="54"/>
+      <c r="AI37" s="54"/>
       <c r="AJ37" s="6"/>
     </row>
-    <row r="38" ht="14.4" customHeight="1">
+    <row r="38" ht="14.4" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -4356,17 +4283,17 @@
       <c r="Y38" s="6"/>
       <c r="Z38" s="6"/>
       <c r="AA38" s="6"/>
-      <c r="AB38" s="55"/>
-      <c r="AC38" s="56"/>
-      <c r="AD38" s="55"/>
-      <c r="AE38" s="55"/>
-      <c r="AF38" s="55"/>
-      <c r="AG38" s="55"/>
-      <c r="AH38" s="55"/>
-      <c r="AI38" s="55"/>
+      <c r="AB38" s="56"/>
+      <c r="AC38" s="57"/>
+      <c r="AD38" s="56"/>
+      <c r="AE38" s="56"/>
+      <c r="AF38" s="56"/>
+      <c r="AG38" s="56"/>
+      <c r="AH38" s="56"/>
+      <c r="AI38" s="56"/>
       <c r="AJ38" s="6"/>
     </row>
-    <row r="39" ht="15.6" customHeight="1">
+    <row r="39" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -4394,17 +4321,17 @@
       <c r="Y39" s="6"/>
       <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
-      <c r="AB39" s="53"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="53"/>
-      <c r="AE39" s="53"/>
-      <c r="AF39" s="53"/>
-      <c r="AG39" s="53"/>
-      <c r="AH39" s="53"/>
-      <c r="AI39" s="53"/>
+      <c r="AB39" s="54"/>
+      <c r="AC39" s="55"/>
+      <c r="AD39" s="54"/>
+      <c r="AE39" s="54"/>
+      <c r="AF39" s="54"/>
+      <c r="AG39" s="54"/>
+      <c r="AH39" s="54"/>
+      <c r="AI39" s="54"/>
       <c r="AJ39" s="6"/>
     </row>
-    <row r="40" ht="15.6" customHeight="1">
+    <row r="40" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -4432,17 +4359,17 @@
       <c r="Y40" s="6"/>
       <c r="Z40" s="6"/>
       <c r="AA40" s="6"/>
-      <c r="AB40" s="55"/>
-      <c r="AC40" s="56"/>
-      <c r="AD40" s="55"/>
-      <c r="AE40" s="55"/>
-      <c r="AF40" s="55"/>
-      <c r="AG40" s="55"/>
-      <c r="AH40" s="55"/>
-      <c r="AI40" s="55"/>
+      <c r="AB40" s="56"/>
+      <c r="AC40" s="57"/>
+      <c r="AD40" s="56"/>
+      <c r="AE40" s="56"/>
+      <c r="AF40" s="56"/>
+      <c r="AG40" s="56"/>
+      <c r="AH40" s="56"/>
+      <c r="AI40" s="56"/>
       <c r="AJ40" s="6"/>
     </row>
-    <row r="41" ht="15.6" customHeight="1">
+    <row r="41" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -4470,17 +4397,17 @@
       <c r="Y41" s="6"/>
       <c r="Z41" s="6"/>
       <c r="AA41" s="6"/>
-      <c r="AB41" s="53"/>
-      <c r="AC41" s="54"/>
-      <c r="AD41" s="53"/>
-      <c r="AE41" s="53"/>
-      <c r="AF41" s="53"/>
-      <c r="AG41" s="53"/>
-      <c r="AH41" s="53"/>
-      <c r="AI41" s="53"/>
+      <c r="AB41" s="54"/>
+      <c r="AC41" s="55"/>
+      <c r="AD41" s="54"/>
+      <c r="AE41" s="54"/>
+      <c r="AF41" s="54"/>
+      <c r="AG41" s="54"/>
+      <c r="AH41" s="54"/>
+      <c r="AI41" s="54"/>
       <c r="AJ41" s="6"/>
     </row>
-    <row r="42" ht="15.6" customHeight="1">
+    <row r="42" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -4508,17 +4435,17 @@
       <c r="Y42" s="6"/>
       <c r="Z42" s="6"/>
       <c r="AA42" s="6"/>
-      <c r="AB42" s="55"/>
-      <c r="AC42" s="56"/>
-      <c r="AD42" s="55"/>
-      <c r="AE42" s="55"/>
-      <c r="AF42" s="55"/>
-      <c r="AG42" s="55"/>
-      <c r="AH42" s="55"/>
-      <c r="AI42" s="55"/>
+      <c r="AB42" s="56"/>
+      <c r="AC42" s="57"/>
+      <c r="AD42" s="56"/>
+      <c r="AE42" s="56"/>
+      <c r="AF42" s="56"/>
+      <c r="AG42" s="56"/>
+      <c r="AH42" s="56"/>
+      <c r="AI42" s="56"/>
       <c r="AJ42" s="6"/>
     </row>
-    <row r="43" ht="15.6" customHeight="1">
+    <row r="43" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -4546,17 +4473,17 @@
       <c r="Y43" s="6"/>
       <c r="Z43" s="6"/>
       <c r="AA43" s="6"/>
-      <c r="AB43" s="53"/>
-      <c r="AC43" s="54"/>
-      <c r="AD43" s="53"/>
-      <c r="AE43" s="53"/>
-      <c r="AF43" s="53"/>
-      <c r="AG43" s="53"/>
-      <c r="AH43" s="53"/>
-      <c r="AI43" s="53"/>
+      <c r="AB43" s="54"/>
+      <c r="AC43" s="55"/>
+      <c r="AD43" s="54"/>
+      <c r="AE43" s="54"/>
+      <c r="AF43" s="54"/>
+      <c r="AG43" s="54"/>
+      <c r="AH43" s="54"/>
+      <c r="AI43" s="54"/>
       <c r="AJ43" s="6"/>
     </row>
-    <row r="44" ht="15.6" customHeight="1">
+    <row r="44" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -4584,17 +4511,17 @@
       <c r="Y44" s="6"/>
       <c r="Z44" s="6"/>
       <c r="AA44" s="6"/>
-      <c r="AB44" s="55"/>
-      <c r="AC44" s="56"/>
-      <c r="AD44" s="55"/>
-      <c r="AE44" s="55"/>
-      <c r="AF44" s="55"/>
-      <c r="AG44" s="55"/>
-      <c r="AH44" s="55"/>
-      <c r="AI44" s="55"/>
+      <c r="AB44" s="56"/>
+      <c r="AC44" s="57"/>
+      <c r="AD44" s="56"/>
+      <c r="AE44" s="56"/>
+      <c r="AF44" s="56"/>
+      <c r="AG44" s="56"/>
+      <c r="AH44" s="56"/>
+      <c r="AI44" s="56"/>
       <c r="AJ44" s="6"/>
     </row>
-    <row r="45" ht="15.6" customHeight="1">
+    <row r="45" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -4622,17 +4549,17 @@
       <c r="Y45" s="6"/>
       <c r="Z45" s="6"/>
       <c r="AA45" s="6"/>
-      <c r="AB45" s="53"/>
-      <c r="AC45" s="54"/>
-      <c r="AD45" s="53"/>
-      <c r="AE45" s="53"/>
-      <c r="AF45" s="53"/>
-      <c r="AG45" s="53"/>
-      <c r="AH45" s="53"/>
-      <c r="AI45" s="53"/>
+      <c r="AB45" s="54"/>
+      <c r="AC45" s="55"/>
+      <c r="AD45" s="54"/>
+      <c r="AE45" s="54"/>
+      <c r="AF45" s="54"/>
+      <c r="AG45" s="54"/>
+      <c r="AH45" s="54"/>
+      <c r="AI45" s="54"/>
       <c r="AJ45" s="6"/>
     </row>
-    <row r="46" ht="15.6" customHeight="1">
+    <row r="46" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -4660,17 +4587,17 @@
       <c r="Y46" s="6"/>
       <c r="Z46" s="6"/>
       <c r="AA46" s="6"/>
-      <c r="AB46" s="55"/>
-      <c r="AC46" s="56"/>
-      <c r="AD46" s="55"/>
-      <c r="AE46" s="55"/>
-      <c r="AF46" s="55"/>
-      <c r="AG46" s="55"/>
-      <c r="AH46" s="55"/>
-      <c r="AI46" s="55"/>
+      <c r="AB46" s="56"/>
+      <c r="AC46" s="57"/>
+      <c r="AD46" s="56"/>
+      <c r="AE46" s="56"/>
+      <c r="AF46" s="56"/>
+      <c r="AG46" s="56"/>
+      <c r="AH46" s="56"/>
+      <c r="AI46" s="56"/>
       <c r="AJ46" s="6"/>
     </row>
-    <row r="47" ht="15.6" customHeight="1">
+    <row r="47" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -4698,17 +4625,17 @@
       <c r="Y47" s="6"/>
       <c r="Z47" s="6"/>
       <c r="AA47" s="6"/>
-      <c r="AB47" s="53"/>
-      <c r="AC47" s="54"/>
-      <c r="AD47" s="53"/>
-      <c r="AE47" s="53"/>
-      <c r="AF47" s="53"/>
-      <c r="AG47" s="53"/>
-      <c r="AH47" s="53"/>
-      <c r="AI47" s="53"/>
+      <c r="AB47" s="54"/>
+      <c r="AC47" s="55"/>
+      <c r="AD47" s="54"/>
+      <c r="AE47" s="54"/>
+      <c r="AF47" s="54"/>
+      <c r="AG47" s="54"/>
+      <c r="AH47" s="54"/>
+      <c r="AI47" s="54"/>
       <c r="AJ47" s="6"/>
     </row>
-    <row r="48" ht="15.6" customHeight="1">
+    <row r="48" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -4736,17 +4663,17 @@
       <c r="Y48" s="6"/>
       <c r="Z48" s="6"/>
       <c r="AA48" s="6"/>
-      <c r="AB48" s="55"/>
-      <c r="AC48" s="56"/>
-      <c r="AD48" s="55"/>
-      <c r="AE48" s="55"/>
-      <c r="AF48" s="55"/>
-      <c r="AG48" s="55"/>
-      <c r="AH48" s="55"/>
-      <c r="AI48" s="55"/>
+      <c r="AB48" s="56"/>
+      <c r="AC48" s="57"/>
+      <c r="AD48" s="56"/>
+      <c r="AE48" s="56"/>
+      <c r="AF48" s="56"/>
+      <c r="AG48" s="56"/>
+      <c r="AH48" s="56"/>
+      <c r="AI48" s="56"/>
       <c r="AJ48" s="6"/>
     </row>
-    <row r="49" ht="15.6" customHeight="1">
+    <row r="49" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -4774,17 +4701,17 @@
       <c r="Y49" s="6"/>
       <c r="Z49" s="6"/>
       <c r="AA49" s="6"/>
-      <c r="AB49" s="53"/>
-      <c r="AC49" s="54"/>
-      <c r="AD49" s="53"/>
-      <c r="AE49" s="53"/>
-      <c r="AF49" s="53"/>
-      <c r="AG49" s="53"/>
-      <c r="AH49" s="53"/>
-      <c r="AI49" s="53"/>
+      <c r="AB49" s="54"/>
+      <c r="AC49" s="55"/>
+      <c r="AD49" s="54"/>
+      <c r="AE49" s="54"/>
+      <c r="AF49" s="54"/>
+      <c r="AG49" s="54"/>
+      <c r="AH49" s="54"/>
+      <c r="AI49" s="54"/>
       <c r="AJ49" s="6"/>
     </row>
-    <row r="50" ht="15.6" customHeight="1">
+    <row r="50" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -4812,17 +4739,17 @@
       <c r="Y50" s="6"/>
       <c r="Z50" s="6"/>
       <c r="AA50" s="6"/>
-      <c r="AB50" s="55"/>
-      <c r="AC50" s="56"/>
-      <c r="AD50" s="55"/>
-      <c r="AE50" s="55"/>
-      <c r="AF50" s="55"/>
-      <c r="AG50" s="55"/>
-      <c r="AH50" s="55"/>
-      <c r="AI50" s="55"/>
+      <c r="AB50" s="56"/>
+      <c r="AC50" s="57"/>
+      <c r="AD50" s="56"/>
+      <c r="AE50" s="56"/>
+      <c r="AF50" s="56"/>
+      <c r="AG50" s="56"/>
+      <c r="AH50" s="56"/>
+      <c r="AI50" s="56"/>
       <c r="AJ50" s="6"/>
     </row>
-    <row r="51" ht="15.6" customHeight="1">
+    <row r="51" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -4850,17 +4777,17 @@
       <c r="Y51" s="6"/>
       <c r="Z51" s="6"/>
       <c r="AA51" s="6"/>
-      <c r="AB51" s="53"/>
-      <c r="AC51" s="54"/>
-      <c r="AD51" s="53"/>
-      <c r="AE51" s="53"/>
-      <c r="AF51" s="53"/>
-      <c r="AG51" s="53"/>
-      <c r="AH51" s="53"/>
-      <c r="AI51" s="53"/>
+      <c r="AB51" s="54"/>
+      <c r="AC51" s="55"/>
+      <c r="AD51" s="54"/>
+      <c r="AE51" s="54"/>
+      <c r="AF51" s="54"/>
+      <c r="AG51" s="54"/>
+      <c r="AH51" s="54"/>
+      <c r="AI51" s="54"/>
       <c r="AJ51" s="6"/>
     </row>
-    <row r="52" ht="15.6" customHeight="1">
+    <row r="52" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -4888,17 +4815,17 @@
       <c r="Y52" s="6"/>
       <c r="Z52" s="6"/>
       <c r="AA52" s="6"/>
-      <c r="AB52" s="55"/>
-      <c r="AC52" s="56"/>
-      <c r="AD52" s="55"/>
-      <c r="AE52" s="55"/>
-      <c r="AF52" s="55"/>
-      <c r="AG52" s="55"/>
-      <c r="AH52" s="55"/>
-      <c r="AI52" s="55"/>
+      <c r="AB52" s="56"/>
+      <c r="AC52" s="57"/>
+      <c r="AD52" s="56"/>
+      <c r="AE52" s="56"/>
+      <c r="AF52" s="56"/>
+      <c r="AG52" s="56"/>
+      <c r="AH52" s="56"/>
+      <c r="AI52" s="56"/>
       <c r="AJ52" s="6"/>
     </row>
-    <row r="53" ht="15.6" customHeight="1">
+    <row r="53" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -4926,17 +4853,17 @@
       <c r="Y53" s="6"/>
       <c r="Z53" s="6"/>
       <c r="AA53" s="6"/>
-      <c r="AB53" s="53"/>
-      <c r="AC53" s="54"/>
-      <c r="AD53" s="53"/>
-      <c r="AE53" s="53"/>
-      <c r="AF53" s="53"/>
-      <c r="AG53" s="53"/>
-      <c r="AH53" s="53"/>
-      <c r="AI53" s="53"/>
+      <c r="AB53" s="54"/>
+      <c r="AC53" s="55"/>
+      <c r="AD53" s="54"/>
+      <c r="AE53" s="54"/>
+      <c r="AF53" s="54"/>
+      <c r="AG53" s="54"/>
+      <c r="AH53" s="54"/>
+      <c r="AI53" s="54"/>
       <c r="AJ53" s="6"/>
     </row>
-    <row r="54" ht="15.6" customHeight="1">
+    <row r="54" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -4964,17 +4891,17 @@
       <c r="Y54" s="6"/>
       <c r="Z54" s="6"/>
       <c r="AA54" s="6"/>
-      <c r="AB54" s="55"/>
-      <c r="AC54" s="56"/>
-      <c r="AD54" s="55"/>
-      <c r="AE54" s="55"/>
-      <c r="AF54" s="55"/>
-      <c r="AG54" s="55"/>
-      <c r="AH54" s="55"/>
-      <c r="AI54" s="55"/>
+      <c r="AB54" s="56"/>
+      <c r="AC54" s="57"/>
+      <c r="AD54" s="56"/>
+      <c r="AE54" s="56"/>
+      <c r="AF54" s="56"/>
+      <c r="AG54" s="56"/>
+      <c r="AH54" s="56"/>
+      <c r="AI54" s="56"/>
       <c r="AJ54" s="6"/>
     </row>
-    <row r="55" ht="15.6" customHeight="1">
+    <row r="55" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
@@ -5002,17 +4929,17 @@
       <c r="Y55" s="6"/>
       <c r="Z55" s="6"/>
       <c r="AA55" s="6"/>
-      <c r="AB55" s="53"/>
-      <c r="AC55" s="54"/>
-      <c r="AD55" s="53"/>
-      <c r="AE55" s="53"/>
-      <c r="AF55" s="53"/>
-      <c r="AG55" s="53"/>
-      <c r="AH55" s="53"/>
-      <c r="AI55" s="53"/>
+      <c r="AB55" s="54"/>
+      <c r="AC55" s="55"/>
+      <c r="AD55" s="54"/>
+      <c r="AE55" s="54"/>
+      <c r="AF55" s="54"/>
+      <c r="AG55" s="54"/>
+      <c r="AH55" s="54"/>
+      <c r="AI55" s="54"/>
       <c r="AJ55" s="6"/>
     </row>
-    <row r="56" ht="15.6" customHeight="1">
+    <row r="56" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -5040,17 +4967,17 @@
       <c r="Y56" s="6"/>
       <c r="Z56" s="6"/>
       <c r="AA56" s="6"/>
-      <c r="AB56" s="55"/>
-      <c r="AC56" s="56"/>
-      <c r="AD56" s="55"/>
-      <c r="AE56" s="55"/>
-      <c r="AF56" s="55"/>
-      <c r="AG56" s="55"/>
-      <c r="AH56" s="55"/>
-      <c r="AI56" s="55"/>
+      <c r="AB56" s="56"/>
+      <c r="AC56" s="57"/>
+      <c r="AD56" s="56"/>
+      <c r="AE56" s="56"/>
+      <c r="AF56" s="56"/>
+      <c r="AG56" s="56"/>
+      <c r="AH56" s="56"/>
+      <c r="AI56" s="56"/>
       <c r="AJ56" s="6"/>
     </row>
-    <row r="57" ht="15.6" customHeight="1">
+    <row r="57" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -5078,17 +5005,17 @@
       <c r="Y57" s="6"/>
       <c r="Z57" s="6"/>
       <c r="AA57" s="6"/>
-      <c r="AB57" s="53"/>
-      <c r="AC57" s="54"/>
-      <c r="AD57" s="53"/>
-      <c r="AE57" s="53"/>
-      <c r="AF57" s="53"/>
-      <c r="AG57" s="53"/>
-      <c r="AH57" s="53"/>
-      <c r="AI57" s="53"/>
+      <c r="AB57" s="54"/>
+      <c r="AC57" s="55"/>
+      <c r="AD57" s="54"/>
+      <c r="AE57" s="54"/>
+      <c r="AF57" s="54"/>
+      <c r="AG57" s="54"/>
+      <c r="AH57" s="54"/>
+      <c r="AI57" s="54"/>
       <c r="AJ57" s="6"/>
     </row>
-    <row r="58" ht="15.6" customHeight="1">
+    <row r="58" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -5116,17 +5043,17 @@
       <c r="Y58" s="6"/>
       <c r="Z58" s="6"/>
       <c r="AA58" s="6"/>
-      <c r="AB58" s="55"/>
-      <c r="AC58" s="56"/>
-      <c r="AD58" s="55"/>
-      <c r="AE58" s="55"/>
-      <c r="AF58" s="55"/>
-      <c r="AG58" s="55"/>
-      <c r="AH58" s="55"/>
-      <c r="AI58" s="55"/>
+      <c r="AB58" s="56"/>
+      <c r="AC58" s="57"/>
+      <c r="AD58" s="56"/>
+      <c r="AE58" s="56"/>
+      <c r="AF58" s="56"/>
+      <c r="AG58" s="56"/>
+      <c r="AH58" s="56"/>
+      <c r="AI58" s="56"/>
       <c r="AJ58" s="6"/>
     </row>
-    <row r="59" ht="15.6" customHeight="1">
+    <row r="59" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -5154,17 +5081,17 @@
       <c r="Y59" s="6"/>
       <c r="Z59" s="6"/>
       <c r="AA59" s="6"/>
-      <c r="AB59" s="53"/>
-      <c r="AC59" s="54"/>
-      <c r="AD59" s="53"/>
-      <c r="AE59" s="53"/>
-      <c r="AF59" s="53"/>
-      <c r="AG59" s="53"/>
-      <c r="AH59" s="53"/>
-      <c r="AI59" s="53"/>
+      <c r="AB59" s="54"/>
+      <c r="AC59" s="55"/>
+      <c r="AD59" s="54"/>
+      <c r="AE59" s="54"/>
+      <c r="AF59" s="54"/>
+      <c r="AG59" s="54"/>
+      <c r="AH59" s="54"/>
+      <c r="AI59" s="54"/>
       <c r="AJ59" s="6"/>
     </row>
-    <row r="60" ht="15.6" customHeight="1">
+    <row r="60" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -5192,17 +5119,17 @@
       <c r="Y60" s="6"/>
       <c r="Z60" s="6"/>
       <c r="AA60" s="6"/>
-      <c r="AB60" s="55"/>
-      <c r="AC60" s="56"/>
-      <c r="AD60" s="55"/>
-      <c r="AE60" s="55"/>
-      <c r="AF60" s="55"/>
-      <c r="AG60" s="55"/>
-      <c r="AH60" s="55"/>
-      <c r="AI60" s="55"/>
+      <c r="AB60" s="56"/>
+      <c r="AC60" s="57"/>
+      <c r="AD60" s="56"/>
+      <c r="AE60" s="56"/>
+      <c r="AF60" s="56"/>
+      <c r="AG60" s="56"/>
+      <c r="AH60" s="56"/>
+      <c r="AI60" s="56"/>
       <c r="AJ60" s="6"/>
     </row>
-    <row r="61" ht="15.6" customHeight="1">
+    <row r="61" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -5230,17 +5157,17 @@
       <c r="Y61" s="6"/>
       <c r="Z61" s="6"/>
       <c r="AA61" s="6"/>
-      <c r="AB61" s="53"/>
-      <c r="AC61" s="54"/>
-      <c r="AD61" s="53"/>
-      <c r="AE61" s="53"/>
-      <c r="AF61" s="53"/>
-      <c r="AG61" s="53"/>
-      <c r="AH61" s="53"/>
-      <c r="AI61" s="53"/>
+      <c r="AB61" s="54"/>
+      <c r="AC61" s="55"/>
+      <c r="AD61" s="54"/>
+      <c r="AE61" s="54"/>
+      <c r="AF61" s="54"/>
+      <c r="AG61" s="54"/>
+      <c r="AH61" s="54"/>
+      <c r="AI61" s="54"/>
       <c r="AJ61" s="6"/>
     </row>
-    <row r="62" ht="15.6" customHeight="1">
+    <row r="62" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -5268,17 +5195,17 @@
       <c r="Y62" s="6"/>
       <c r="Z62" s="6"/>
       <c r="AA62" s="6"/>
-      <c r="AB62" s="55"/>
-      <c r="AC62" s="56"/>
-      <c r="AD62" s="55"/>
-      <c r="AE62" s="55"/>
-      <c r="AF62" s="55"/>
-      <c r="AG62" s="55"/>
-      <c r="AH62" s="55"/>
-      <c r="AI62" s="55"/>
+      <c r="AB62" s="56"/>
+      <c r="AC62" s="57"/>
+      <c r="AD62" s="56"/>
+      <c r="AE62" s="56"/>
+      <c r="AF62" s="56"/>
+      <c r="AG62" s="56"/>
+      <c r="AH62" s="56"/>
+      <c r="AI62" s="56"/>
       <c r="AJ62" s="6"/>
     </row>
-    <row r="63" ht="15.6" customHeight="1">
+    <row r="63" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -5306,17 +5233,17 @@
       <c r="Y63" s="6"/>
       <c r="Z63" s="6"/>
       <c r="AA63" s="6"/>
-      <c r="AB63" s="53"/>
-      <c r="AC63" s="54"/>
-      <c r="AD63" s="53"/>
-      <c r="AE63" s="53"/>
-      <c r="AF63" s="53"/>
-      <c r="AG63" s="53"/>
-      <c r="AH63" s="53"/>
-      <c r="AI63" s="53"/>
+      <c r="AB63" s="54"/>
+      <c r="AC63" s="55"/>
+      <c r="AD63" s="54"/>
+      <c r="AE63" s="54"/>
+      <c r="AF63" s="54"/>
+      <c r="AG63" s="54"/>
+      <c r="AH63" s="54"/>
+      <c r="AI63" s="54"/>
       <c r="AJ63" s="6"/>
     </row>
-    <row r="64" ht="15.6" customHeight="1">
+    <row r="64" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -5344,17 +5271,17 @@
       <c r="Y64" s="6"/>
       <c r="Z64" s="6"/>
       <c r="AA64" s="6"/>
-      <c r="AB64" s="55"/>
-      <c r="AC64" s="56"/>
-      <c r="AD64" s="55"/>
-      <c r="AE64" s="55"/>
-      <c r="AF64" s="55"/>
-      <c r="AG64" s="55"/>
-      <c r="AH64" s="55"/>
-      <c r="AI64" s="55"/>
+      <c r="AB64" s="56"/>
+      <c r="AC64" s="57"/>
+      <c r="AD64" s="56"/>
+      <c r="AE64" s="56"/>
+      <c r="AF64" s="56"/>
+      <c r="AG64" s="56"/>
+      <c r="AH64" s="56"/>
+      <c r="AI64" s="56"/>
       <c r="AJ64" s="6"/>
     </row>
-    <row r="65" ht="15.6" customHeight="1">
+    <row r="65" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -5382,17 +5309,17 @@
       <c r="Y65" s="6"/>
       <c r="Z65" s="6"/>
       <c r="AA65" s="6"/>
-      <c r="AB65" s="53"/>
-      <c r="AC65" s="54"/>
-      <c r="AD65" s="53"/>
-      <c r="AE65" s="53"/>
-      <c r="AF65" s="53"/>
-      <c r="AG65" s="53"/>
-      <c r="AH65" s="53"/>
-      <c r="AI65" s="53"/>
+      <c r="AB65" s="54"/>
+      <c r="AC65" s="55"/>
+      <c r="AD65" s="54"/>
+      <c r="AE65" s="54"/>
+      <c r="AF65" s="54"/>
+      <c r="AG65" s="54"/>
+      <c r="AH65" s="54"/>
+      <c r="AI65" s="54"/>
       <c r="AJ65" s="6"/>
     </row>
-    <row r="66" ht="15.6" customHeight="1">
+    <row r="66" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -5420,17 +5347,17 @@
       <c r="Y66" s="6"/>
       <c r="Z66" s="6"/>
       <c r="AA66" s="6"/>
-      <c r="AB66" s="55"/>
-      <c r="AC66" s="56"/>
-      <c r="AD66" s="55"/>
-      <c r="AE66" s="55"/>
-      <c r="AF66" s="55"/>
-      <c r="AG66" s="55"/>
-      <c r="AH66" s="55"/>
-      <c r="AI66" s="55"/>
+      <c r="AB66" s="56"/>
+      <c r="AC66" s="57"/>
+      <c r="AD66" s="56"/>
+      <c r="AE66" s="56"/>
+      <c r="AF66" s="56"/>
+      <c r="AG66" s="56"/>
+      <c r="AH66" s="56"/>
+      <c r="AI66" s="56"/>
       <c r="AJ66" s="6"/>
     </row>
-    <row r="67" ht="15.6" customHeight="1">
+    <row r="67" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -5458,17 +5385,17 @@
       <c r="Y67" s="6"/>
       <c r="Z67" s="6"/>
       <c r="AA67" s="6"/>
-      <c r="AB67" s="53"/>
-      <c r="AC67" s="54"/>
-      <c r="AD67" s="53"/>
-      <c r="AE67" s="53"/>
-      <c r="AF67" s="53"/>
-      <c r="AG67" s="53"/>
-      <c r="AH67" s="53"/>
-      <c r="AI67" s="53"/>
+      <c r="AB67" s="54"/>
+      <c r="AC67" s="55"/>
+      <c r="AD67" s="54"/>
+      <c r="AE67" s="54"/>
+      <c r="AF67" s="54"/>
+      <c r="AG67" s="54"/>
+      <c r="AH67" s="54"/>
+      <c r="AI67" s="54"/>
       <c r="AJ67" s="6"/>
     </row>
-    <row r="68" ht="15.6" customHeight="1">
+    <row r="68" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -5496,17 +5423,17 @@
       <c r="Y68" s="6"/>
       <c r="Z68" s="6"/>
       <c r="AA68" s="6"/>
-      <c r="AB68" s="55"/>
-      <c r="AC68" s="56"/>
-      <c r="AD68" s="55"/>
-      <c r="AE68" s="55"/>
-      <c r="AF68" s="55"/>
-      <c r="AG68" s="55"/>
-      <c r="AH68" s="55"/>
-      <c r="AI68" s="55"/>
+      <c r="AB68" s="56"/>
+      <c r="AC68" s="57"/>
+      <c r="AD68" s="56"/>
+      <c r="AE68" s="56"/>
+      <c r="AF68" s="56"/>
+      <c r="AG68" s="56"/>
+      <c r="AH68" s="56"/>
+      <c r="AI68" s="56"/>
       <c r="AJ68" s="6"/>
     </row>
-    <row r="69" ht="15.6" customHeight="1">
+    <row r="69" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -5534,17 +5461,17 @@
       <c r="Y69" s="6"/>
       <c r="Z69" s="6"/>
       <c r="AA69" s="6"/>
-      <c r="AB69" s="53"/>
-      <c r="AC69" s="54"/>
-      <c r="AD69" s="53"/>
-      <c r="AE69" s="53"/>
-      <c r="AF69" s="53"/>
-      <c r="AG69" s="53"/>
-      <c r="AH69" s="53"/>
-      <c r="AI69" s="53"/>
+      <c r="AB69" s="54"/>
+      <c r="AC69" s="55"/>
+      <c r="AD69" s="54"/>
+      <c r="AE69" s="54"/>
+      <c r="AF69" s="54"/>
+      <c r="AG69" s="54"/>
+      <c r="AH69" s="54"/>
+      <c r="AI69" s="54"/>
       <c r="AJ69" s="6"/>
     </row>
-    <row r="70" ht="15.6" customHeight="1">
+    <row r="70" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
@@ -5572,17 +5499,17 @@
       <c r="Y70" s="6"/>
       <c r="Z70" s="6"/>
       <c r="AA70" s="6"/>
-      <c r="AB70" s="55"/>
-      <c r="AC70" s="56"/>
-      <c r="AD70" s="55"/>
-      <c r="AE70" s="55"/>
-      <c r="AF70" s="55"/>
-      <c r="AG70" s="55"/>
-      <c r="AH70" s="55"/>
-      <c r="AI70" s="55"/>
+      <c r="AB70" s="56"/>
+      <c r="AC70" s="57"/>
+      <c r="AD70" s="56"/>
+      <c r="AE70" s="56"/>
+      <c r="AF70" s="56"/>
+      <c r="AG70" s="56"/>
+      <c r="AH70" s="56"/>
+      <c r="AI70" s="56"/>
       <c r="AJ70" s="6"/>
     </row>
-    <row r="71" ht="15.6" customHeight="1">
+    <row r="71" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -5610,17 +5537,17 @@
       <c r="Y71" s="6"/>
       <c r="Z71" s="6"/>
       <c r="AA71" s="6"/>
-      <c r="AB71" s="53"/>
-      <c r="AC71" s="54"/>
-      <c r="AD71" s="53"/>
-      <c r="AE71" s="53"/>
-      <c r="AF71" s="53"/>
-      <c r="AG71" s="53"/>
-      <c r="AH71" s="53"/>
-      <c r="AI71" s="53"/>
+      <c r="AB71" s="54"/>
+      <c r="AC71" s="55"/>
+      <c r="AD71" s="54"/>
+      <c r="AE71" s="54"/>
+      <c r="AF71" s="54"/>
+      <c r="AG71" s="54"/>
+      <c r="AH71" s="54"/>
+      <c r="AI71" s="54"/>
       <c r="AJ71" s="6"/>
     </row>
-    <row r="72" ht="15.6" customHeight="1">
+    <row r="72" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -5648,17 +5575,17 @@
       <c r="Y72" s="6"/>
       <c r="Z72" s="6"/>
       <c r="AA72" s="6"/>
-      <c r="AB72" s="55"/>
-      <c r="AC72" s="56"/>
-      <c r="AD72" s="55"/>
-      <c r="AE72" s="55"/>
-      <c r="AF72" s="55"/>
-      <c r="AG72" s="55"/>
-      <c r="AH72" s="55"/>
-      <c r="AI72" s="55"/>
+      <c r="AB72" s="56"/>
+      <c r="AC72" s="57"/>
+      <c r="AD72" s="56"/>
+      <c r="AE72" s="56"/>
+      <c r="AF72" s="56"/>
+      <c r="AG72" s="56"/>
+      <c r="AH72" s="56"/>
+      <c r="AI72" s="56"/>
       <c r="AJ72" s="6"/>
     </row>
-    <row r="73" ht="15.6" customHeight="1">
+    <row r="73" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -5686,17 +5613,17 @@
       <c r="Y73" s="6"/>
       <c r="Z73" s="6"/>
       <c r="AA73" s="6"/>
-      <c r="AB73" s="53"/>
-      <c r="AC73" s="54"/>
-      <c r="AD73" s="53"/>
-      <c r="AE73" s="53"/>
-      <c r="AF73" s="53"/>
-      <c r="AG73" s="53"/>
-      <c r="AH73" s="53"/>
-      <c r="AI73" s="53"/>
+      <c r="AB73" s="54"/>
+      <c r="AC73" s="55"/>
+      <c r="AD73" s="54"/>
+      <c r="AE73" s="54"/>
+      <c r="AF73" s="54"/>
+      <c r="AG73" s="54"/>
+      <c r="AH73" s="54"/>
+      <c r="AI73" s="54"/>
       <c r="AJ73" s="6"/>
     </row>
-    <row r="74" ht="15.6" customHeight="1">
+    <row r="74" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -5724,17 +5651,17 @@
       <c r="Y74" s="6"/>
       <c r="Z74" s="6"/>
       <c r="AA74" s="6"/>
-      <c r="AB74" s="55"/>
-      <c r="AC74" s="56"/>
-      <c r="AD74" s="55"/>
-      <c r="AE74" s="55"/>
-      <c r="AF74" s="55"/>
-      <c r="AG74" s="55"/>
-      <c r="AH74" s="55"/>
-      <c r="AI74" s="55"/>
+      <c r="AB74" s="56"/>
+      <c r="AC74" s="57"/>
+      <c r="AD74" s="56"/>
+      <c r="AE74" s="56"/>
+      <c r="AF74" s="56"/>
+      <c r="AG74" s="56"/>
+      <c r="AH74" s="56"/>
+      <c r="AI74" s="56"/>
       <c r="AJ74" s="6"/>
     </row>
-    <row r="75" ht="15.6" customHeight="1">
+    <row r="75" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
@@ -5762,17 +5689,17 @@
       <c r="Y75" s="6"/>
       <c r="Z75" s="6"/>
       <c r="AA75" s="6"/>
-      <c r="AB75" s="53"/>
-      <c r="AC75" s="54"/>
-      <c r="AD75" s="53"/>
-      <c r="AE75" s="53"/>
-      <c r="AF75" s="53"/>
-      <c r="AG75" s="53"/>
-      <c r="AH75" s="53"/>
-      <c r="AI75" s="53"/>
+      <c r="AB75" s="54"/>
+      <c r="AC75" s="55"/>
+      <c r="AD75" s="54"/>
+      <c r="AE75" s="54"/>
+      <c r="AF75" s="54"/>
+      <c r="AG75" s="54"/>
+      <c r="AH75" s="54"/>
+      <c r="AI75" s="54"/>
       <c r="AJ75" s="6"/>
     </row>
-    <row r="76" ht="15.6" customHeight="1">
+    <row r="76" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -5800,17 +5727,17 @@
       <c r="Y76" s="6"/>
       <c r="Z76" s="6"/>
       <c r="AA76" s="6"/>
-      <c r="AB76" s="55"/>
-      <c r="AC76" s="56"/>
-      <c r="AD76" s="55"/>
-      <c r="AE76" s="55"/>
-      <c r="AF76" s="55"/>
-      <c r="AG76" s="55"/>
-      <c r="AH76" s="55"/>
-      <c r="AI76" s="55"/>
+      <c r="AB76" s="56"/>
+      <c r="AC76" s="57"/>
+      <c r="AD76" s="56"/>
+      <c r="AE76" s="56"/>
+      <c r="AF76" s="56"/>
+      <c r="AG76" s="56"/>
+      <c r="AH76" s="56"/>
+      <c r="AI76" s="56"/>
       <c r="AJ76" s="6"/>
     </row>
-    <row r="77" ht="15.6" customHeight="1">
+    <row r="77" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -5838,17 +5765,17 @@
       <c r="Y77" s="6"/>
       <c r="Z77" s="6"/>
       <c r="AA77" s="6"/>
-      <c r="AB77" s="53"/>
-      <c r="AC77" s="54"/>
-      <c r="AD77" s="53"/>
-      <c r="AE77" s="53"/>
-      <c r="AF77" s="53"/>
-      <c r="AG77" s="53"/>
-      <c r="AH77" s="53"/>
-      <c r="AI77" s="53"/>
+      <c r="AB77" s="54"/>
+      <c r="AC77" s="55"/>
+      <c r="AD77" s="54"/>
+      <c r="AE77" s="54"/>
+      <c r="AF77" s="54"/>
+      <c r="AG77" s="54"/>
+      <c r="AH77" s="54"/>
+      <c r="AI77" s="54"/>
       <c r="AJ77" s="6"/>
     </row>
-    <row r="78" ht="15.6" customHeight="1">
+    <row r="78" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -5876,17 +5803,17 @@
       <c r="Y78" s="6"/>
       <c r="Z78" s="6"/>
       <c r="AA78" s="6"/>
-      <c r="AB78" s="55"/>
-      <c r="AC78" s="56"/>
-      <c r="AD78" s="55"/>
-      <c r="AE78" s="55"/>
-      <c r="AF78" s="55"/>
-      <c r="AG78" s="55"/>
-      <c r="AH78" s="55"/>
-      <c r="AI78" s="55"/>
+      <c r="AB78" s="56"/>
+      <c r="AC78" s="57"/>
+      <c r="AD78" s="56"/>
+      <c r="AE78" s="56"/>
+      <c r="AF78" s="56"/>
+      <c r="AG78" s="56"/>
+      <c r="AH78" s="56"/>
+      <c r="AI78" s="56"/>
       <c r="AJ78" s="6"/>
     </row>
-    <row r="79" ht="15.6" customHeight="1">
+    <row r="79" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -5914,17 +5841,17 @@
       <c r="Y79" s="6"/>
       <c r="Z79" s="6"/>
       <c r="AA79" s="6"/>
-      <c r="AB79" s="53"/>
-      <c r="AC79" s="54"/>
-      <c r="AD79" s="53"/>
-      <c r="AE79" s="53"/>
-      <c r="AF79" s="53"/>
-      <c r="AG79" s="53"/>
-      <c r="AH79" s="53"/>
-      <c r="AI79" s="53"/>
+      <c r="AB79" s="54"/>
+      <c r="AC79" s="55"/>
+      <c r="AD79" s="54"/>
+      <c r="AE79" s="54"/>
+      <c r="AF79" s="54"/>
+      <c r="AG79" s="54"/>
+      <c r="AH79" s="54"/>
+      <c r="AI79" s="54"/>
       <c r="AJ79" s="6"/>
     </row>
-    <row r="80" ht="15.6" customHeight="1">
+    <row r="80" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -5952,17 +5879,17 @@
       <c r="Y80" s="6"/>
       <c r="Z80" s="6"/>
       <c r="AA80" s="6"/>
-      <c r="AB80" s="55"/>
-      <c r="AC80" s="56"/>
-      <c r="AD80" s="55"/>
-      <c r="AE80" s="55"/>
-      <c r="AF80" s="55"/>
-      <c r="AG80" s="55"/>
-      <c r="AH80" s="55"/>
-      <c r="AI80" s="55"/>
+      <c r="AB80" s="56"/>
+      <c r="AC80" s="57"/>
+      <c r="AD80" s="56"/>
+      <c r="AE80" s="56"/>
+      <c r="AF80" s="56"/>
+      <c r="AG80" s="56"/>
+      <c r="AH80" s="56"/>
+      <c r="AI80" s="56"/>
       <c r="AJ80" s="6"/>
     </row>
-    <row r="81" ht="15.6" customHeight="1">
+    <row r="81" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -5990,17 +5917,17 @@
       <c r="Y81" s="6"/>
       <c r="Z81" s="6"/>
       <c r="AA81" s="6"/>
-      <c r="AB81" s="53"/>
-      <c r="AC81" s="54"/>
-      <c r="AD81" s="53"/>
-      <c r="AE81" s="53"/>
-      <c r="AF81" s="53"/>
-      <c r="AG81" s="53"/>
-      <c r="AH81" s="53"/>
-      <c r="AI81" s="53"/>
+      <c r="AB81" s="54"/>
+      <c r="AC81" s="55"/>
+      <c r="AD81" s="54"/>
+      <c r="AE81" s="54"/>
+      <c r="AF81" s="54"/>
+      <c r="AG81" s="54"/>
+      <c r="AH81" s="54"/>
+      <c r="AI81" s="54"/>
       <c r="AJ81" s="6"/>
     </row>
-    <row r="82" ht="15.6" customHeight="1">
+    <row r="82" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -6028,17 +5955,17 @@
       <c r="Y82" s="6"/>
       <c r="Z82" s="6"/>
       <c r="AA82" s="6"/>
-      <c r="AB82" s="55"/>
-      <c r="AC82" s="56"/>
-      <c r="AD82" s="55"/>
-      <c r="AE82" s="55"/>
-      <c r="AF82" s="55"/>
-      <c r="AG82" s="55"/>
-      <c r="AH82" s="55"/>
-      <c r="AI82" s="55"/>
+      <c r="AB82" s="56"/>
+      <c r="AC82" s="57"/>
+      <c r="AD82" s="56"/>
+      <c r="AE82" s="56"/>
+      <c r="AF82" s="56"/>
+      <c r="AG82" s="56"/>
+      <c r="AH82" s="56"/>
+      <c r="AI82" s="56"/>
       <c r="AJ82" s="6"/>
     </row>
-    <row r="83" ht="15.6" customHeight="1">
+    <row r="83" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -6066,17 +5993,17 @@
       <c r="Y83" s="6"/>
       <c r="Z83" s="6"/>
       <c r="AA83" s="6"/>
-      <c r="AB83" s="53"/>
-      <c r="AC83" s="54"/>
-      <c r="AD83" s="53"/>
-      <c r="AE83" s="53"/>
-      <c r="AF83" s="53"/>
-      <c r="AG83" s="53"/>
-      <c r="AH83" s="53"/>
-      <c r="AI83" s="53"/>
+      <c r="AB83" s="54"/>
+      <c r="AC83" s="55"/>
+      <c r="AD83" s="54"/>
+      <c r="AE83" s="54"/>
+      <c r="AF83" s="54"/>
+      <c r="AG83" s="54"/>
+      <c r="AH83" s="54"/>
+      <c r="AI83" s="54"/>
       <c r="AJ83" s="6"/>
     </row>
-    <row r="84" ht="15.6" customHeight="1">
+    <row r="84" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -6104,17 +6031,17 @@
       <c r="Y84" s="6"/>
       <c r="Z84" s="6"/>
       <c r="AA84" s="6"/>
-      <c r="AB84" s="55"/>
-      <c r="AC84" s="56"/>
-      <c r="AD84" s="55"/>
-      <c r="AE84" s="55"/>
-      <c r="AF84" s="55"/>
-      <c r="AG84" s="55"/>
-      <c r="AH84" s="55"/>
-      <c r="AI84" s="55"/>
+      <c r="AB84" s="56"/>
+      <c r="AC84" s="57"/>
+      <c r="AD84" s="56"/>
+      <c r="AE84" s="56"/>
+      <c r="AF84" s="56"/>
+      <c r="AG84" s="56"/>
+      <c r="AH84" s="56"/>
+      <c r="AI84" s="56"/>
       <c r="AJ84" s="6"/>
     </row>
-    <row r="85" ht="15.6" customHeight="1">
+    <row r="85" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -6142,17 +6069,17 @@
       <c r="Y85" s="6"/>
       <c r="Z85" s="6"/>
       <c r="AA85" s="6"/>
-      <c r="AB85" s="53"/>
-      <c r="AC85" s="54"/>
-      <c r="AD85" s="53"/>
-      <c r="AE85" s="53"/>
-      <c r="AF85" s="53"/>
-      <c r="AG85" s="53"/>
-      <c r="AH85" s="53"/>
-      <c r="AI85" s="53"/>
+      <c r="AB85" s="54"/>
+      <c r="AC85" s="55"/>
+      <c r="AD85" s="54"/>
+      <c r="AE85" s="54"/>
+      <c r="AF85" s="54"/>
+      <c r="AG85" s="54"/>
+      <c r="AH85" s="54"/>
+      <c r="AI85" s="54"/>
       <c r="AJ85" s="6"/>
     </row>
-    <row r="86" ht="15.6" customHeight="1">
+    <row r="86" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -6180,17 +6107,17 @@
       <c r="Y86" s="6"/>
       <c r="Z86" s="6"/>
       <c r="AA86" s="6"/>
-      <c r="AB86" s="55"/>
-      <c r="AC86" s="56"/>
-      <c r="AD86" s="55"/>
-      <c r="AE86" s="55"/>
-      <c r="AF86" s="55"/>
-      <c r="AG86" s="55"/>
-      <c r="AH86" s="55"/>
-      <c r="AI86" s="55"/>
+      <c r="AB86" s="56"/>
+      <c r="AC86" s="57"/>
+      <c r="AD86" s="56"/>
+      <c r="AE86" s="56"/>
+      <c r="AF86" s="56"/>
+      <c r="AG86" s="56"/>
+      <c r="AH86" s="56"/>
+      <c r="AI86" s="56"/>
       <c r="AJ86" s="6"/>
     </row>
-    <row r="87" ht="15.6" customHeight="1">
+    <row r="87" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -6218,17 +6145,17 @@
       <c r="Y87" s="6"/>
       <c r="Z87" s="6"/>
       <c r="AA87" s="6"/>
-      <c r="AB87" s="53"/>
-      <c r="AC87" s="54"/>
-      <c r="AD87" s="53"/>
-      <c r="AE87" s="53"/>
-      <c r="AF87" s="53"/>
-      <c r="AG87" s="53"/>
-      <c r="AH87" s="53"/>
-      <c r="AI87" s="53"/>
+      <c r="AB87" s="54"/>
+      <c r="AC87" s="55"/>
+      <c r="AD87" s="54"/>
+      <c r="AE87" s="54"/>
+      <c r="AF87" s="54"/>
+      <c r="AG87" s="54"/>
+      <c r="AH87" s="54"/>
+      <c r="AI87" s="54"/>
       <c r="AJ87" s="6"/>
     </row>
-    <row r="88" ht="15.6" customHeight="1">
+    <row r="88" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -6256,17 +6183,17 @@
       <c r="Y88" s="6"/>
       <c r="Z88" s="6"/>
       <c r="AA88" s="6"/>
-      <c r="AB88" s="55"/>
-      <c r="AC88" s="56"/>
-      <c r="AD88" s="55"/>
-      <c r="AE88" s="55"/>
-      <c r="AF88" s="55"/>
-      <c r="AG88" s="55"/>
-      <c r="AH88" s="55"/>
-      <c r="AI88" s="55"/>
+      <c r="AB88" s="56"/>
+      <c r="AC88" s="57"/>
+      <c r="AD88" s="56"/>
+      <c r="AE88" s="56"/>
+      <c r="AF88" s="56"/>
+      <c r="AG88" s="56"/>
+      <c r="AH88" s="56"/>
+      <c r="AI88" s="56"/>
       <c r="AJ88" s="6"/>
     </row>
-    <row r="89" ht="15.6" customHeight="1">
+    <row r="89" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -6294,17 +6221,17 @@
       <c r="Y89" s="6"/>
       <c r="Z89" s="6"/>
       <c r="AA89" s="6"/>
-      <c r="AB89" s="53"/>
-      <c r="AC89" s="54"/>
-      <c r="AD89" s="53"/>
-      <c r="AE89" s="53"/>
-      <c r="AF89" s="53"/>
-      <c r="AG89" s="53"/>
-      <c r="AH89" s="53"/>
-      <c r="AI89" s="53"/>
+      <c r="AB89" s="54"/>
+      <c r="AC89" s="55"/>
+      <c r="AD89" s="54"/>
+      <c r="AE89" s="54"/>
+      <c r="AF89" s="54"/>
+      <c r="AG89" s="54"/>
+      <c r="AH89" s="54"/>
+      <c r="AI89" s="54"/>
       <c r="AJ89" s="6"/>
     </row>
-    <row r="90" ht="15.6" customHeight="1">
+    <row r="90" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -6332,17 +6259,17 @@
       <c r="Y90" s="6"/>
       <c r="Z90" s="6"/>
       <c r="AA90" s="6"/>
-      <c r="AB90" s="55"/>
-      <c r="AC90" s="56"/>
-      <c r="AD90" s="55"/>
-      <c r="AE90" s="55"/>
-      <c r="AF90" s="55"/>
-      <c r="AG90" s="55"/>
-      <c r="AH90" s="55"/>
-      <c r="AI90" s="55"/>
+      <c r="AB90" s="56"/>
+      <c r="AC90" s="57"/>
+      <c r="AD90" s="56"/>
+      <c r="AE90" s="56"/>
+      <c r="AF90" s="56"/>
+      <c r="AG90" s="56"/>
+      <c r="AH90" s="56"/>
+      <c r="AI90" s="56"/>
       <c r="AJ90" s="6"/>
     </row>
-    <row r="91" ht="15.6" customHeight="1">
+    <row r="91" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -6370,17 +6297,17 @@
       <c r="Y91" s="6"/>
       <c r="Z91" s="6"/>
       <c r="AA91" s="6"/>
-      <c r="AB91" s="53"/>
-      <c r="AC91" s="54"/>
-      <c r="AD91" s="53"/>
-      <c r="AE91" s="53"/>
-      <c r="AF91" s="53"/>
-      <c r="AG91" s="53"/>
-      <c r="AH91" s="53"/>
-      <c r="AI91" s="53"/>
+      <c r="AB91" s="54"/>
+      <c r="AC91" s="55"/>
+      <c r="AD91" s="54"/>
+      <c r="AE91" s="54"/>
+      <c r="AF91" s="54"/>
+      <c r="AG91" s="54"/>
+      <c r="AH91" s="54"/>
+      <c r="AI91" s="54"/>
       <c r="AJ91" s="6"/>
     </row>
-    <row r="92" ht="15.6" customHeight="1">
+    <row r="92" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -6408,17 +6335,17 @@
       <c r="Y92" s="6"/>
       <c r="Z92" s="6"/>
       <c r="AA92" s="6"/>
-      <c r="AB92" s="55"/>
-      <c r="AC92" s="56"/>
-      <c r="AD92" s="55"/>
-      <c r="AE92" s="55"/>
-      <c r="AF92" s="55"/>
-      <c r="AG92" s="55"/>
-      <c r="AH92" s="55"/>
-      <c r="AI92" s="55"/>
+      <c r="AB92" s="56"/>
+      <c r="AC92" s="57"/>
+      <c r="AD92" s="56"/>
+      <c r="AE92" s="56"/>
+      <c r="AF92" s="56"/>
+      <c r="AG92" s="56"/>
+      <c r="AH92" s="56"/>
+      <c r="AI92" s="56"/>
       <c r="AJ92" s="6"/>
     </row>
-    <row r="93" ht="15.6" customHeight="1">
+    <row r="93" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -6446,17 +6373,17 @@
       <c r="Y93" s="6"/>
       <c r="Z93" s="6"/>
       <c r="AA93" s="6"/>
-      <c r="AB93" s="53"/>
-      <c r="AC93" s="54"/>
-      <c r="AD93" s="53"/>
-      <c r="AE93" s="53"/>
-      <c r="AF93" s="53"/>
-      <c r="AG93" s="53"/>
-      <c r="AH93" s="53"/>
-      <c r="AI93" s="53"/>
+      <c r="AB93" s="54"/>
+      <c r="AC93" s="55"/>
+      <c r="AD93" s="54"/>
+      <c r="AE93" s="54"/>
+      <c r="AF93" s="54"/>
+      <c r="AG93" s="54"/>
+      <c r="AH93" s="54"/>
+      <c r="AI93" s="54"/>
       <c r="AJ93" s="6"/>
     </row>
-    <row r="94" ht="15.6" customHeight="1">
+    <row r="94" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -6484,17 +6411,17 @@
       <c r="Y94" s="6"/>
       <c r="Z94" s="6"/>
       <c r="AA94" s="6"/>
-      <c r="AB94" s="55"/>
-      <c r="AC94" s="56"/>
-      <c r="AD94" s="55"/>
-      <c r="AE94" s="55"/>
-      <c r="AF94" s="55"/>
-      <c r="AG94" s="55"/>
-      <c r="AH94" s="55"/>
-      <c r="AI94" s="55"/>
+      <c r="AB94" s="56"/>
+      <c r="AC94" s="57"/>
+      <c r="AD94" s="56"/>
+      <c r="AE94" s="56"/>
+      <c r="AF94" s="56"/>
+      <c r="AG94" s="56"/>
+      <c r="AH94" s="56"/>
+      <c r="AI94" s="56"/>
       <c r="AJ94" s="6"/>
     </row>
-    <row r="95" ht="15.6" customHeight="1">
+    <row r="95" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -6522,17 +6449,17 @@
       <c r="Y95" s="6"/>
       <c r="Z95" s="6"/>
       <c r="AA95" s="6"/>
-      <c r="AB95" s="53"/>
-      <c r="AC95" s="54"/>
-      <c r="AD95" s="53"/>
-      <c r="AE95" s="53"/>
-      <c r="AF95" s="53"/>
-      <c r="AG95" s="53"/>
-      <c r="AH95" s="53"/>
-      <c r="AI95" s="53"/>
+      <c r="AB95" s="54"/>
+      <c r="AC95" s="55"/>
+      <c r="AD95" s="54"/>
+      <c r="AE95" s="54"/>
+      <c r="AF95" s="54"/>
+      <c r="AG95" s="54"/>
+      <c r="AH95" s="54"/>
+      <c r="AI95" s="54"/>
       <c r="AJ95" s="6"/>
     </row>
-    <row r="96" ht="15.6" customHeight="1">
+    <row r="96" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -6560,17 +6487,17 @@
       <c r="Y96" s="6"/>
       <c r="Z96" s="6"/>
       <c r="AA96" s="6"/>
-      <c r="AB96" s="55"/>
-      <c r="AC96" s="56"/>
-      <c r="AD96" s="55"/>
-      <c r="AE96" s="55"/>
-      <c r="AF96" s="55"/>
-      <c r="AG96" s="55"/>
-      <c r="AH96" s="55"/>
-      <c r="AI96" s="55"/>
+      <c r="AB96" s="56"/>
+      <c r="AC96" s="57"/>
+      <c r="AD96" s="56"/>
+      <c r="AE96" s="56"/>
+      <c r="AF96" s="56"/>
+      <c r="AG96" s="56"/>
+      <c r="AH96" s="56"/>
+      <c r="AI96" s="56"/>
       <c r="AJ96" s="6"/>
     </row>
-    <row r="97" ht="15.6" customHeight="1">
+    <row r="97" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -6598,17 +6525,17 @@
       <c r="Y97" s="6"/>
       <c r="Z97" s="6"/>
       <c r="AA97" s="6"/>
-      <c r="AB97" s="53"/>
-      <c r="AC97" s="54"/>
-      <c r="AD97" s="53"/>
-      <c r="AE97" s="53"/>
-      <c r="AF97" s="53"/>
-      <c r="AG97" s="53"/>
-      <c r="AH97" s="53"/>
-      <c r="AI97" s="53"/>
+      <c r="AB97" s="54"/>
+      <c r="AC97" s="55"/>
+      <c r="AD97" s="54"/>
+      <c r="AE97" s="54"/>
+      <c r="AF97" s="54"/>
+      <c r="AG97" s="54"/>
+      <c r="AH97" s="54"/>
+      <c r="AI97" s="54"/>
       <c r="AJ97" s="6"/>
     </row>
-    <row r="98" ht="15.6" customHeight="1">
+    <row r="98" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -6636,17 +6563,17 @@
       <c r="Y98" s="6"/>
       <c r="Z98" s="6"/>
       <c r="AA98" s="6"/>
-      <c r="AB98" s="55"/>
-      <c r="AC98" s="56"/>
-      <c r="AD98" s="55"/>
-      <c r="AE98" s="55"/>
-      <c r="AF98" s="55"/>
-      <c r="AG98" s="55"/>
-      <c r="AH98" s="55"/>
-      <c r="AI98" s="55"/>
+      <c r="AB98" s="56"/>
+      <c r="AC98" s="57"/>
+      <c r="AD98" s="56"/>
+      <c r="AE98" s="56"/>
+      <c r="AF98" s="56"/>
+      <c r="AG98" s="56"/>
+      <c r="AH98" s="56"/>
+      <c r="AI98" s="56"/>
       <c r="AJ98" s="6"/>
     </row>
-    <row r="99" ht="15.6" customHeight="1">
+    <row r="99" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -6674,17 +6601,17 @@
       <c r="Y99" s="6"/>
       <c r="Z99" s="6"/>
       <c r="AA99" s="6"/>
-      <c r="AB99" s="53"/>
-      <c r="AC99" s="54"/>
-      <c r="AD99" s="53"/>
-      <c r="AE99" s="53"/>
-      <c r="AF99" s="53"/>
-      <c r="AG99" s="53"/>
-      <c r="AH99" s="53"/>
-      <c r="AI99" s="53"/>
+      <c r="AB99" s="54"/>
+      <c r="AC99" s="55"/>
+      <c r="AD99" s="54"/>
+      <c r="AE99" s="54"/>
+      <c r="AF99" s="54"/>
+      <c r="AG99" s="54"/>
+      <c r="AH99" s="54"/>
+      <c r="AI99" s="54"/>
       <c r="AJ99" s="6"/>
     </row>
-    <row r="100" ht="15.6" customHeight="1">
+    <row r="100" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -6712,17 +6639,17 @@
       <c r="Y100" s="6"/>
       <c r="Z100" s="6"/>
       <c r="AA100" s="6"/>
-      <c r="AB100" s="55"/>
-      <c r="AC100" s="56"/>
-      <c r="AD100" s="55"/>
-      <c r="AE100" s="55"/>
-      <c r="AF100" s="55"/>
-      <c r="AG100" s="55"/>
-      <c r="AH100" s="55"/>
-      <c r="AI100" s="55"/>
+      <c r="AB100" s="56"/>
+      <c r="AC100" s="57"/>
+      <c r="AD100" s="56"/>
+      <c r="AE100" s="56"/>
+      <c r="AF100" s="56"/>
+      <c r="AG100" s="56"/>
+      <c r="AH100" s="56"/>
+      <c r="AI100" s="56"/>
       <c r="AJ100" s="6"/>
     </row>
-    <row r="101" ht="15.6" customHeight="1">
+    <row r="101" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -6750,98 +6677,98 @@
       <c r="Y101" s="6"/>
       <c r="Z101" s="6"/>
       <c r="AA101" s="6"/>
-      <c r="AB101" s="53"/>
-      <c r="AC101" s="54"/>
-      <c r="AD101" s="53"/>
-      <c r="AE101" s="53"/>
-      <c r="AF101" s="53"/>
-      <c r="AG101" s="53"/>
-      <c r="AH101" s="53"/>
-      <c r="AI101" s="53"/>
+      <c r="AB101" s="54"/>
+      <c r="AC101" s="55"/>
+      <c r="AD101" s="54"/>
+      <c r="AE101" s="54"/>
+      <c r="AF101" s="54"/>
+      <c r="AG101" s="54"/>
+      <c r="AH101" s="54"/>
+      <c r="AI101" s="54"/>
       <c r="AJ101" s="6"/>
     </row>
-    <row r="102" ht="15.6" customHeight="1">
-      <c r="A102" s="57"/>
-      <c r="B102" s="57"/>
-      <c r="C102" s="57"/>
-      <c r="D102" s="57"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="57"/>
-      <c r="G102" s="57"/>
-      <c r="H102" s="57"/>
-      <c r="I102" s="57"/>
-      <c r="J102" s="57"/>
-      <c r="K102" s="57"/>
-      <c r="L102" s="57"/>
-      <c r="M102" s="57"/>
-      <c r="N102" s="57"/>
-      <c r="O102" s="57"/>
-      <c r="P102" s="57"/>
-      <c r="Q102" s="57"/>
-      <c r="R102" s="57"/>
-      <c r="S102" s="57"/>
-      <c r="T102" s="57"/>
-      <c r="U102" s="57"/>
-      <c r="V102" s="57"/>
-      <c r="W102" s="57"/>
-      <c r="X102" s="57"/>
-      <c r="Y102" s="57"/>
-      <c r="Z102" s="57"/>
-      <c r="AA102" s="57"/>
-      <c r="AB102" s="55"/>
-      <c r="AC102" s="56"/>
-      <c r="AD102" s="55"/>
-      <c r="AE102" s="55"/>
-      <c r="AF102" s="55"/>
-      <c r="AG102" s="55"/>
-      <c r="AH102" s="55"/>
-      <c r="AI102" s="55"/>
+    <row r="102" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A102" s="58"/>
+      <c r="B102" s="58"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="58"/>
+      <c r="F102" s="58"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="58"/>
+      <c r="I102" s="58"/>
+      <c r="J102" s="58"/>
+      <c r="K102" s="58"/>
+      <c r="L102" s="58"/>
+      <c r="M102" s="58"/>
+      <c r="N102" s="58"/>
+      <c r="O102" s="58"/>
+      <c r="P102" s="58"/>
+      <c r="Q102" s="58"/>
+      <c r="R102" s="58"/>
+      <c r="S102" s="58"/>
+      <c r="T102" s="58"/>
+      <c r="U102" s="58"/>
+      <c r="V102" s="58"/>
+      <c r="W102" s="58"/>
+      <c r="X102" s="58"/>
+      <c r="Y102" s="58"/>
+      <c r="Z102" s="58"/>
+      <c r="AA102" s="58"/>
+      <c r="AB102" s="56"/>
+      <c r="AC102" s="57"/>
+      <c r="AD102" s="56"/>
+      <c r="AE102" s="56"/>
+      <c r="AF102" s="56"/>
+      <c r="AG102" s="56"/>
+      <c r="AH102" s="56"/>
+      <c r="AI102" s="56"/>
       <c r="AJ102" s="6"/>
     </row>
-    <row r="103" ht="15.6" customHeight="1">
-      <c r="A103" s="58"/>
-      <c r="B103" s="59"/>
-      <c r="C103" s="59"/>
-      <c r="D103" s="59"/>
-      <c r="E103" s="58"/>
-      <c r="F103" s="60"/>
-      <c r="G103" s="60"/>
-      <c r="H103" s="59"/>
-      <c r="I103" s="59"/>
-      <c r="J103" s="59"/>
-      <c r="K103" s="59"/>
-      <c r="L103" s="59"/>
-      <c r="M103" s="59"/>
-      <c r="N103" s="59"/>
-      <c r="O103" s="61"/>
-      <c r="P103" s="60"/>
-      <c r="Q103" s="59"/>
-      <c r="R103" s="59"/>
-      <c r="S103" s="59"/>
-      <c r="T103" s="62"/>
-      <c r="U103" s="59"/>
-      <c r="V103" s="59"/>
-      <c r="W103" s="59"/>
-      <c r="X103" s="59"/>
-      <c r="Y103" s="59"/>
-      <c r="Z103" s="63"/>
-      <c r="AA103" s="63"/>
-      <c r="AB103" s="59"/>
-      <c r="AC103" s="60"/>
-      <c r="AD103" s="59"/>
-      <c r="AE103" s="59"/>
-      <c r="AF103" s="59"/>
-      <c r="AG103" s="59"/>
-      <c r="AH103" s="59"/>
-      <c r="AI103" s="59"/>
+    <row r="103" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A103" s="59"/>
+      <c r="B103" s="60"/>
+      <c r="C103" s="60"/>
+      <c r="D103" s="60"/>
+      <c r="E103" s="59"/>
+      <c r="F103" s="61"/>
+      <c r="G103" s="61"/>
+      <c r="H103" s="60"/>
+      <c r="I103" s="60"/>
+      <c r="J103" s="60"/>
+      <c r="K103" s="60"/>
+      <c r="L103" s="60"/>
+      <c r="M103" s="60"/>
+      <c r="N103" s="60"/>
+      <c r="O103" s="62"/>
+      <c r="P103" s="61"/>
+      <c r="Q103" s="60"/>
+      <c r="R103" s="60"/>
+      <c r="S103" s="60"/>
+      <c r="T103" s="63"/>
+      <c r="U103" s="60"/>
+      <c r="V103" s="60"/>
+      <c r="W103" s="60"/>
+      <c r="X103" s="60"/>
+      <c r="Y103" s="60"/>
+      <c r="Z103" s="64"/>
+      <c r="AA103" s="64"/>
+      <c r="AB103" s="60"/>
+      <c r="AC103" s="61"/>
+      <c r="AD103" s="60"/>
+      <c r="AE103" s="60"/>
+      <c r="AF103" s="60"/>
+      <c r="AG103" s="60"/>
+      <c r="AH103" s="60"/>
+      <c r="AI103" s="60"/>
       <c r="AJ103" s="33"/>
     </row>
-    <row r="104" ht="15.6" customHeight="1">
-      <c r="A104" s="64"/>
+    <row r="104" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A104" s="65"/>
       <c r="B104" s="45"/>
       <c r="C104" s="45"/>
       <c r="D104" s="45"/>
-      <c r="E104" s="64"/>
+      <c r="E104" s="65"/>
       <c r="F104" s="44"/>
       <c r="G104" s="44"/>
       <c r="H104" s="45"/>
@@ -6851,12 +6778,12 @@
       <c r="L104" s="45"/>
       <c r="M104" s="45"/>
       <c r="N104" s="45"/>
-      <c r="O104" s="65"/>
+      <c r="O104" s="66"/>
       <c r="P104" s="44"/>
       <c r="Q104" s="45"/>
       <c r="R104" s="45"/>
       <c r="S104" s="45"/>
-      <c r="T104" s="66"/>
+      <c r="T104" s="67"/>
       <c r="U104" s="45"/>
       <c r="V104" s="45"/>
       <c r="W104" s="45"/>
@@ -6874,50 +6801,50 @@
       <c r="AI104" s="45"/>
       <c r="AJ104" s="33"/>
     </row>
-    <row r="105" ht="15.6" customHeight="1">
-      <c r="A105" s="58"/>
-      <c r="B105" s="59"/>
-      <c r="C105" s="59"/>
-      <c r="D105" s="59"/>
-      <c r="E105" s="58"/>
-      <c r="F105" s="60"/>
-      <c r="G105" s="60"/>
-      <c r="H105" s="59"/>
-      <c r="I105" s="59"/>
-      <c r="J105" s="59"/>
-      <c r="K105" s="59"/>
-      <c r="L105" s="59"/>
-      <c r="M105" s="59"/>
-      <c r="N105" s="59"/>
-      <c r="O105" s="61"/>
-      <c r="P105" s="60"/>
-      <c r="Q105" s="59"/>
-      <c r="R105" s="59"/>
-      <c r="S105" s="59"/>
-      <c r="T105" s="62"/>
-      <c r="U105" s="59"/>
-      <c r="V105" s="59"/>
-      <c r="W105" s="59"/>
-      <c r="X105" s="59"/>
-      <c r="Y105" s="59"/>
-      <c r="Z105" s="63"/>
-      <c r="AA105" s="63"/>
-      <c r="AB105" s="59"/>
-      <c r="AC105" s="60"/>
-      <c r="AD105" s="59"/>
-      <c r="AE105" s="59"/>
-      <c r="AF105" s="59"/>
-      <c r="AG105" s="59"/>
-      <c r="AH105" s="59"/>
-      <c r="AI105" s="59"/>
+    <row r="105" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A105" s="59"/>
+      <c r="B105" s="60"/>
+      <c r="C105" s="60"/>
+      <c r="D105" s="60"/>
+      <c r="E105" s="59"/>
+      <c r="F105" s="61"/>
+      <c r="G105" s="61"/>
+      <c r="H105" s="60"/>
+      <c r="I105" s="60"/>
+      <c r="J105" s="60"/>
+      <c r="K105" s="60"/>
+      <c r="L105" s="60"/>
+      <c r="M105" s="60"/>
+      <c r="N105" s="60"/>
+      <c r="O105" s="62"/>
+      <c r="P105" s="61"/>
+      <c r="Q105" s="60"/>
+      <c r="R105" s="60"/>
+      <c r="S105" s="60"/>
+      <c r="T105" s="63"/>
+      <c r="U105" s="60"/>
+      <c r="V105" s="60"/>
+      <c r="W105" s="60"/>
+      <c r="X105" s="60"/>
+      <c r="Y105" s="60"/>
+      <c r="Z105" s="64"/>
+      <c r="AA105" s="64"/>
+      <c r="AB105" s="60"/>
+      <c r="AC105" s="61"/>
+      <c r="AD105" s="60"/>
+      <c r="AE105" s="60"/>
+      <c r="AF105" s="60"/>
+      <c r="AG105" s="60"/>
+      <c r="AH105" s="60"/>
+      <c r="AI105" s="60"/>
       <c r="AJ105" s="33"/>
     </row>
-    <row r="106" ht="15.6" customHeight="1">
-      <c r="A106" s="64"/>
+    <row r="106" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A106" s="65"/>
       <c r="B106" s="45"/>
       <c r="C106" s="45"/>
       <c r="D106" s="45"/>
-      <c r="E106" s="64"/>
+      <c r="E106" s="65"/>
       <c r="F106" s="44"/>
       <c r="G106" s="44"/>
       <c r="H106" s="45"/>
@@ -6927,12 +6854,12 @@
       <c r="L106" s="45"/>
       <c r="M106" s="45"/>
       <c r="N106" s="45"/>
-      <c r="O106" s="65"/>
+      <c r="O106" s="66"/>
       <c r="P106" s="44"/>
       <c r="Q106" s="45"/>
       <c r="R106" s="45"/>
       <c r="S106" s="45"/>
-      <c r="T106" s="66"/>
+      <c r="T106" s="67"/>
       <c r="U106" s="45"/>
       <c r="V106" s="45"/>
       <c r="W106" s="45"/>
@@ -6950,50 +6877,50 @@
       <c r="AI106" s="45"/>
       <c r="AJ106" s="33"/>
     </row>
-    <row r="107" ht="15.6" customHeight="1">
-      <c r="A107" s="58"/>
-      <c r="B107" s="59"/>
-      <c r="C107" s="59"/>
-      <c r="D107" s="59"/>
-      <c r="E107" s="58"/>
-      <c r="F107" s="60"/>
-      <c r="G107" s="60"/>
-      <c r="H107" s="59"/>
-      <c r="I107" s="59"/>
-      <c r="J107" s="59"/>
-      <c r="K107" s="59"/>
-      <c r="L107" s="59"/>
-      <c r="M107" s="59"/>
-      <c r="N107" s="59"/>
-      <c r="O107" s="61"/>
-      <c r="P107" s="60"/>
-      <c r="Q107" s="59"/>
-      <c r="R107" s="59"/>
-      <c r="S107" s="59"/>
-      <c r="T107" s="62"/>
-      <c r="U107" s="59"/>
-      <c r="V107" s="59"/>
-      <c r="W107" s="59"/>
-      <c r="X107" s="59"/>
-      <c r="Y107" s="59"/>
-      <c r="Z107" s="63"/>
-      <c r="AA107" s="63"/>
-      <c r="AB107" s="59"/>
-      <c r="AC107" s="60"/>
-      <c r="AD107" s="59"/>
-      <c r="AE107" s="59"/>
-      <c r="AF107" s="59"/>
-      <c r="AG107" s="59"/>
-      <c r="AH107" s="59"/>
-      <c r="AI107" s="59"/>
+    <row r="107" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A107" s="59"/>
+      <c r="B107" s="60"/>
+      <c r="C107" s="60"/>
+      <c r="D107" s="60"/>
+      <c r="E107" s="59"/>
+      <c r="F107" s="61"/>
+      <c r="G107" s="61"/>
+      <c r="H107" s="60"/>
+      <c r="I107" s="60"/>
+      <c r="J107" s="60"/>
+      <c r="K107" s="60"/>
+      <c r="L107" s="60"/>
+      <c r="M107" s="60"/>
+      <c r="N107" s="60"/>
+      <c r="O107" s="62"/>
+      <c r="P107" s="61"/>
+      <c r="Q107" s="60"/>
+      <c r="R107" s="60"/>
+      <c r="S107" s="60"/>
+      <c r="T107" s="63"/>
+      <c r="U107" s="60"/>
+      <c r="V107" s="60"/>
+      <c r="W107" s="60"/>
+      <c r="X107" s="60"/>
+      <c r="Y107" s="60"/>
+      <c r="Z107" s="64"/>
+      <c r="AA107" s="64"/>
+      <c r="AB107" s="60"/>
+      <c r="AC107" s="61"/>
+      <c r="AD107" s="60"/>
+      <c r="AE107" s="60"/>
+      <c r="AF107" s="60"/>
+      <c r="AG107" s="60"/>
+      <c r="AH107" s="60"/>
+      <c r="AI107" s="60"/>
       <c r="AJ107" s="33"/>
     </row>
-    <row r="108" ht="15.6" customHeight="1">
-      <c r="A108" s="64"/>
+    <row r="108" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A108" s="65"/>
       <c r="B108" s="45"/>
       <c r="C108" s="45"/>
       <c r="D108" s="45"/>
-      <c r="E108" s="64"/>
+      <c r="E108" s="65"/>
       <c r="F108" s="44"/>
       <c r="G108" s="44"/>
       <c r="H108" s="45"/>
@@ -7003,12 +6930,12 @@
       <c r="L108" s="45"/>
       <c r="M108" s="45"/>
       <c r="N108" s="45"/>
-      <c r="O108" s="65"/>
+      <c r="O108" s="66"/>
       <c r="P108" s="44"/>
       <c r="Q108" s="45"/>
       <c r="R108" s="45"/>
       <c r="S108" s="45"/>
-      <c r="T108" s="66"/>
+      <c r="T108" s="67"/>
       <c r="U108" s="45"/>
       <c r="V108" s="45"/>
       <c r="W108" s="45"/>
@@ -7026,50 +6953,50 @@
       <c r="AI108" s="45"/>
       <c r="AJ108" s="33"/>
     </row>
-    <row r="109" ht="15.6" customHeight="1">
-      <c r="A109" s="58"/>
-      <c r="B109" s="59"/>
-      <c r="C109" s="59"/>
-      <c r="D109" s="59"/>
-      <c r="E109" s="58"/>
-      <c r="F109" s="60"/>
-      <c r="G109" s="60"/>
-      <c r="H109" s="59"/>
-      <c r="I109" s="59"/>
-      <c r="J109" s="59"/>
-      <c r="K109" s="59"/>
-      <c r="L109" s="59"/>
-      <c r="M109" s="59"/>
-      <c r="N109" s="59"/>
-      <c r="O109" s="61"/>
-      <c r="P109" s="60"/>
-      <c r="Q109" s="59"/>
-      <c r="R109" s="59"/>
-      <c r="S109" s="59"/>
-      <c r="T109" s="62"/>
-      <c r="U109" s="59"/>
-      <c r="V109" s="59"/>
-      <c r="W109" s="59"/>
-      <c r="X109" s="59"/>
-      <c r="Y109" s="59"/>
-      <c r="Z109" s="63"/>
-      <c r="AA109" s="63"/>
-      <c r="AB109" s="59"/>
-      <c r="AC109" s="60"/>
-      <c r="AD109" s="59"/>
-      <c r="AE109" s="59"/>
-      <c r="AF109" s="59"/>
-      <c r="AG109" s="59"/>
-      <c r="AH109" s="59"/>
-      <c r="AI109" s="59"/>
+    <row r="109" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A109" s="59"/>
+      <c r="B109" s="60"/>
+      <c r="C109" s="60"/>
+      <c r="D109" s="60"/>
+      <c r="E109" s="59"/>
+      <c r="F109" s="61"/>
+      <c r="G109" s="61"/>
+      <c r="H109" s="60"/>
+      <c r="I109" s="60"/>
+      <c r="J109" s="60"/>
+      <c r="K109" s="60"/>
+      <c r="L109" s="60"/>
+      <c r="M109" s="60"/>
+      <c r="N109" s="60"/>
+      <c r="O109" s="62"/>
+      <c r="P109" s="61"/>
+      <c r="Q109" s="60"/>
+      <c r="R109" s="60"/>
+      <c r="S109" s="60"/>
+      <c r="T109" s="63"/>
+      <c r="U109" s="60"/>
+      <c r="V109" s="60"/>
+      <c r="W109" s="60"/>
+      <c r="X109" s="60"/>
+      <c r="Y109" s="60"/>
+      <c r="Z109" s="64"/>
+      <c r="AA109" s="64"/>
+      <c r="AB109" s="60"/>
+      <c r="AC109" s="61"/>
+      <c r="AD109" s="60"/>
+      <c r="AE109" s="60"/>
+      <c r="AF109" s="60"/>
+      <c r="AG109" s="60"/>
+      <c r="AH109" s="60"/>
+      <c r="AI109" s="60"/>
       <c r="AJ109" s="33"/>
     </row>
-    <row r="110" ht="15.6" customHeight="1">
-      <c r="A110" s="64"/>
+    <row r="110" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A110" s="65"/>
       <c r="B110" s="45"/>
       <c r="C110" s="45"/>
       <c r="D110" s="45"/>
-      <c r="E110" s="64"/>
+      <c r="E110" s="65"/>
       <c r="F110" s="44"/>
       <c r="G110" s="44"/>
       <c r="H110" s="45"/>
@@ -7079,12 +7006,12 @@
       <c r="L110" s="45"/>
       <c r="M110" s="45"/>
       <c r="N110" s="45"/>
-      <c r="O110" s="65"/>
+      <c r="O110" s="66"/>
       <c r="P110" s="44"/>
       <c r="Q110" s="45"/>
       <c r="R110" s="45"/>
       <c r="S110" s="45"/>
-      <c r="T110" s="66"/>
+      <c r="T110" s="67"/>
       <c r="U110" s="45"/>
       <c r="V110" s="45"/>
       <c r="W110" s="45"/>
@@ -7102,50 +7029,50 @@
       <c r="AI110" s="45"/>
       <c r="AJ110" s="33"/>
     </row>
-    <row r="111" ht="15.6" customHeight="1">
-      <c r="A111" s="58"/>
-      <c r="B111" s="59"/>
-      <c r="C111" s="59"/>
-      <c r="D111" s="59"/>
-      <c r="E111" s="58"/>
-      <c r="F111" s="60"/>
-      <c r="G111" s="60"/>
-      <c r="H111" s="59"/>
-      <c r="I111" s="59"/>
-      <c r="J111" s="59"/>
-      <c r="K111" s="59"/>
-      <c r="L111" s="59"/>
-      <c r="M111" s="59"/>
-      <c r="N111" s="59"/>
-      <c r="O111" s="61"/>
-      <c r="P111" s="60"/>
-      <c r="Q111" s="59"/>
-      <c r="R111" s="59"/>
-      <c r="S111" s="59"/>
-      <c r="T111" s="62"/>
-      <c r="U111" s="59"/>
-      <c r="V111" s="59"/>
-      <c r="W111" s="59"/>
-      <c r="X111" s="59"/>
-      <c r="Y111" s="59"/>
-      <c r="Z111" s="63"/>
-      <c r="AA111" s="63"/>
-      <c r="AB111" s="59"/>
-      <c r="AC111" s="60"/>
-      <c r="AD111" s="59"/>
-      <c r="AE111" s="59"/>
-      <c r="AF111" s="59"/>
-      <c r="AG111" s="59"/>
-      <c r="AH111" s="59"/>
-      <c r="AI111" s="59"/>
+    <row r="111" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A111" s="59"/>
+      <c r="B111" s="60"/>
+      <c r="C111" s="60"/>
+      <c r="D111" s="60"/>
+      <c r="E111" s="59"/>
+      <c r="F111" s="61"/>
+      <c r="G111" s="61"/>
+      <c r="H111" s="60"/>
+      <c r="I111" s="60"/>
+      <c r="J111" s="60"/>
+      <c r="K111" s="60"/>
+      <c r="L111" s="60"/>
+      <c r="M111" s="60"/>
+      <c r="N111" s="60"/>
+      <c r="O111" s="62"/>
+      <c r="P111" s="61"/>
+      <c r="Q111" s="60"/>
+      <c r="R111" s="60"/>
+      <c r="S111" s="60"/>
+      <c r="T111" s="63"/>
+      <c r="U111" s="60"/>
+      <c r="V111" s="60"/>
+      <c r="W111" s="60"/>
+      <c r="X111" s="60"/>
+      <c r="Y111" s="60"/>
+      <c r="Z111" s="64"/>
+      <c r="AA111" s="64"/>
+      <c r="AB111" s="60"/>
+      <c r="AC111" s="61"/>
+      <c r="AD111" s="60"/>
+      <c r="AE111" s="60"/>
+      <c r="AF111" s="60"/>
+      <c r="AG111" s="60"/>
+      <c r="AH111" s="60"/>
+      <c r="AI111" s="60"/>
       <c r="AJ111" s="33"/>
     </row>
-    <row r="112" ht="15.6" customHeight="1">
-      <c r="A112" s="64"/>
+    <row r="112" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A112" s="65"/>
       <c r="B112" s="45"/>
       <c r="C112" s="45"/>
       <c r="D112" s="45"/>
-      <c r="E112" s="64"/>
+      <c r="E112" s="65"/>
       <c r="F112" s="44"/>
       <c r="G112" s="44"/>
       <c r="H112" s="45"/>
@@ -7155,12 +7082,12 @@
       <c r="L112" s="45"/>
       <c r="M112" s="45"/>
       <c r="N112" s="45"/>
-      <c r="O112" s="65"/>
+      <c r="O112" s="66"/>
       <c r="P112" s="44"/>
       <c r="Q112" s="45"/>
       <c r="R112" s="45"/>
       <c r="S112" s="45"/>
-      <c r="T112" s="66"/>
+      <c r="T112" s="67"/>
       <c r="U112" s="45"/>
       <c r="V112" s="45"/>
       <c r="W112" s="45"/>
@@ -7178,50 +7105,50 @@
       <c r="AI112" s="45"/>
       <c r="AJ112" s="33"/>
     </row>
-    <row r="113" ht="15.6" customHeight="1">
-      <c r="A113" s="58"/>
-      <c r="B113" s="59"/>
-      <c r="C113" s="59"/>
-      <c r="D113" s="59"/>
-      <c r="E113" s="58"/>
-      <c r="F113" s="60"/>
-      <c r="G113" s="60"/>
-      <c r="H113" s="59"/>
-      <c r="I113" s="59"/>
-      <c r="J113" s="59"/>
-      <c r="K113" s="59"/>
-      <c r="L113" s="59"/>
-      <c r="M113" s="59"/>
-      <c r="N113" s="59"/>
-      <c r="O113" s="61"/>
-      <c r="P113" s="60"/>
-      <c r="Q113" s="59"/>
-      <c r="R113" s="59"/>
-      <c r="S113" s="59"/>
-      <c r="T113" s="62"/>
-      <c r="U113" s="59"/>
-      <c r="V113" s="59"/>
-      <c r="W113" s="59"/>
-      <c r="X113" s="59"/>
-      <c r="Y113" s="59"/>
-      <c r="Z113" s="63"/>
-      <c r="AA113" s="63"/>
-      <c r="AB113" s="59"/>
-      <c r="AC113" s="60"/>
-      <c r="AD113" s="59"/>
-      <c r="AE113" s="59"/>
-      <c r="AF113" s="59"/>
-      <c r="AG113" s="59"/>
-      <c r="AH113" s="59"/>
-      <c r="AI113" s="59"/>
+    <row r="113" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A113" s="59"/>
+      <c r="B113" s="60"/>
+      <c r="C113" s="60"/>
+      <c r="D113" s="60"/>
+      <c r="E113" s="59"/>
+      <c r="F113" s="61"/>
+      <c r="G113" s="61"/>
+      <c r="H113" s="60"/>
+      <c r="I113" s="60"/>
+      <c r="J113" s="60"/>
+      <c r="K113" s="60"/>
+      <c r="L113" s="60"/>
+      <c r="M113" s="60"/>
+      <c r="N113" s="60"/>
+      <c r="O113" s="62"/>
+      <c r="P113" s="61"/>
+      <c r="Q113" s="60"/>
+      <c r="R113" s="60"/>
+      <c r="S113" s="60"/>
+      <c r="T113" s="63"/>
+      <c r="U113" s="60"/>
+      <c r="V113" s="60"/>
+      <c r="W113" s="60"/>
+      <c r="X113" s="60"/>
+      <c r="Y113" s="60"/>
+      <c r="Z113" s="64"/>
+      <c r="AA113" s="64"/>
+      <c r="AB113" s="60"/>
+      <c r="AC113" s="61"/>
+      <c r="AD113" s="60"/>
+      <c r="AE113" s="60"/>
+      <c r="AF113" s="60"/>
+      <c r="AG113" s="60"/>
+      <c r="AH113" s="60"/>
+      <c r="AI113" s="60"/>
       <c r="AJ113" s="33"/>
     </row>
-    <row r="114" ht="15.6" customHeight="1">
-      <c r="A114" s="64"/>
+    <row r="114" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A114" s="65"/>
       <c r="B114" s="45"/>
       <c r="C114" s="45"/>
       <c r="D114" s="45"/>
-      <c r="E114" s="64"/>
+      <c r="E114" s="65"/>
       <c r="F114" s="44"/>
       <c r="G114" s="44"/>
       <c r="H114" s="45"/>
@@ -7231,12 +7158,12 @@
       <c r="L114" s="45"/>
       <c r="M114" s="45"/>
       <c r="N114" s="45"/>
-      <c r="O114" s="65"/>
+      <c r="O114" s="66"/>
       <c r="P114" s="44"/>
       <c r="Q114" s="45"/>
       <c r="R114" s="45"/>
       <c r="S114" s="45"/>
-      <c r="T114" s="66"/>
+      <c r="T114" s="67"/>
       <c r="U114" s="45"/>
       <c r="V114" s="45"/>
       <c r="W114" s="45"/>
@@ -7254,50 +7181,50 @@
       <c r="AI114" s="45"/>
       <c r="AJ114" s="33"/>
     </row>
-    <row r="115" ht="15.6" customHeight="1">
-      <c r="A115" s="58"/>
-      <c r="B115" s="59"/>
-      <c r="C115" s="59"/>
-      <c r="D115" s="59"/>
-      <c r="E115" s="58"/>
-      <c r="F115" s="60"/>
-      <c r="G115" s="60"/>
-      <c r="H115" s="59"/>
-      <c r="I115" s="59"/>
-      <c r="J115" s="59"/>
-      <c r="K115" s="59"/>
-      <c r="L115" s="59"/>
-      <c r="M115" s="59"/>
-      <c r="N115" s="59"/>
-      <c r="O115" s="61"/>
-      <c r="P115" s="60"/>
-      <c r="Q115" s="59"/>
-      <c r="R115" s="59"/>
-      <c r="S115" s="59"/>
-      <c r="T115" s="62"/>
-      <c r="U115" s="59"/>
-      <c r="V115" s="59"/>
-      <c r="W115" s="59"/>
-      <c r="X115" s="59"/>
-      <c r="Y115" s="59"/>
-      <c r="Z115" s="63"/>
-      <c r="AA115" s="63"/>
-      <c r="AB115" s="59"/>
-      <c r="AC115" s="60"/>
-      <c r="AD115" s="59"/>
-      <c r="AE115" s="59"/>
-      <c r="AF115" s="59"/>
-      <c r="AG115" s="59"/>
-      <c r="AH115" s="59"/>
-      <c r="AI115" s="59"/>
+    <row r="115" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A115" s="59"/>
+      <c r="B115" s="60"/>
+      <c r="C115" s="60"/>
+      <c r="D115" s="60"/>
+      <c r="E115" s="59"/>
+      <c r="F115" s="61"/>
+      <c r="G115" s="61"/>
+      <c r="H115" s="60"/>
+      <c r="I115" s="60"/>
+      <c r="J115" s="60"/>
+      <c r="K115" s="60"/>
+      <c r="L115" s="60"/>
+      <c r="M115" s="60"/>
+      <c r="N115" s="60"/>
+      <c r="O115" s="62"/>
+      <c r="P115" s="61"/>
+      <c r="Q115" s="60"/>
+      <c r="R115" s="60"/>
+      <c r="S115" s="60"/>
+      <c r="T115" s="63"/>
+      <c r="U115" s="60"/>
+      <c r="V115" s="60"/>
+      <c r="W115" s="60"/>
+      <c r="X115" s="60"/>
+      <c r="Y115" s="60"/>
+      <c r="Z115" s="64"/>
+      <c r="AA115" s="64"/>
+      <c r="AB115" s="60"/>
+      <c r="AC115" s="61"/>
+      <c r="AD115" s="60"/>
+      <c r="AE115" s="60"/>
+      <c r="AF115" s="60"/>
+      <c r="AG115" s="60"/>
+      <c r="AH115" s="60"/>
+      <c r="AI115" s="60"/>
       <c r="AJ115" s="33"/>
     </row>
-    <row r="116" ht="15.6" customHeight="1">
-      <c r="A116" s="64"/>
+    <row r="116" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A116" s="65"/>
       <c r="B116" s="45"/>
       <c r="C116" s="45"/>
       <c r="D116" s="45"/>
-      <c r="E116" s="64"/>
+      <c r="E116" s="65"/>
       <c r="F116" s="44"/>
       <c r="G116" s="44"/>
       <c r="H116" s="45"/>
@@ -7307,12 +7234,12 @@
       <c r="L116" s="45"/>
       <c r="M116" s="45"/>
       <c r="N116" s="45"/>
-      <c r="O116" s="65"/>
+      <c r="O116" s="66"/>
       <c r="P116" s="44"/>
       <c r="Q116" s="45"/>
       <c r="R116" s="45"/>
       <c r="S116" s="45"/>
-      <c r="T116" s="66"/>
+      <c r="T116" s="67"/>
       <c r="U116" s="45"/>
       <c r="V116" s="45"/>
       <c r="W116" s="45"/>
@@ -7330,50 +7257,50 @@
       <c r="AI116" s="45"/>
       <c r="AJ116" s="33"/>
     </row>
-    <row r="117" ht="15.6" customHeight="1">
-      <c r="A117" s="58"/>
-      <c r="B117" s="59"/>
-      <c r="C117" s="59"/>
-      <c r="D117" s="59"/>
-      <c r="E117" s="58"/>
-      <c r="F117" s="60"/>
-      <c r="G117" s="60"/>
-      <c r="H117" s="59"/>
-      <c r="I117" s="59"/>
-      <c r="J117" s="59"/>
-      <c r="K117" s="59"/>
-      <c r="L117" s="59"/>
-      <c r="M117" s="59"/>
-      <c r="N117" s="59"/>
-      <c r="O117" s="61"/>
-      <c r="P117" s="60"/>
-      <c r="Q117" s="59"/>
-      <c r="R117" s="59"/>
-      <c r="S117" s="59"/>
-      <c r="T117" s="62"/>
-      <c r="U117" s="59"/>
-      <c r="V117" s="59"/>
-      <c r="W117" s="59"/>
-      <c r="X117" s="59"/>
-      <c r="Y117" s="59"/>
-      <c r="Z117" s="63"/>
-      <c r="AA117" s="63"/>
-      <c r="AB117" s="59"/>
-      <c r="AC117" s="60"/>
-      <c r="AD117" s="59"/>
-      <c r="AE117" s="59"/>
-      <c r="AF117" s="59"/>
-      <c r="AG117" s="59"/>
-      <c r="AH117" s="59"/>
-      <c r="AI117" s="59"/>
+    <row r="117" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A117" s="59"/>
+      <c r="B117" s="60"/>
+      <c r="C117" s="60"/>
+      <c r="D117" s="60"/>
+      <c r="E117" s="59"/>
+      <c r="F117" s="61"/>
+      <c r="G117" s="61"/>
+      <c r="H117" s="60"/>
+      <c r="I117" s="60"/>
+      <c r="J117" s="60"/>
+      <c r="K117" s="60"/>
+      <c r="L117" s="60"/>
+      <c r="M117" s="60"/>
+      <c r="N117" s="60"/>
+      <c r="O117" s="62"/>
+      <c r="P117" s="61"/>
+      <c r="Q117" s="60"/>
+      <c r="R117" s="60"/>
+      <c r="S117" s="60"/>
+      <c r="T117" s="63"/>
+      <c r="U117" s="60"/>
+      <c r="V117" s="60"/>
+      <c r="W117" s="60"/>
+      <c r="X117" s="60"/>
+      <c r="Y117" s="60"/>
+      <c r="Z117" s="64"/>
+      <c r="AA117" s="64"/>
+      <c r="AB117" s="60"/>
+      <c r="AC117" s="61"/>
+      <c r="AD117" s="60"/>
+      <c r="AE117" s="60"/>
+      <c r="AF117" s="60"/>
+      <c r="AG117" s="60"/>
+      <c r="AH117" s="60"/>
+      <c r="AI117" s="60"/>
       <c r="AJ117" s="33"/>
     </row>
-    <row r="118" ht="15.6" customHeight="1">
-      <c r="A118" s="64"/>
+    <row r="118" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A118" s="65"/>
       <c r="B118" s="45"/>
       <c r="C118" s="45"/>
       <c r="D118" s="45"/>
-      <c r="E118" s="64"/>
+      <c r="E118" s="65"/>
       <c r="F118" s="44"/>
       <c r="G118" s="44"/>
       <c r="H118" s="45"/>
@@ -7383,12 +7310,12 @@
       <c r="L118" s="45"/>
       <c r="M118" s="45"/>
       <c r="N118" s="45"/>
-      <c r="O118" s="65"/>
+      <c r="O118" s="66"/>
       <c r="P118" s="44"/>
       <c r="Q118" s="45"/>
       <c r="R118" s="45"/>
       <c r="S118" s="45"/>
-      <c r="T118" s="66"/>
+      <c r="T118" s="67"/>
       <c r="U118" s="45"/>
       <c r="V118" s="45"/>
       <c r="W118" s="45"/>
@@ -7406,50 +7333,50 @@
       <c r="AI118" s="45"/>
       <c r="AJ118" s="33"/>
     </row>
-    <row r="119" ht="15.6" customHeight="1">
-      <c r="A119" s="58"/>
-      <c r="B119" s="59"/>
-      <c r="C119" s="59"/>
-      <c r="D119" s="59"/>
-      <c r="E119" s="58"/>
-      <c r="F119" s="60"/>
-      <c r="G119" s="60"/>
-      <c r="H119" s="59"/>
-      <c r="I119" s="59"/>
-      <c r="J119" s="59"/>
-      <c r="K119" s="59"/>
-      <c r="L119" s="59"/>
-      <c r="M119" s="59"/>
-      <c r="N119" s="59"/>
-      <c r="O119" s="61"/>
-      <c r="P119" s="60"/>
-      <c r="Q119" s="59"/>
-      <c r="R119" s="59"/>
-      <c r="S119" s="59"/>
-      <c r="T119" s="62"/>
-      <c r="U119" s="59"/>
-      <c r="V119" s="59"/>
-      <c r="W119" s="59"/>
-      <c r="X119" s="59"/>
-      <c r="Y119" s="59"/>
-      <c r="Z119" s="63"/>
-      <c r="AA119" s="63"/>
-      <c r="AB119" s="59"/>
-      <c r="AC119" s="60"/>
-      <c r="AD119" s="59"/>
-      <c r="AE119" s="59"/>
-      <c r="AF119" s="59"/>
-      <c r="AG119" s="59"/>
-      <c r="AH119" s="59"/>
-      <c r="AI119" s="59"/>
+    <row r="119" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A119" s="59"/>
+      <c r="B119" s="60"/>
+      <c r="C119" s="60"/>
+      <c r="D119" s="60"/>
+      <c r="E119" s="59"/>
+      <c r="F119" s="61"/>
+      <c r="G119" s="61"/>
+      <c r="H119" s="60"/>
+      <c r="I119" s="60"/>
+      <c r="J119" s="60"/>
+      <c r="K119" s="60"/>
+      <c r="L119" s="60"/>
+      <c r="M119" s="60"/>
+      <c r="N119" s="60"/>
+      <c r="O119" s="62"/>
+      <c r="P119" s="61"/>
+      <c r="Q119" s="60"/>
+      <c r="R119" s="60"/>
+      <c r="S119" s="60"/>
+      <c r="T119" s="63"/>
+      <c r="U119" s="60"/>
+      <c r="V119" s="60"/>
+      <c r="W119" s="60"/>
+      <c r="X119" s="60"/>
+      <c r="Y119" s="60"/>
+      <c r="Z119" s="64"/>
+      <c r="AA119" s="64"/>
+      <c r="AB119" s="60"/>
+      <c r="AC119" s="61"/>
+      <c r="AD119" s="60"/>
+      <c r="AE119" s="60"/>
+      <c r="AF119" s="60"/>
+      <c r="AG119" s="60"/>
+      <c r="AH119" s="60"/>
+      <c r="AI119" s="60"/>
       <c r="AJ119" s="33"/>
     </row>
-    <row r="120" ht="15.6" customHeight="1">
-      <c r="A120" s="64"/>
+    <row r="120" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A120" s="65"/>
       <c r="B120" s="45"/>
       <c r="C120" s="45"/>
       <c r="D120" s="45"/>
-      <c r="E120" s="64"/>
+      <c r="E120" s="65"/>
       <c r="F120" s="44"/>
       <c r="G120" s="44"/>
       <c r="H120" s="45"/>
@@ -7459,12 +7386,12 @@
       <c r="L120" s="45"/>
       <c r="M120" s="45"/>
       <c r="N120" s="45"/>
-      <c r="O120" s="65"/>
+      <c r="O120" s="66"/>
       <c r="P120" s="44"/>
       <c r="Q120" s="45"/>
       <c r="R120" s="45"/>
       <c r="S120" s="45"/>
-      <c r="T120" s="66"/>
+      <c r="T120" s="67"/>
       <c r="U120" s="45"/>
       <c r="V120" s="45"/>
       <c r="W120" s="45"/>
@@ -7482,50 +7409,50 @@
       <c r="AI120" s="45"/>
       <c r="AJ120" s="33"/>
     </row>
-    <row r="121" ht="15.6" customHeight="1">
-      <c r="A121" s="58"/>
-      <c r="B121" s="59"/>
-      <c r="C121" s="59"/>
-      <c r="D121" s="59"/>
-      <c r="E121" s="58"/>
-      <c r="F121" s="60"/>
-      <c r="G121" s="60"/>
-      <c r="H121" s="59"/>
-      <c r="I121" s="59"/>
-      <c r="J121" s="59"/>
-      <c r="K121" s="59"/>
-      <c r="L121" s="59"/>
-      <c r="M121" s="59"/>
-      <c r="N121" s="59"/>
-      <c r="O121" s="61"/>
-      <c r="P121" s="60"/>
-      <c r="Q121" s="59"/>
-      <c r="R121" s="59"/>
-      <c r="S121" s="59"/>
-      <c r="T121" s="62"/>
-      <c r="U121" s="59"/>
-      <c r="V121" s="59"/>
-      <c r="W121" s="59"/>
-      <c r="X121" s="59"/>
-      <c r="Y121" s="59"/>
-      <c r="Z121" s="63"/>
-      <c r="AA121" s="63"/>
-      <c r="AB121" s="59"/>
-      <c r="AC121" s="60"/>
-      <c r="AD121" s="59"/>
-      <c r="AE121" s="59"/>
-      <c r="AF121" s="59"/>
-      <c r="AG121" s="59"/>
-      <c r="AH121" s="59"/>
-      <c r="AI121" s="59"/>
+    <row r="121" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A121" s="59"/>
+      <c r="B121" s="60"/>
+      <c r="C121" s="60"/>
+      <c r="D121" s="60"/>
+      <c r="E121" s="59"/>
+      <c r="F121" s="61"/>
+      <c r="G121" s="61"/>
+      <c r="H121" s="60"/>
+      <c r="I121" s="60"/>
+      <c r="J121" s="60"/>
+      <c r="K121" s="60"/>
+      <c r="L121" s="60"/>
+      <c r="M121" s="60"/>
+      <c r="N121" s="60"/>
+      <c r="O121" s="62"/>
+      <c r="P121" s="61"/>
+      <c r="Q121" s="60"/>
+      <c r="R121" s="60"/>
+      <c r="S121" s="60"/>
+      <c r="T121" s="63"/>
+      <c r="U121" s="60"/>
+      <c r="V121" s="60"/>
+      <c r="W121" s="60"/>
+      <c r="X121" s="60"/>
+      <c r="Y121" s="60"/>
+      <c r="Z121" s="64"/>
+      <c r="AA121" s="64"/>
+      <c r="AB121" s="60"/>
+      <c r="AC121" s="61"/>
+      <c r="AD121" s="60"/>
+      <c r="AE121" s="60"/>
+      <c r="AF121" s="60"/>
+      <c r="AG121" s="60"/>
+      <c r="AH121" s="60"/>
+      <c r="AI121" s="60"/>
       <c r="AJ121" s="33"/>
     </row>
-    <row r="122" ht="15.6" customHeight="1">
-      <c r="A122" s="64"/>
+    <row r="122" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A122" s="65"/>
       <c r="B122" s="45"/>
       <c r="C122" s="45"/>
       <c r="D122" s="45"/>
-      <c r="E122" s="64"/>
+      <c r="E122" s="65"/>
       <c r="F122" s="44"/>
       <c r="G122" s="44"/>
       <c r="H122" s="45"/>
@@ -7535,12 +7462,12 @@
       <c r="L122" s="45"/>
       <c r="M122" s="45"/>
       <c r="N122" s="45"/>
-      <c r="O122" s="65"/>
+      <c r="O122" s="66"/>
       <c r="P122" s="44"/>
       <c r="Q122" s="45"/>
       <c r="R122" s="45"/>
       <c r="S122" s="45"/>
-      <c r="T122" s="66"/>
+      <c r="T122" s="67"/>
       <c r="U122" s="45"/>
       <c r="V122" s="45"/>
       <c r="W122" s="45"/>
@@ -7558,50 +7485,50 @@
       <c r="AI122" s="45"/>
       <c r="AJ122" s="33"/>
     </row>
-    <row r="123" ht="15.6" customHeight="1">
-      <c r="A123" s="58"/>
-      <c r="B123" s="59"/>
-      <c r="C123" s="59"/>
-      <c r="D123" s="59"/>
-      <c r="E123" s="58"/>
-      <c r="F123" s="60"/>
-      <c r="G123" s="60"/>
-      <c r="H123" s="59"/>
-      <c r="I123" s="59"/>
-      <c r="J123" s="59"/>
-      <c r="K123" s="59"/>
-      <c r="L123" s="59"/>
-      <c r="M123" s="59"/>
-      <c r="N123" s="59"/>
-      <c r="O123" s="61"/>
-      <c r="P123" s="60"/>
-      <c r="Q123" s="59"/>
-      <c r="R123" s="59"/>
-      <c r="S123" s="59"/>
-      <c r="T123" s="62"/>
-      <c r="U123" s="59"/>
-      <c r="V123" s="59"/>
-      <c r="W123" s="59"/>
-      <c r="X123" s="59"/>
-      <c r="Y123" s="59"/>
-      <c r="Z123" s="63"/>
-      <c r="AA123" s="63"/>
-      <c r="AB123" s="59"/>
-      <c r="AC123" s="60"/>
-      <c r="AD123" s="59"/>
-      <c r="AE123" s="59"/>
-      <c r="AF123" s="59"/>
-      <c r="AG123" s="59"/>
-      <c r="AH123" s="59"/>
-      <c r="AI123" s="59"/>
+    <row r="123" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A123" s="59"/>
+      <c r="B123" s="60"/>
+      <c r="C123" s="60"/>
+      <c r="D123" s="60"/>
+      <c r="E123" s="59"/>
+      <c r="F123" s="61"/>
+      <c r="G123" s="61"/>
+      <c r="H123" s="60"/>
+      <c r="I123" s="60"/>
+      <c r="J123" s="60"/>
+      <c r="K123" s="60"/>
+      <c r="L123" s="60"/>
+      <c r="M123" s="60"/>
+      <c r="N123" s="60"/>
+      <c r="O123" s="62"/>
+      <c r="P123" s="61"/>
+      <c r="Q123" s="60"/>
+      <c r="R123" s="60"/>
+      <c r="S123" s="60"/>
+      <c r="T123" s="63"/>
+      <c r="U123" s="60"/>
+      <c r="V123" s="60"/>
+      <c r="W123" s="60"/>
+      <c r="X123" s="60"/>
+      <c r="Y123" s="60"/>
+      <c r="Z123" s="64"/>
+      <c r="AA123" s="64"/>
+      <c r="AB123" s="60"/>
+      <c r="AC123" s="61"/>
+      <c r="AD123" s="60"/>
+      <c r="AE123" s="60"/>
+      <c r="AF123" s="60"/>
+      <c r="AG123" s="60"/>
+      <c r="AH123" s="60"/>
+      <c r="AI123" s="60"/>
       <c r="AJ123" s="33"/>
     </row>
-    <row r="124" ht="15.6" customHeight="1">
-      <c r="A124" s="64"/>
+    <row r="124" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A124" s="65"/>
       <c r="B124" s="45"/>
       <c r="C124" s="45"/>
       <c r="D124" s="45"/>
-      <c r="E124" s="64"/>
+      <c r="E124" s="65"/>
       <c r="F124" s="44"/>
       <c r="G124" s="44"/>
       <c r="H124" s="45"/>
@@ -7611,12 +7538,12 @@
       <c r="L124" s="45"/>
       <c r="M124" s="45"/>
       <c r="N124" s="45"/>
-      <c r="O124" s="65"/>
+      <c r="O124" s="66"/>
       <c r="P124" s="44"/>
       <c r="Q124" s="45"/>
       <c r="R124" s="45"/>
       <c r="S124" s="45"/>
-      <c r="T124" s="66"/>
+      <c r="T124" s="67"/>
       <c r="U124" s="45"/>
       <c r="V124" s="45"/>
       <c r="W124" s="45"/>
@@ -7634,50 +7561,50 @@
       <c r="AI124" s="45"/>
       <c r="AJ124" s="33"/>
     </row>
-    <row r="125" ht="15.6" customHeight="1">
-      <c r="A125" s="58"/>
-      <c r="B125" s="59"/>
-      <c r="C125" s="59"/>
-      <c r="D125" s="59"/>
-      <c r="E125" s="58"/>
-      <c r="F125" s="60"/>
-      <c r="G125" s="60"/>
-      <c r="H125" s="59"/>
-      <c r="I125" s="59"/>
-      <c r="J125" s="59"/>
-      <c r="K125" s="59"/>
-      <c r="L125" s="59"/>
-      <c r="M125" s="59"/>
-      <c r="N125" s="59"/>
-      <c r="O125" s="61"/>
-      <c r="P125" s="60"/>
-      <c r="Q125" s="59"/>
-      <c r="R125" s="59"/>
-      <c r="S125" s="59"/>
-      <c r="T125" s="62"/>
-      <c r="U125" s="59"/>
-      <c r="V125" s="59"/>
-      <c r="W125" s="59"/>
-      <c r="X125" s="59"/>
-      <c r="Y125" s="59"/>
-      <c r="Z125" s="63"/>
-      <c r="AA125" s="63"/>
-      <c r="AB125" s="59"/>
-      <c r="AC125" s="60"/>
-      <c r="AD125" s="59"/>
-      <c r="AE125" s="59"/>
-      <c r="AF125" s="59"/>
-      <c r="AG125" s="59"/>
-      <c r="AH125" s="59"/>
-      <c r="AI125" s="59"/>
+    <row r="125" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A125" s="59"/>
+      <c r="B125" s="60"/>
+      <c r="C125" s="60"/>
+      <c r="D125" s="60"/>
+      <c r="E125" s="59"/>
+      <c r="F125" s="61"/>
+      <c r="G125" s="61"/>
+      <c r="H125" s="60"/>
+      <c r="I125" s="60"/>
+      <c r="J125" s="60"/>
+      <c r="K125" s="60"/>
+      <c r="L125" s="60"/>
+      <c r="M125" s="60"/>
+      <c r="N125" s="60"/>
+      <c r="O125" s="62"/>
+      <c r="P125" s="61"/>
+      <c r="Q125" s="60"/>
+      <c r="R125" s="60"/>
+      <c r="S125" s="60"/>
+      <c r="T125" s="63"/>
+      <c r="U125" s="60"/>
+      <c r="V125" s="60"/>
+      <c r="W125" s="60"/>
+      <c r="X125" s="60"/>
+      <c r="Y125" s="60"/>
+      <c r="Z125" s="64"/>
+      <c r="AA125" s="64"/>
+      <c r="AB125" s="60"/>
+      <c r="AC125" s="61"/>
+      <c r="AD125" s="60"/>
+      <c r="AE125" s="60"/>
+      <c r="AF125" s="60"/>
+      <c r="AG125" s="60"/>
+      <c r="AH125" s="60"/>
+      <c r="AI125" s="60"/>
       <c r="AJ125" s="33"/>
     </row>
-    <row r="126" ht="15.6" customHeight="1">
-      <c r="A126" s="64"/>
+    <row r="126" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A126" s="65"/>
       <c r="B126" s="45"/>
       <c r="C126" s="45"/>
       <c r="D126" s="45"/>
-      <c r="E126" s="64"/>
+      <c r="E126" s="65"/>
       <c r="F126" s="44"/>
       <c r="G126" s="44"/>
       <c r="H126" s="45"/>
@@ -7687,12 +7614,12 @@
       <c r="L126" s="45"/>
       <c r="M126" s="45"/>
       <c r="N126" s="45"/>
-      <c r="O126" s="65"/>
+      <c r="O126" s="66"/>
       <c r="P126" s="44"/>
       <c r="Q126" s="45"/>
       <c r="R126" s="45"/>
       <c r="S126" s="45"/>
-      <c r="T126" s="66"/>
+      <c r="T126" s="67"/>
       <c r="U126" s="45"/>
       <c r="V126" s="45"/>
       <c r="W126" s="45"/>
@@ -7710,50 +7637,50 @@
       <c r="AI126" s="45"/>
       <c r="AJ126" s="33"/>
     </row>
-    <row r="127" ht="15.6" customHeight="1">
-      <c r="A127" s="58"/>
-      <c r="B127" s="59"/>
-      <c r="C127" s="59"/>
-      <c r="D127" s="59"/>
-      <c r="E127" s="58"/>
-      <c r="F127" s="60"/>
-      <c r="G127" s="60"/>
-      <c r="H127" s="59"/>
-      <c r="I127" s="59"/>
-      <c r="J127" s="59"/>
-      <c r="K127" s="59"/>
-      <c r="L127" s="59"/>
-      <c r="M127" s="59"/>
-      <c r="N127" s="59"/>
-      <c r="O127" s="61"/>
-      <c r="P127" s="60"/>
-      <c r="Q127" s="59"/>
-      <c r="R127" s="59"/>
-      <c r="S127" s="59"/>
-      <c r="T127" s="62"/>
-      <c r="U127" s="59"/>
-      <c r="V127" s="59"/>
-      <c r="W127" s="59"/>
-      <c r="X127" s="59"/>
-      <c r="Y127" s="59"/>
-      <c r="Z127" s="63"/>
-      <c r="AA127" s="63"/>
-      <c r="AB127" s="59"/>
-      <c r="AC127" s="60"/>
-      <c r="AD127" s="59"/>
-      <c r="AE127" s="59"/>
-      <c r="AF127" s="59"/>
-      <c r="AG127" s="59"/>
-      <c r="AH127" s="59"/>
-      <c r="AI127" s="59"/>
+    <row r="127" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A127" s="59"/>
+      <c r="B127" s="60"/>
+      <c r="C127" s="60"/>
+      <c r="D127" s="60"/>
+      <c r="E127" s="59"/>
+      <c r="F127" s="61"/>
+      <c r="G127" s="61"/>
+      <c r="H127" s="60"/>
+      <c r="I127" s="60"/>
+      <c r="J127" s="60"/>
+      <c r="K127" s="60"/>
+      <c r="L127" s="60"/>
+      <c r="M127" s="60"/>
+      <c r="N127" s="60"/>
+      <c r="O127" s="62"/>
+      <c r="P127" s="61"/>
+      <c r="Q127" s="60"/>
+      <c r="R127" s="60"/>
+      <c r="S127" s="60"/>
+      <c r="T127" s="63"/>
+      <c r="U127" s="60"/>
+      <c r="V127" s="60"/>
+      <c r="W127" s="60"/>
+      <c r="X127" s="60"/>
+      <c r="Y127" s="60"/>
+      <c r="Z127" s="64"/>
+      <c r="AA127" s="64"/>
+      <c r="AB127" s="60"/>
+      <c r="AC127" s="61"/>
+      <c r="AD127" s="60"/>
+      <c r="AE127" s="60"/>
+      <c r="AF127" s="60"/>
+      <c r="AG127" s="60"/>
+      <c r="AH127" s="60"/>
+      <c r="AI127" s="60"/>
       <c r="AJ127" s="33"/>
     </row>
-    <row r="128" ht="15.6" customHeight="1">
-      <c r="A128" s="64"/>
+    <row r="128" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A128" s="65"/>
       <c r="B128" s="45"/>
       <c r="C128" s="45"/>
       <c r="D128" s="45"/>
-      <c r="E128" s="64"/>
+      <c r="E128" s="65"/>
       <c r="F128" s="44"/>
       <c r="G128" s="44"/>
       <c r="H128" s="45"/>
@@ -7763,12 +7690,12 @@
       <c r="L128" s="45"/>
       <c r="M128" s="45"/>
       <c r="N128" s="45"/>
-      <c r="O128" s="65"/>
+      <c r="O128" s="66"/>
       <c r="P128" s="44"/>
       <c r="Q128" s="45"/>
       <c r="R128" s="45"/>
       <c r="S128" s="45"/>
-      <c r="T128" s="66"/>
+      <c r="T128" s="67"/>
       <c r="U128" s="45"/>
       <c r="V128" s="45"/>
       <c r="W128" s="45"/>
@@ -7786,50 +7713,50 @@
       <c r="AI128" s="45"/>
       <c r="AJ128" s="33"/>
     </row>
-    <row r="129" ht="15.6" customHeight="1">
-      <c r="A129" s="58"/>
-      <c r="B129" s="59"/>
-      <c r="C129" s="59"/>
-      <c r="D129" s="59"/>
-      <c r="E129" s="58"/>
-      <c r="F129" s="60"/>
-      <c r="G129" s="60"/>
-      <c r="H129" s="59"/>
-      <c r="I129" s="59"/>
-      <c r="J129" s="59"/>
-      <c r="K129" s="59"/>
-      <c r="L129" s="59"/>
-      <c r="M129" s="59"/>
-      <c r="N129" s="59"/>
-      <c r="O129" s="61"/>
-      <c r="P129" s="60"/>
-      <c r="Q129" s="59"/>
-      <c r="R129" s="59"/>
-      <c r="S129" s="59"/>
-      <c r="T129" s="62"/>
-      <c r="U129" s="59"/>
-      <c r="V129" s="59"/>
-      <c r="W129" s="59"/>
-      <c r="X129" s="59"/>
-      <c r="Y129" s="59"/>
-      <c r="Z129" s="63"/>
-      <c r="AA129" s="63"/>
-      <c r="AB129" s="59"/>
-      <c r="AC129" s="60"/>
-      <c r="AD129" s="59"/>
-      <c r="AE129" s="59"/>
-      <c r="AF129" s="59"/>
-      <c r="AG129" s="59"/>
-      <c r="AH129" s="59"/>
-      <c r="AI129" s="59"/>
+    <row r="129" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A129" s="59"/>
+      <c r="B129" s="60"/>
+      <c r="C129" s="60"/>
+      <c r="D129" s="60"/>
+      <c r="E129" s="59"/>
+      <c r="F129" s="61"/>
+      <c r="G129" s="61"/>
+      <c r="H129" s="60"/>
+      <c r="I129" s="60"/>
+      <c r="J129" s="60"/>
+      <c r="K129" s="60"/>
+      <c r="L129" s="60"/>
+      <c r="M129" s="60"/>
+      <c r="N129" s="60"/>
+      <c r="O129" s="62"/>
+      <c r="P129" s="61"/>
+      <c r="Q129" s="60"/>
+      <c r="R129" s="60"/>
+      <c r="S129" s="60"/>
+      <c r="T129" s="63"/>
+      <c r="U129" s="60"/>
+      <c r="V129" s="60"/>
+      <c r="W129" s="60"/>
+      <c r="X129" s="60"/>
+      <c r="Y129" s="60"/>
+      <c r="Z129" s="64"/>
+      <c r="AA129" s="64"/>
+      <c r="AB129" s="60"/>
+      <c r="AC129" s="61"/>
+      <c r="AD129" s="60"/>
+      <c r="AE129" s="60"/>
+      <c r="AF129" s="60"/>
+      <c r="AG129" s="60"/>
+      <c r="AH129" s="60"/>
+      <c r="AI129" s="60"/>
       <c r="AJ129" s="33"/>
     </row>
-    <row r="130" ht="15.6" customHeight="1">
-      <c r="A130" s="64"/>
+    <row r="130" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A130" s="65"/>
       <c r="B130" s="45"/>
       <c r="C130" s="45"/>
       <c r="D130" s="45"/>
-      <c r="E130" s="64"/>
+      <c r="E130" s="65"/>
       <c r="F130" s="44"/>
       <c r="G130" s="44"/>
       <c r="H130" s="45"/>
@@ -7839,12 +7766,12 @@
       <c r="L130" s="45"/>
       <c r="M130" s="45"/>
       <c r="N130" s="45"/>
-      <c r="O130" s="65"/>
+      <c r="O130" s="66"/>
       <c r="P130" s="44"/>
       <c r="Q130" s="45"/>
       <c r="R130" s="45"/>
       <c r="S130" s="45"/>
-      <c r="T130" s="66"/>
+      <c r="T130" s="67"/>
       <c r="U130" s="45"/>
       <c r="V130" s="45"/>
       <c r="W130" s="45"/>
@@ -7862,50 +7789,50 @@
       <c r="AI130" s="45"/>
       <c r="AJ130" s="33"/>
     </row>
-    <row r="131" ht="15.6" customHeight="1">
-      <c r="A131" s="58"/>
-      <c r="B131" s="59"/>
-      <c r="C131" s="59"/>
-      <c r="D131" s="59"/>
-      <c r="E131" s="58"/>
-      <c r="F131" s="60"/>
-      <c r="G131" s="60"/>
-      <c r="H131" s="59"/>
-      <c r="I131" s="59"/>
-      <c r="J131" s="59"/>
-      <c r="K131" s="59"/>
-      <c r="L131" s="59"/>
-      <c r="M131" s="59"/>
-      <c r="N131" s="59"/>
-      <c r="O131" s="61"/>
-      <c r="P131" s="60"/>
-      <c r="Q131" s="59"/>
-      <c r="R131" s="59"/>
-      <c r="S131" s="59"/>
-      <c r="T131" s="62"/>
-      <c r="U131" s="59"/>
-      <c r="V131" s="59"/>
-      <c r="W131" s="59"/>
-      <c r="X131" s="59"/>
-      <c r="Y131" s="59"/>
-      <c r="Z131" s="63"/>
-      <c r="AA131" s="63"/>
-      <c r="AB131" s="59"/>
-      <c r="AC131" s="60"/>
-      <c r="AD131" s="59"/>
-      <c r="AE131" s="59"/>
-      <c r="AF131" s="59"/>
-      <c r="AG131" s="59"/>
-      <c r="AH131" s="59"/>
-      <c r="AI131" s="59"/>
+    <row r="131" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A131" s="59"/>
+      <c r="B131" s="60"/>
+      <c r="C131" s="60"/>
+      <c r="D131" s="60"/>
+      <c r="E131" s="59"/>
+      <c r="F131" s="61"/>
+      <c r="G131" s="61"/>
+      <c r="H131" s="60"/>
+      <c r="I131" s="60"/>
+      <c r="J131" s="60"/>
+      <c r="K131" s="60"/>
+      <c r="L131" s="60"/>
+      <c r="M131" s="60"/>
+      <c r="N131" s="60"/>
+      <c r="O131" s="62"/>
+      <c r="P131" s="61"/>
+      <c r="Q131" s="60"/>
+      <c r="R131" s="60"/>
+      <c r="S131" s="60"/>
+      <c r="T131" s="63"/>
+      <c r="U131" s="60"/>
+      <c r="V131" s="60"/>
+      <c r="W131" s="60"/>
+      <c r="X131" s="60"/>
+      <c r="Y131" s="60"/>
+      <c r="Z131" s="64"/>
+      <c r="AA131" s="64"/>
+      <c r="AB131" s="60"/>
+      <c r="AC131" s="61"/>
+      <c r="AD131" s="60"/>
+      <c r="AE131" s="60"/>
+      <c r="AF131" s="60"/>
+      <c r="AG131" s="60"/>
+      <c r="AH131" s="60"/>
+      <c r="AI131" s="60"/>
       <c r="AJ131" s="33"/>
     </row>
-    <row r="132" ht="15.6" customHeight="1">
-      <c r="A132" s="64"/>
+    <row r="132" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A132" s="65"/>
       <c r="B132" s="45"/>
       <c r="C132" s="45"/>
       <c r="D132" s="45"/>
-      <c r="E132" s="64"/>
+      <c r="E132" s="65"/>
       <c r="F132" s="44"/>
       <c r="G132" s="44"/>
       <c r="H132" s="45"/>
@@ -7915,12 +7842,12 @@
       <c r="L132" s="45"/>
       <c r="M132" s="45"/>
       <c r="N132" s="45"/>
-      <c r="O132" s="65"/>
+      <c r="O132" s="66"/>
       <c r="P132" s="44"/>
       <c r="Q132" s="45"/>
       <c r="R132" s="45"/>
       <c r="S132" s="45"/>
-      <c r="T132" s="66"/>
+      <c r="T132" s="67"/>
       <c r="U132" s="45"/>
       <c r="V132" s="45"/>
       <c r="W132" s="45"/>
@@ -7938,50 +7865,50 @@
       <c r="AI132" s="45"/>
       <c r="AJ132" s="33"/>
     </row>
-    <row r="133" ht="15.6" customHeight="1">
-      <c r="A133" s="58"/>
-      <c r="B133" s="59"/>
-      <c r="C133" s="59"/>
-      <c r="D133" s="59"/>
-      <c r="E133" s="58"/>
-      <c r="F133" s="60"/>
-      <c r="G133" s="60"/>
-      <c r="H133" s="59"/>
-      <c r="I133" s="59"/>
-      <c r="J133" s="59"/>
-      <c r="K133" s="59"/>
-      <c r="L133" s="59"/>
-      <c r="M133" s="59"/>
-      <c r="N133" s="59"/>
-      <c r="O133" s="61"/>
-      <c r="P133" s="60"/>
-      <c r="Q133" s="59"/>
-      <c r="R133" s="59"/>
-      <c r="S133" s="59"/>
-      <c r="T133" s="62"/>
-      <c r="U133" s="59"/>
-      <c r="V133" s="59"/>
-      <c r="W133" s="59"/>
-      <c r="X133" s="59"/>
-      <c r="Y133" s="59"/>
-      <c r="Z133" s="63"/>
-      <c r="AA133" s="63"/>
-      <c r="AB133" s="59"/>
-      <c r="AC133" s="60"/>
-      <c r="AD133" s="59"/>
-      <c r="AE133" s="59"/>
-      <c r="AF133" s="59"/>
-      <c r="AG133" s="59"/>
-      <c r="AH133" s="59"/>
-      <c r="AI133" s="59"/>
+    <row r="133" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A133" s="59"/>
+      <c r="B133" s="60"/>
+      <c r="C133" s="60"/>
+      <c r="D133" s="60"/>
+      <c r="E133" s="59"/>
+      <c r="F133" s="61"/>
+      <c r="G133" s="61"/>
+      <c r="H133" s="60"/>
+      <c r="I133" s="60"/>
+      <c r="J133" s="60"/>
+      <c r="K133" s="60"/>
+      <c r="L133" s="60"/>
+      <c r="M133" s="60"/>
+      <c r="N133" s="60"/>
+      <c r="O133" s="62"/>
+      <c r="P133" s="61"/>
+      <c r="Q133" s="60"/>
+      <c r="R133" s="60"/>
+      <c r="S133" s="60"/>
+      <c r="T133" s="63"/>
+      <c r="U133" s="60"/>
+      <c r="V133" s="60"/>
+      <c r="W133" s="60"/>
+      <c r="X133" s="60"/>
+      <c r="Y133" s="60"/>
+      <c r="Z133" s="64"/>
+      <c r="AA133" s="64"/>
+      <c r="AB133" s="60"/>
+      <c r="AC133" s="61"/>
+      <c r="AD133" s="60"/>
+      <c r="AE133" s="60"/>
+      <c r="AF133" s="60"/>
+      <c r="AG133" s="60"/>
+      <c r="AH133" s="60"/>
+      <c r="AI133" s="60"/>
       <c r="AJ133" s="33"/>
     </row>
-    <row r="134" ht="15.6" customHeight="1">
-      <c r="A134" s="64"/>
+    <row r="134" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A134" s="65"/>
       <c r="B134" s="45"/>
       <c r="C134" s="45"/>
       <c r="D134" s="45"/>
-      <c r="E134" s="64"/>
+      <c r="E134" s="65"/>
       <c r="F134" s="44"/>
       <c r="G134" s="44"/>
       <c r="H134" s="45"/>
@@ -7991,12 +7918,12 @@
       <c r="L134" s="45"/>
       <c r="M134" s="45"/>
       <c r="N134" s="45"/>
-      <c r="O134" s="65"/>
+      <c r="O134" s="66"/>
       <c r="P134" s="44"/>
       <c r="Q134" s="45"/>
       <c r="R134" s="45"/>
       <c r="S134" s="45"/>
-      <c r="T134" s="66"/>
+      <c r="T134" s="67"/>
       <c r="U134" s="45"/>
       <c r="V134" s="45"/>
       <c r="W134" s="45"/>
@@ -8014,50 +7941,50 @@
       <c r="AI134" s="45"/>
       <c r="AJ134" s="33"/>
     </row>
-    <row r="135" ht="15.6" customHeight="1">
-      <c r="A135" s="58"/>
-      <c r="B135" s="59"/>
-      <c r="C135" s="59"/>
-      <c r="D135" s="59"/>
-      <c r="E135" s="58"/>
-      <c r="F135" s="60"/>
-      <c r="G135" s="60"/>
-      <c r="H135" s="59"/>
-      <c r="I135" s="59"/>
-      <c r="J135" s="59"/>
-      <c r="K135" s="59"/>
-      <c r="L135" s="59"/>
-      <c r="M135" s="59"/>
-      <c r="N135" s="59"/>
-      <c r="O135" s="61"/>
-      <c r="P135" s="60"/>
-      <c r="Q135" s="59"/>
-      <c r="R135" s="59"/>
-      <c r="S135" s="59"/>
-      <c r="T135" s="62"/>
-      <c r="U135" s="59"/>
-      <c r="V135" s="59"/>
-      <c r="W135" s="59"/>
-      <c r="X135" s="59"/>
-      <c r="Y135" s="59"/>
-      <c r="Z135" s="63"/>
-      <c r="AA135" s="63"/>
-      <c r="AB135" s="59"/>
-      <c r="AC135" s="60"/>
-      <c r="AD135" s="59"/>
-      <c r="AE135" s="59"/>
-      <c r="AF135" s="59"/>
-      <c r="AG135" s="59"/>
-      <c r="AH135" s="59"/>
-      <c r="AI135" s="59"/>
+    <row r="135" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A135" s="59"/>
+      <c r="B135" s="60"/>
+      <c r="C135" s="60"/>
+      <c r="D135" s="60"/>
+      <c r="E135" s="59"/>
+      <c r="F135" s="61"/>
+      <c r="G135" s="61"/>
+      <c r="H135" s="60"/>
+      <c r="I135" s="60"/>
+      <c r="J135" s="60"/>
+      <c r="K135" s="60"/>
+      <c r="L135" s="60"/>
+      <c r="M135" s="60"/>
+      <c r="N135" s="60"/>
+      <c r="O135" s="62"/>
+      <c r="P135" s="61"/>
+      <c r="Q135" s="60"/>
+      <c r="R135" s="60"/>
+      <c r="S135" s="60"/>
+      <c r="T135" s="63"/>
+      <c r="U135" s="60"/>
+      <c r="V135" s="60"/>
+      <c r="W135" s="60"/>
+      <c r="X135" s="60"/>
+      <c r="Y135" s="60"/>
+      <c r="Z135" s="64"/>
+      <c r="AA135" s="64"/>
+      <c r="AB135" s="60"/>
+      <c r="AC135" s="61"/>
+      <c r="AD135" s="60"/>
+      <c r="AE135" s="60"/>
+      <c r="AF135" s="60"/>
+      <c r="AG135" s="60"/>
+      <c r="AH135" s="60"/>
+      <c r="AI135" s="60"/>
       <c r="AJ135" s="33"/>
     </row>
-    <row r="136" ht="15.6" customHeight="1">
-      <c r="A136" s="64"/>
+    <row r="136" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A136" s="65"/>
       <c r="B136" s="45"/>
       <c r="C136" s="45"/>
       <c r="D136" s="45"/>
-      <c r="E136" s="64"/>
+      <c r="E136" s="65"/>
       <c r="F136" s="44"/>
       <c r="G136" s="44"/>
       <c r="H136" s="45"/>
@@ -8067,12 +7994,12 @@
       <c r="L136" s="45"/>
       <c r="M136" s="45"/>
       <c r="N136" s="45"/>
-      <c r="O136" s="65"/>
+      <c r="O136" s="66"/>
       <c r="P136" s="44"/>
       <c r="Q136" s="45"/>
       <c r="R136" s="45"/>
       <c r="S136" s="45"/>
-      <c r="T136" s="66"/>
+      <c r="T136" s="67"/>
       <c r="U136" s="45"/>
       <c r="V136" s="45"/>
       <c r="W136" s="45"/>
@@ -8090,50 +8017,50 @@
       <c r="AI136" s="45"/>
       <c r="AJ136" s="33"/>
     </row>
-    <row r="137" ht="15.6" customHeight="1">
-      <c r="A137" s="58"/>
-      <c r="B137" s="59"/>
-      <c r="C137" s="59"/>
-      <c r="D137" s="59"/>
-      <c r="E137" s="58"/>
-      <c r="F137" s="60"/>
-      <c r="G137" s="60"/>
-      <c r="H137" s="59"/>
-      <c r="I137" s="59"/>
-      <c r="J137" s="59"/>
-      <c r="K137" s="59"/>
-      <c r="L137" s="59"/>
-      <c r="M137" s="59"/>
-      <c r="N137" s="59"/>
-      <c r="O137" s="61"/>
-      <c r="P137" s="60"/>
-      <c r="Q137" s="59"/>
-      <c r="R137" s="59"/>
-      <c r="S137" s="59"/>
-      <c r="T137" s="62"/>
-      <c r="U137" s="59"/>
-      <c r="V137" s="59"/>
-      <c r="W137" s="59"/>
-      <c r="X137" s="59"/>
-      <c r="Y137" s="59"/>
-      <c r="Z137" s="63"/>
-      <c r="AA137" s="63"/>
-      <c r="AB137" s="59"/>
-      <c r="AC137" s="60"/>
-      <c r="AD137" s="59"/>
-      <c r="AE137" s="59"/>
-      <c r="AF137" s="59"/>
-      <c r="AG137" s="59"/>
-      <c r="AH137" s="59"/>
-      <c r="AI137" s="59"/>
+    <row r="137" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A137" s="59"/>
+      <c r="B137" s="60"/>
+      <c r="C137" s="60"/>
+      <c r="D137" s="60"/>
+      <c r="E137" s="59"/>
+      <c r="F137" s="61"/>
+      <c r="G137" s="61"/>
+      <c r="H137" s="60"/>
+      <c r="I137" s="60"/>
+      <c r="J137" s="60"/>
+      <c r="K137" s="60"/>
+      <c r="L137" s="60"/>
+      <c r="M137" s="60"/>
+      <c r="N137" s="60"/>
+      <c r="O137" s="62"/>
+      <c r="P137" s="61"/>
+      <c r="Q137" s="60"/>
+      <c r="R137" s="60"/>
+      <c r="S137" s="60"/>
+      <c r="T137" s="63"/>
+      <c r="U137" s="60"/>
+      <c r="V137" s="60"/>
+      <c r="W137" s="60"/>
+      <c r="X137" s="60"/>
+      <c r="Y137" s="60"/>
+      <c r="Z137" s="64"/>
+      <c r="AA137" s="64"/>
+      <c r="AB137" s="60"/>
+      <c r="AC137" s="61"/>
+      <c r="AD137" s="60"/>
+      <c r="AE137" s="60"/>
+      <c r="AF137" s="60"/>
+      <c r="AG137" s="60"/>
+      <c r="AH137" s="60"/>
+      <c r="AI137" s="60"/>
       <c r="AJ137" s="33"/>
     </row>
-    <row r="138" ht="15.6" customHeight="1">
-      <c r="A138" s="64"/>
+    <row r="138" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A138" s="65"/>
       <c r="B138" s="45"/>
       <c r="C138" s="45"/>
       <c r="D138" s="45"/>
-      <c r="E138" s="64"/>
+      <c r="E138" s="65"/>
       <c r="F138" s="44"/>
       <c r="G138" s="44"/>
       <c r="H138" s="45"/>
@@ -8143,12 +8070,12 @@
       <c r="L138" s="45"/>
       <c r="M138" s="45"/>
       <c r="N138" s="45"/>
-      <c r="O138" s="65"/>
+      <c r="O138" s="66"/>
       <c r="P138" s="44"/>
       <c r="Q138" s="45"/>
       <c r="R138" s="45"/>
       <c r="S138" s="45"/>
-      <c r="T138" s="66"/>
+      <c r="T138" s="67"/>
       <c r="U138" s="45"/>
       <c r="V138" s="45"/>
       <c r="W138" s="45"/>
@@ -8166,50 +8093,50 @@
       <c r="AI138" s="45"/>
       <c r="AJ138" s="33"/>
     </row>
-    <row r="139" ht="15.6" customHeight="1">
-      <c r="A139" s="58"/>
-      <c r="B139" s="59"/>
-      <c r="C139" s="59"/>
-      <c r="D139" s="59"/>
-      <c r="E139" s="58"/>
-      <c r="F139" s="60"/>
-      <c r="G139" s="60"/>
-      <c r="H139" s="59"/>
-      <c r="I139" s="59"/>
-      <c r="J139" s="59"/>
-      <c r="K139" s="59"/>
-      <c r="L139" s="59"/>
-      <c r="M139" s="59"/>
-      <c r="N139" s="59"/>
-      <c r="O139" s="61"/>
-      <c r="P139" s="60"/>
-      <c r="Q139" s="59"/>
-      <c r="R139" s="59"/>
-      <c r="S139" s="59"/>
-      <c r="T139" s="62"/>
-      <c r="U139" s="59"/>
-      <c r="V139" s="59"/>
-      <c r="W139" s="59"/>
-      <c r="X139" s="59"/>
-      <c r="Y139" s="59"/>
-      <c r="Z139" s="63"/>
-      <c r="AA139" s="63"/>
-      <c r="AB139" s="59"/>
-      <c r="AC139" s="60"/>
-      <c r="AD139" s="59"/>
-      <c r="AE139" s="59"/>
-      <c r="AF139" s="59"/>
-      <c r="AG139" s="59"/>
-      <c r="AH139" s="59"/>
-      <c r="AI139" s="59"/>
+    <row r="139" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A139" s="59"/>
+      <c r="B139" s="60"/>
+      <c r="C139" s="60"/>
+      <c r="D139" s="60"/>
+      <c r="E139" s="59"/>
+      <c r="F139" s="61"/>
+      <c r="G139" s="61"/>
+      <c r="H139" s="60"/>
+      <c r="I139" s="60"/>
+      <c r="J139" s="60"/>
+      <c r="K139" s="60"/>
+      <c r="L139" s="60"/>
+      <c r="M139" s="60"/>
+      <c r="N139" s="60"/>
+      <c r="O139" s="62"/>
+      <c r="P139" s="61"/>
+      <c r="Q139" s="60"/>
+      <c r="R139" s="60"/>
+      <c r="S139" s="60"/>
+      <c r="T139" s="63"/>
+      <c r="U139" s="60"/>
+      <c r="V139" s="60"/>
+      <c r="W139" s="60"/>
+      <c r="X139" s="60"/>
+      <c r="Y139" s="60"/>
+      <c r="Z139" s="64"/>
+      <c r="AA139" s="64"/>
+      <c r="AB139" s="60"/>
+      <c r="AC139" s="61"/>
+      <c r="AD139" s="60"/>
+      <c r="AE139" s="60"/>
+      <c r="AF139" s="60"/>
+      <c r="AG139" s="60"/>
+      <c r="AH139" s="60"/>
+      <c r="AI139" s="60"/>
       <c r="AJ139" s="33"/>
     </row>
-    <row r="140" ht="15.6" customHeight="1">
-      <c r="A140" s="64"/>
+    <row r="140" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A140" s="65"/>
       <c r="B140" s="45"/>
       <c r="C140" s="45"/>
       <c r="D140" s="45"/>
-      <c r="E140" s="64"/>
+      <c r="E140" s="65"/>
       <c r="F140" s="44"/>
       <c r="G140" s="44"/>
       <c r="H140" s="45"/>
@@ -8219,12 +8146,12 @@
       <c r="L140" s="45"/>
       <c r="M140" s="45"/>
       <c r="N140" s="45"/>
-      <c r="O140" s="65"/>
+      <c r="O140" s="66"/>
       <c r="P140" s="44"/>
       <c r="Q140" s="45"/>
       <c r="R140" s="45"/>
       <c r="S140" s="45"/>
-      <c r="T140" s="66"/>
+      <c r="T140" s="67"/>
       <c r="U140" s="45"/>
       <c r="V140" s="45"/>
       <c r="W140" s="45"/>
@@ -8242,50 +8169,50 @@
       <c r="AI140" s="45"/>
       <c r="AJ140" s="33"/>
     </row>
-    <row r="141" ht="15.6" customHeight="1">
-      <c r="A141" s="58"/>
-      <c r="B141" s="59"/>
-      <c r="C141" s="59"/>
-      <c r="D141" s="59"/>
-      <c r="E141" s="58"/>
-      <c r="F141" s="60"/>
-      <c r="G141" s="60"/>
-      <c r="H141" s="59"/>
-      <c r="I141" s="59"/>
-      <c r="J141" s="59"/>
-      <c r="K141" s="59"/>
-      <c r="L141" s="59"/>
-      <c r="M141" s="59"/>
-      <c r="N141" s="59"/>
-      <c r="O141" s="61"/>
-      <c r="P141" s="60"/>
-      <c r="Q141" s="59"/>
-      <c r="R141" s="59"/>
-      <c r="S141" s="59"/>
-      <c r="T141" s="62"/>
-      <c r="U141" s="59"/>
-      <c r="V141" s="59"/>
-      <c r="W141" s="59"/>
-      <c r="X141" s="59"/>
-      <c r="Y141" s="59"/>
-      <c r="Z141" s="63"/>
-      <c r="AA141" s="63"/>
-      <c r="AB141" s="59"/>
-      <c r="AC141" s="60"/>
-      <c r="AD141" s="59"/>
-      <c r="AE141" s="59"/>
-      <c r="AF141" s="59"/>
-      <c r="AG141" s="59"/>
-      <c r="AH141" s="59"/>
-      <c r="AI141" s="59"/>
+    <row r="141" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A141" s="59"/>
+      <c r="B141" s="60"/>
+      <c r="C141" s="60"/>
+      <c r="D141" s="60"/>
+      <c r="E141" s="59"/>
+      <c r="F141" s="61"/>
+      <c r="G141" s="61"/>
+      <c r="H141" s="60"/>
+      <c r="I141" s="60"/>
+      <c r="J141" s="60"/>
+      <c r="K141" s="60"/>
+      <c r="L141" s="60"/>
+      <c r="M141" s="60"/>
+      <c r="N141" s="60"/>
+      <c r="O141" s="62"/>
+      <c r="P141" s="61"/>
+      <c r="Q141" s="60"/>
+      <c r="R141" s="60"/>
+      <c r="S141" s="60"/>
+      <c r="T141" s="63"/>
+      <c r="U141" s="60"/>
+      <c r="V141" s="60"/>
+      <c r="W141" s="60"/>
+      <c r="X141" s="60"/>
+      <c r="Y141" s="60"/>
+      <c r="Z141" s="64"/>
+      <c r="AA141" s="64"/>
+      <c r="AB141" s="60"/>
+      <c r="AC141" s="61"/>
+      <c r="AD141" s="60"/>
+      <c r="AE141" s="60"/>
+      <c r="AF141" s="60"/>
+      <c r="AG141" s="60"/>
+      <c r="AH141" s="60"/>
+      <c r="AI141" s="60"/>
       <c r="AJ141" s="33"/>
     </row>
-    <row r="142" ht="15.6" customHeight="1">
-      <c r="A142" s="64"/>
+    <row r="142" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A142" s="65"/>
       <c r="B142" s="45"/>
       <c r="C142" s="45"/>
       <c r="D142" s="45"/>
-      <c r="E142" s="64"/>
+      <c r="E142" s="65"/>
       <c r="F142" s="44"/>
       <c r="G142" s="44"/>
       <c r="H142" s="45"/>
@@ -8295,12 +8222,12 @@
       <c r="L142" s="45"/>
       <c r="M142" s="45"/>
       <c r="N142" s="45"/>
-      <c r="O142" s="65"/>
+      <c r="O142" s="66"/>
       <c r="P142" s="44"/>
       <c r="Q142" s="45"/>
       <c r="R142" s="45"/>
       <c r="S142" s="45"/>
-      <c r="T142" s="66"/>
+      <c r="T142" s="67"/>
       <c r="U142" s="45"/>
       <c r="V142" s="45"/>
       <c r="W142" s="45"/>
@@ -8318,50 +8245,50 @@
       <c r="AI142" s="45"/>
       <c r="AJ142" s="33"/>
     </row>
-    <row r="143" ht="15.6" customHeight="1">
-      <c r="A143" s="58"/>
-      <c r="B143" s="59"/>
-      <c r="C143" s="59"/>
-      <c r="D143" s="59"/>
-      <c r="E143" s="58"/>
-      <c r="F143" s="60"/>
-      <c r="G143" s="60"/>
-      <c r="H143" s="59"/>
-      <c r="I143" s="59"/>
-      <c r="J143" s="59"/>
-      <c r="K143" s="59"/>
-      <c r="L143" s="59"/>
-      <c r="M143" s="59"/>
-      <c r="N143" s="59"/>
-      <c r="O143" s="61"/>
-      <c r="P143" s="60"/>
-      <c r="Q143" s="59"/>
-      <c r="R143" s="59"/>
-      <c r="S143" s="59"/>
-      <c r="T143" s="62"/>
-      <c r="U143" s="59"/>
-      <c r="V143" s="59"/>
-      <c r="W143" s="59"/>
-      <c r="X143" s="59"/>
-      <c r="Y143" s="59"/>
-      <c r="Z143" s="63"/>
-      <c r="AA143" s="63"/>
-      <c r="AB143" s="59"/>
-      <c r="AC143" s="60"/>
-      <c r="AD143" s="59"/>
-      <c r="AE143" s="59"/>
-      <c r="AF143" s="59"/>
-      <c r="AG143" s="59"/>
-      <c r="AH143" s="59"/>
-      <c r="AI143" s="59"/>
+    <row r="143" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A143" s="59"/>
+      <c r="B143" s="60"/>
+      <c r="C143" s="60"/>
+      <c r="D143" s="60"/>
+      <c r="E143" s="59"/>
+      <c r="F143" s="61"/>
+      <c r="G143" s="61"/>
+      <c r="H143" s="60"/>
+      <c r="I143" s="60"/>
+      <c r="J143" s="60"/>
+      <c r="K143" s="60"/>
+      <c r="L143" s="60"/>
+      <c r="M143" s="60"/>
+      <c r="N143" s="60"/>
+      <c r="O143" s="62"/>
+      <c r="P143" s="61"/>
+      <c r="Q143" s="60"/>
+      <c r="R143" s="60"/>
+      <c r="S143" s="60"/>
+      <c r="T143" s="63"/>
+      <c r="U143" s="60"/>
+      <c r="V143" s="60"/>
+      <c r="W143" s="60"/>
+      <c r="X143" s="60"/>
+      <c r="Y143" s="60"/>
+      <c r="Z143" s="64"/>
+      <c r="AA143" s="64"/>
+      <c r="AB143" s="60"/>
+      <c r="AC143" s="61"/>
+      <c r="AD143" s="60"/>
+      <c r="AE143" s="60"/>
+      <c r="AF143" s="60"/>
+      <c r="AG143" s="60"/>
+      <c r="AH143" s="60"/>
+      <c r="AI143" s="60"/>
       <c r="AJ143" s="33"/>
     </row>
-    <row r="144" ht="15.6" customHeight="1">
-      <c r="A144" s="64"/>
+    <row r="144" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A144" s="65"/>
       <c r="B144" s="45"/>
       <c r="C144" s="45"/>
       <c r="D144" s="45"/>
-      <c r="E144" s="64"/>
+      <c r="E144" s="65"/>
       <c r="F144" s="44"/>
       <c r="G144" s="44"/>
       <c r="H144" s="45"/>
@@ -8371,12 +8298,12 @@
       <c r="L144" s="45"/>
       <c r="M144" s="45"/>
       <c r="N144" s="45"/>
-      <c r="O144" s="65"/>
+      <c r="O144" s="66"/>
       <c r="P144" s="44"/>
       <c r="Q144" s="45"/>
       <c r="R144" s="45"/>
       <c r="S144" s="45"/>
-      <c r="T144" s="66"/>
+      <c r="T144" s="67"/>
       <c r="U144" s="45"/>
       <c r="V144" s="45"/>
       <c r="W144" s="45"/>
@@ -8394,50 +8321,50 @@
       <c r="AI144" s="45"/>
       <c r="AJ144" s="33"/>
     </row>
-    <row r="145" ht="15.6" customHeight="1">
-      <c r="A145" s="58"/>
-      <c r="B145" s="59"/>
-      <c r="C145" s="59"/>
-      <c r="D145" s="59"/>
-      <c r="E145" s="58"/>
-      <c r="F145" s="60"/>
-      <c r="G145" s="60"/>
-      <c r="H145" s="59"/>
-      <c r="I145" s="59"/>
-      <c r="J145" s="59"/>
-      <c r="K145" s="59"/>
-      <c r="L145" s="59"/>
-      <c r="M145" s="59"/>
-      <c r="N145" s="59"/>
-      <c r="O145" s="61"/>
-      <c r="P145" s="60"/>
-      <c r="Q145" s="59"/>
-      <c r="R145" s="59"/>
-      <c r="S145" s="59"/>
-      <c r="T145" s="62"/>
-      <c r="U145" s="59"/>
-      <c r="V145" s="59"/>
-      <c r="W145" s="59"/>
-      <c r="X145" s="59"/>
-      <c r="Y145" s="59"/>
-      <c r="Z145" s="63"/>
-      <c r="AA145" s="63"/>
-      <c r="AB145" s="59"/>
-      <c r="AC145" s="60"/>
-      <c r="AD145" s="59"/>
-      <c r="AE145" s="59"/>
-      <c r="AF145" s="59"/>
-      <c r="AG145" s="59"/>
-      <c r="AH145" s="59"/>
-      <c r="AI145" s="59"/>
+    <row r="145" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A145" s="59"/>
+      <c r="B145" s="60"/>
+      <c r="C145" s="60"/>
+      <c r="D145" s="60"/>
+      <c r="E145" s="59"/>
+      <c r="F145" s="61"/>
+      <c r="G145" s="61"/>
+      <c r="H145" s="60"/>
+      <c r="I145" s="60"/>
+      <c r="J145" s="60"/>
+      <c r="K145" s="60"/>
+      <c r="L145" s="60"/>
+      <c r="M145" s="60"/>
+      <c r="N145" s="60"/>
+      <c r="O145" s="62"/>
+      <c r="P145" s="61"/>
+      <c r="Q145" s="60"/>
+      <c r="R145" s="60"/>
+      <c r="S145" s="60"/>
+      <c r="T145" s="63"/>
+      <c r="U145" s="60"/>
+      <c r="V145" s="60"/>
+      <c r="W145" s="60"/>
+      <c r="X145" s="60"/>
+      <c r="Y145" s="60"/>
+      <c r="Z145" s="64"/>
+      <c r="AA145" s="64"/>
+      <c r="AB145" s="60"/>
+      <c r="AC145" s="61"/>
+      <c r="AD145" s="60"/>
+      <c r="AE145" s="60"/>
+      <c r="AF145" s="60"/>
+      <c r="AG145" s="60"/>
+      <c r="AH145" s="60"/>
+      <c r="AI145" s="60"/>
       <c r="AJ145" s="33"/>
     </row>
-    <row r="146" ht="15.6" customHeight="1">
-      <c r="A146" s="64"/>
+    <row r="146" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A146" s="65"/>
       <c r="B146" s="45"/>
       <c r="C146" s="45"/>
       <c r="D146" s="45"/>
-      <c r="E146" s="64"/>
+      <c r="E146" s="65"/>
       <c r="F146" s="44"/>
       <c r="G146" s="44"/>
       <c r="H146" s="45"/>
@@ -8447,12 +8374,12 @@
       <c r="L146" s="45"/>
       <c r="M146" s="45"/>
       <c r="N146" s="45"/>
-      <c r="O146" s="65"/>
+      <c r="O146" s="66"/>
       <c r="P146" s="44"/>
       <c r="Q146" s="45"/>
       <c r="R146" s="45"/>
       <c r="S146" s="45"/>
-      <c r="T146" s="66"/>
+      <c r="T146" s="67"/>
       <c r="U146" s="45"/>
       <c r="V146" s="45"/>
       <c r="W146" s="45"/>
@@ -8470,50 +8397,50 @@
       <c r="AI146" s="45"/>
       <c r="AJ146" s="33"/>
     </row>
-    <row r="147" ht="15.6" customHeight="1">
-      <c r="A147" s="58"/>
-      <c r="B147" s="59"/>
-      <c r="C147" s="59"/>
-      <c r="D147" s="59"/>
-      <c r="E147" s="58"/>
-      <c r="F147" s="60"/>
-      <c r="G147" s="60"/>
-      <c r="H147" s="59"/>
-      <c r="I147" s="59"/>
-      <c r="J147" s="59"/>
-      <c r="K147" s="59"/>
-      <c r="L147" s="59"/>
-      <c r="M147" s="59"/>
-      <c r="N147" s="59"/>
-      <c r="O147" s="61"/>
-      <c r="P147" s="60"/>
-      <c r="Q147" s="59"/>
-      <c r="R147" s="59"/>
-      <c r="S147" s="59"/>
-      <c r="T147" s="62"/>
-      <c r="U147" s="59"/>
-      <c r="V147" s="59"/>
-      <c r="W147" s="59"/>
-      <c r="X147" s="59"/>
-      <c r="Y147" s="59"/>
-      <c r="Z147" s="63"/>
-      <c r="AA147" s="63"/>
-      <c r="AB147" s="59"/>
-      <c r="AC147" s="60"/>
-      <c r="AD147" s="59"/>
-      <c r="AE147" s="59"/>
-      <c r="AF147" s="59"/>
-      <c r="AG147" s="59"/>
-      <c r="AH147" s="59"/>
-      <c r="AI147" s="59"/>
+    <row r="147" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A147" s="59"/>
+      <c r="B147" s="60"/>
+      <c r="C147" s="60"/>
+      <c r="D147" s="60"/>
+      <c r="E147" s="59"/>
+      <c r="F147" s="61"/>
+      <c r="G147" s="61"/>
+      <c r="H147" s="60"/>
+      <c r="I147" s="60"/>
+      <c r="J147" s="60"/>
+      <c r="K147" s="60"/>
+      <c r="L147" s="60"/>
+      <c r="M147" s="60"/>
+      <c r="N147" s="60"/>
+      <c r="O147" s="62"/>
+      <c r="P147" s="61"/>
+      <c r="Q147" s="60"/>
+      <c r="R147" s="60"/>
+      <c r="S147" s="60"/>
+      <c r="T147" s="63"/>
+      <c r="U147" s="60"/>
+      <c r="V147" s="60"/>
+      <c r="W147" s="60"/>
+      <c r="X147" s="60"/>
+      <c r="Y147" s="60"/>
+      <c r="Z147" s="64"/>
+      <c r="AA147" s="64"/>
+      <c r="AB147" s="60"/>
+      <c r="AC147" s="61"/>
+      <c r="AD147" s="60"/>
+      <c r="AE147" s="60"/>
+      <c r="AF147" s="60"/>
+      <c r="AG147" s="60"/>
+      <c r="AH147" s="60"/>
+      <c r="AI147" s="60"/>
       <c r="AJ147" s="33"/>
     </row>
-    <row r="148" ht="15.6" customHeight="1">
-      <c r="A148" s="64"/>
+    <row r="148" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A148" s="65"/>
       <c r="B148" s="45"/>
       <c r="C148" s="45"/>
       <c r="D148" s="45"/>
-      <c r="E148" s="64"/>
+      <c r="E148" s="65"/>
       <c r="F148" s="44"/>
       <c r="G148" s="44"/>
       <c r="H148" s="45"/>
@@ -8523,12 +8450,12 @@
       <c r="L148" s="45"/>
       <c r="M148" s="45"/>
       <c r="N148" s="45"/>
-      <c r="O148" s="65"/>
+      <c r="O148" s="66"/>
       <c r="P148" s="44"/>
       <c r="Q148" s="45"/>
       <c r="R148" s="45"/>
       <c r="S148" s="45"/>
-      <c r="T148" s="66"/>
+      <c r="T148" s="67"/>
       <c r="U148" s="45"/>
       <c r="V148" s="45"/>
       <c r="W148" s="45"/>
@@ -8546,50 +8473,50 @@
       <c r="AI148" s="45"/>
       <c r="AJ148" s="33"/>
     </row>
-    <row r="149" ht="15.6" customHeight="1">
-      <c r="A149" s="58"/>
-      <c r="B149" s="59"/>
-      <c r="C149" s="59"/>
-      <c r="D149" s="59"/>
-      <c r="E149" s="58"/>
-      <c r="F149" s="60"/>
-      <c r="G149" s="60"/>
-      <c r="H149" s="59"/>
-      <c r="I149" s="59"/>
-      <c r="J149" s="59"/>
-      <c r="K149" s="59"/>
-      <c r="L149" s="59"/>
-      <c r="M149" s="59"/>
-      <c r="N149" s="59"/>
-      <c r="O149" s="61"/>
-      <c r="P149" s="60"/>
-      <c r="Q149" s="59"/>
-      <c r="R149" s="59"/>
-      <c r="S149" s="59"/>
-      <c r="T149" s="62"/>
-      <c r="U149" s="59"/>
-      <c r="V149" s="59"/>
-      <c r="W149" s="59"/>
-      <c r="X149" s="59"/>
-      <c r="Y149" s="59"/>
-      <c r="Z149" s="63"/>
-      <c r="AA149" s="63"/>
-      <c r="AB149" s="59"/>
-      <c r="AC149" s="60"/>
-      <c r="AD149" s="59"/>
-      <c r="AE149" s="59"/>
-      <c r="AF149" s="59"/>
-      <c r="AG149" s="59"/>
-      <c r="AH149" s="59"/>
-      <c r="AI149" s="59"/>
+    <row r="149" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A149" s="59"/>
+      <c r="B149" s="60"/>
+      <c r="C149" s="60"/>
+      <c r="D149" s="60"/>
+      <c r="E149" s="59"/>
+      <c r="F149" s="61"/>
+      <c r="G149" s="61"/>
+      <c r="H149" s="60"/>
+      <c r="I149" s="60"/>
+      <c r="J149" s="60"/>
+      <c r="K149" s="60"/>
+      <c r="L149" s="60"/>
+      <c r="M149" s="60"/>
+      <c r="N149" s="60"/>
+      <c r="O149" s="62"/>
+      <c r="P149" s="61"/>
+      <c r="Q149" s="60"/>
+      <c r="R149" s="60"/>
+      <c r="S149" s="60"/>
+      <c r="T149" s="63"/>
+      <c r="U149" s="60"/>
+      <c r="V149" s="60"/>
+      <c r="W149" s="60"/>
+      <c r="X149" s="60"/>
+      <c r="Y149" s="60"/>
+      <c r="Z149" s="64"/>
+      <c r="AA149" s="64"/>
+      <c r="AB149" s="60"/>
+      <c r="AC149" s="61"/>
+      <c r="AD149" s="60"/>
+      <c r="AE149" s="60"/>
+      <c r="AF149" s="60"/>
+      <c r="AG149" s="60"/>
+      <c r="AH149" s="60"/>
+      <c r="AI149" s="60"/>
       <c r="AJ149" s="33"/>
     </row>
-    <row r="150" ht="15.6" customHeight="1">
-      <c r="A150" s="64"/>
+    <row r="150" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A150" s="65"/>
       <c r="B150" s="45"/>
       <c r="C150" s="45"/>
       <c r="D150" s="45"/>
-      <c r="E150" s="64"/>
+      <c r="E150" s="65"/>
       <c r="F150" s="44"/>
       <c r="G150" s="44"/>
       <c r="H150" s="45"/>
@@ -8599,12 +8526,12 @@
       <c r="L150" s="45"/>
       <c r="M150" s="45"/>
       <c r="N150" s="45"/>
-      <c r="O150" s="65"/>
+      <c r="O150" s="66"/>
       <c r="P150" s="44"/>
       <c r="Q150" s="45"/>
       <c r="R150" s="45"/>
       <c r="S150" s="45"/>
-      <c r="T150" s="66"/>
+      <c r="T150" s="67"/>
       <c r="U150" s="45"/>
       <c r="V150" s="45"/>
       <c r="W150" s="45"/>
@@ -8622,50 +8549,50 @@
       <c r="AI150" s="45"/>
       <c r="AJ150" s="33"/>
     </row>
-    <row r="151" ht="15.6" customHeight="1">
-      <c r="A151" s="58"/>
-      <c r="B151" s="59"/>
-      <c r="C151" s="59"/>
-      <c r="D151" s="59"/>
-      <c r="E151" s="58"/>
-      <c r="F151" s="60"/>
-      <c r="G151" s="60"/>
-      <c r="H151" s="59"/>
-      <c r="I151" s="59"/>
-      <c r="J151" s="59"/>
-      <c r="K151" s="59"/>
-      <c r="L151" s="59"/>
-      <c r="M151" s="59"/>
-      <c r="N151" s="59"/>
-      <c r="O151" s="61"/>
-      <c r="P151" s="60"/>
-      <c r="Q151" s="59"/>
-      <c r="R151" s="59"/>
-      <c r="S151" s="59"/>
-      <c r="T151" s="62"/>
-      <c r="U151" s="59"/>
-      <c r="V151" s="59"/>
-      <c r="W151" s="59"/>
-      <c r="X151" s="59"/>
-      <c r="Y151" s="59"/>
-      <c r="Z151" s="63"/>
-      <c r="AA151" s="63"/>
-      <c r="AB151" s="59"/>
-      <c r="AC151" s="60"/>
-      <c r="AD151" s="59"/>
-      <c r="AE151" s="59"/>
-      <c r="AF151" s="59"/>
-      <c r="AG151" s="59"/>
-      <c r="AH151" s="59"/>
-      <c r="AI151" s="59"/>
+    <row r="151" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A151" s="59"/>
+      <c r="B151" s="60"/>
+      <c r="C151" s="60"/>
+      <c r="D151" s="60"/>
+      <c r="E151" s="59"/>
+      <c r="F151" s="61"/>
+      <c r="G151" s="61"/>
+      <c r="H151" s="60"/>
+      <c r="I151" s="60"/>
+      <c r="J151" s="60"/>
+      <c r="K151" s="60"/>
+      <c r="L151" s="60"/>
+      <c r="M151" s="60"/>
+      <c r="N151" s="60"/>
+      <c r="O151" s="62"/>
+      <c r="P151" s="61"/>
+      <c r="Q151" s="60"/>
+      <c r="R151" s="60"/>
+      <c r="S151" s="60"/>
+      <c r="T151" s="63"/>
+      <c r="U151" s="60"/>
+      <c r="V151" s="60"/>
+      <c r="W151" s="60"/>
+      <c r="X151" s="60"/>
+      <c r="Y151" s="60"/>
+      <c r="Z151" s="64"/>
+      <c r="AA151" s="64"/>
+      <c r="AB151" s="60"/>
+      <c r="AC151" s="61"/>
+      <c r="AD151" s="60"/>
+      <c r="AE151" s="60"/>
+      <c r="AF151" s="60"/>
+      <c r="AG151" s="60"/>
+      <c r="AH151" s="60"/>
+      <c r="AI151" s="60"/>
       <c r="AJ151" s="33"/>
     </row>
-    <row r="152" ht="15.6" customHeight="1">
-      <c r="A152" s="64"/>
+    <row r="152" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A152" s="65"/>
       <c r="B152" s="45"/>
       <c r="C152" s="45"/>
       <c r="D152" s="45"/>
-      <c r="E152" s="64"/>
+      <c r="E152" s="65"/>
       <c r="F152" s="44"/>
       <c r="G152" s="44"/>
       <c r="H152" s="45"/>
@@ -8675,12 +8602,12 @@
       <c r="L152" s="45"/>
       <c r="M152" s="45"/>
       <c r="N152" s="45"/>
-      <c r="O152" s="65"/>
+      <c r="O152" s="66"/>
       <c r="P152" s="44"/>
       <c r="Q152" s="45"/>
       <c r="R152" s="45"/>
       <c r="S152" s="45"/>
-      <c r="T152" s="66"/>
+      <c r="T152" s="67"/>
       <c r="U152" s="45"/>
       <c r="V152" s="45"/>
       <c r="W152" s="45"/>
@@ -8698,50 +8625,50 @@
       <c r="AI152" s="45"/>
       <c r="AJ152" s="33"/>
     </row>
-    <row r="153" ht="15.6" customHeight="1">
-      <c r="A153" s="58"/>
-      <c r="B153" s="59"/>
-      <c r="C153" s="59"/>
-      <c r="D153" s="59"/>
-      <c r="E153" s="58"/>
-      <c r="F153" s="60"/>
-      <c r="G153" s="60"/>
-      <c r="H153" s="59"/>
-      <c r="I153" s="59"/>
-      <c r="J153" s="59"/>
-      <c r="K153" s="59"/>
-      <c r="L153" s="59"/>
-      <c r="M153" s="59"/>
-      <c r="N153" s="59"/>
-      <c r="O153" s="61"/>
-      <c r="P153" s="60"/>
-      <c r="Q153" s="59"/>
-      <c r="R153" s="59"/>
-      <c r="S153" s="59"/>
-      <c r="T153" s="62"/>
-      <c r="U153" s="59"/>
-      <c r="V153" s="59"/>
-      <c r="W153" s="59"/>
-      <c r="X153" s="59"/>
-      <c r="Y153" s="59"/>
-      <c r="Z153" s="63"/>
-      <c r="AA153" s="63"/>
-      <c r="AB153" s="59"/>
-      <c r="AC153" s="60"/>
-      <c r="AD153" s="59"/>
-      <c r="AE153" s="59"/>
-      <c r="AF153" s="59"/>
-      <c r="AG153" s="59"/>
-      <c r="AH153" s="59"/>
-      <c r="AI153" s="59"/>
+    <row r="153" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A153" s="59"/>
+      <c r="B153" s="60"/>
+      <c r="C153" s="60"/>
+      <c r="D153" s="60"/>
+      <c r="E153" s="59"/>
+      <c r="F153" s="61"/>
+      <c r="G153" s="61"/>
+      <c r="H153" s="60"/>
+      <c r="I153" s="60"/>
+      <c r="J153" s="60"/>
+      <c r="K153" s="60"/>
+      <c r="L153" s="60"/>
+      <c r="M153" s="60"/>
+      <c r="N153" s="60"/>
+      <c r="O153" s="62"/>
+      <c r="P153" s="61"/>
+      <c r="Q153" s="60"/>
+      <c r="R153" s="60"/>
+      <c r="S153" s="60"/>
+      <c r="T153" s="63"/>
+      <c r="U153" s="60"/>
+      <c r="V153" s="60"/>
+      <c r="W153" s="60"/>
+      <c r="X153" s="60"/>
+      <c r="Y153" s="60"/>
+      <c r="Z153" s="64"/>
+      <c r="AA153" s="64"/>
+      <c r="AB153" s="60"/>
+      <c r="AC153" s="61"/>
+      <c r="AD153" s="60"/>
+      <c r="AE153" s="60"/>
+      <c r="AF153" s="60"/>
+      <c r="AG153" s="60"/>
+      <c r="AH153" s="60"/>
+      <c r="AI153" s="60"/>
       <c r="AJ153" s="33"/>
     </row>
-    <row r="154" ht="15.6" customHeight="1">
-      <c r="A154" s="64"/>
+    <row r="154" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A154" s="65"/>
       <c r="B154" s="45"/>
       <c r="C154" s="45"/>
       <c r="D154" s="45"/>
-      <c r="E154" s="64"/>
+      <c r="E154" s="65"/>
       <c r="F154" s="44"/>
       <c r="G154" s="44"/>
       <c r="H154" s="45"/>
@@ -8751,12 +8678,12 @@
       <c r="L154" s="45"/>
       <c r="M154" s="45"/>
       <c r="N154" s="45"/>
-      <c r="O154" s="65"/>
+      <c r="O154" s="66"/>
       <c r="P154" s="44"/>
       <c r="Q154" s="45"/>
       <c r="R154" s="45"/>
       <c r="S154" s="45"/>
-      <c r="T154" s="66"/>
+      <c r="T154" s="67"/>
       <c r="U154" s="45"/>
       <c r="V154" s="45"/>
       <c r="W154" s="45"/>
@@ -8774,50 +8701,50 @@
       <c r="AI154" s="45"/>
       <c r="AJ154" s="33"/>
     </row>
-    <row r="155" ht="15.6" customHeight="1">
-      <c r="A155" s="58"/>
-      <c r="B155" s="59"/>
-      <c r="C155" s="59"/>
-      <c r="D155" s="59"/>
-      <c r="E155" s="58"/>
-      <c r="F155" s="60"/>
-      <c r="G155" s="60"/>
-      <c r="H155" s="59"/>
-      <c r="I155" s="59"/>
-      <c r="J155" s="59"/>
-      <c r="K155" s="59"/>
-      <c r="L155" s="59"/>
-      <c r="M155" s="59"/>
-      <c r="N155" s="59"/>
-      <c r="O155" s="61"/>
-      <c r="P155" s="60"/>
-      <c r="Q155" s="59"/>
-      <c r="R155" s="59"/>
-      <c r="S155" s="59"/>
-      <c r="T155" s="62"/>
-      <c r="U155" s="59"/>
-      <c r="V155" s="59"/>
-      <c r="W155" s="59"/>
-      <c r="X155" s="59"/>
-      <c r="Y155" s="59"/>
-      <c r="Z155" s="63"/>
-      <c r="AA155" s="63"/>
-      <c r="AB155" s="59"/>
-      <c r="AC155" s="60"/>
-      <c r="AD155" s="59"/>
-      <c r="AE155" s="59"/>
-      <c r="AF155" s="59"/>
-      <c r="AG155" s="59"/>
-      <c r="AH155" s="59"/>
-      <c r="AI155" s="59"/>
+    <row r="155" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A155" s="59"/>
+      <c r="B155" s="60"/>
+      <c r="C155" s="60"/>
+      <c r="D155" s="60"/>
+      <c r="E155" s="59"/>
+      <c r="F155" s="61"/>
+      <c r="G155" s="61"/>
+      <c r="H155" s="60"/>
+      <c r="I155" s="60"/>
+      <c r="J155" s="60"/>
+      <c r="K155" s="60"/>
+      <c r="L155" s="60"/>
+      <c r="M155" s="60"/>
+      <c r="N155" s="60"/>
+      <c r="O155" s="62"/>
+      <c r="P155" s="61"/>
+      <c r="Q155" s="60"/>
+      <c r="R155" s="60"/>
+      <c r="S155" s="60"/>
+      <c r="T155" s="63"/>
+      <c r="U155" s="60"/>
+      <c r="V155" s="60"/>
+      <c r="W155" s="60"/>
+      <c r="X155" s="60"/>
+      <c r="Y155" s="60"/>
+      <c r="Z155" s="64"/>
+      <c r="AA155" s="64"/>
+      <c r="AB155" s="60"/>
+      <c r="AC155" s="61"/>
+      <c r="AD155" s="60"/>
+      <c r="AE155" s="60"/>
+      <c r="AF155" s="60"/>
+      <c r="AG155" s="60"/>
+      <c r="AH155" s="60"/>
+      <c r="AI155" s="60"/>
       <c r="AJ155" s="33"/>
     </row>
-    <row r="156" ht="15.6" customHeight="1">
-      <c r="A156" s="64"/>
+    <row r="156" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A156" s="65"/>
       <c r="B156" s="45"/>
       <c r="C156" s="45"/>
       <c r="D156" s="45"/>
-      <c r="E156" s="64"/>
+      <c r="E156" s="65"/>
       <c r="F156" s="44"/>
       <c r="G156" s="44"/>
       <c r="H156" s="45"/>
@@ -8827,12 +8754,12 @@
       <c r="L156" s="45"/>
       <c r="M156" s="45"/>
       <c r="N156" s="45"/>
-      <c r="O156" s="65"/>
+      <c r="O156" s="66"/>
       <c r="P156" s="44"/>
       <c r="Q156" s="45"/>
       <c r="R156" s="45"/>
       <c r="S156" s="45"/>
-      <c r="T156" s="66"/>
+      <c r="T156" s="67"/>
       <c r="U156" s="45"/>
       <c r="V156" s="45"/>
       <c r="W156" s="45"/>
@@ -8850,50 +8777,50 @@
       <c r="AI156" s="45"/>
       <c r="AJ156" s="33"/>
     </row>
-    <row r="157" ht="15.6" customHeight="1">
-      <c r="A157" s="58"/>
-      <c r="B157" s="59"/>
-      <c r="C157" s="59"/>
-      <c r="D157" s="59"/>
-      <c r="E157" s="58"/>
-      <c r="F157" s="60"/>
-      <c r="G157" s="60"/>
-      <c r="H157" s="59"/>
-      <c r="I157" s="59"/>
-      <c r="J157" s="59"/>
-      <c r="K157" s="59"/>
-      <c r="L157" s="59"/>
-      <c r="M157" s="59"/>
-      <c r="N157" s="59"/>
-      <c r="O157" s="61"/>
-      <c r="P157" s="60"/>
-      <c r="Q157" s="59"/>
-      <c r="R157" s="59"/>
-      <c r="S157" s="59"/>
-      <c r="T157" s="62"/>
-      <c r="U157" s="59"/>
-      <c r="V157" s="59"/>
-      <c r="W157" s="59"/>
-      <c r="X157" s="59"/>
-      <c r="Y157" s="59"/>
-      <c r="Z157" s="63"/>
-      <c r="AA157" s="63"/>
-      <c r="AB157" s="59"/>
-      <c r="AC157" s="60"/>
-      <c r="AD157" s="59"/>
-      <c r="AE157" s="59"/>
-      <c r="AF157" s="59"/>
-      <c r="AG157" s="59"/>
-      <c r="AH157" s="59"/>
-      <c r="AI157" s="59"/>
+    <row r="157" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A157" s="59"/>
+      <c r="B157" s="60"/>
+      <c r="C157" s="60"/>
+      <c r="D157" s="60"/>
+      <c r="E157" s="59"/>
+      <c r="F157" s="61"/>
+      <c r="G157" s="61"/>
+      <c r="H157" s="60"/>
+      <c r="I157" s="60"/>
+      <c r="J157" s="60"/>
+      <c r="K157" s="60"/>
+      <c r="L157" s="60"/>
+      <c r="M157" s="60"/>
+      <c r="N157" s="60"/>
+      <c r="O157" s="62"/>
+      <c r="P157" s="61"/>
+      <c r="Q157" s="60"/>
+      <c r="R157" s="60"/>
+      <c r="S157" s="60"/>
+      <c r="T157" s="63"/>
+      <c r="U157" s="60"/>
+      <c r="V157" s="60"/>
+      <c r="W157" s="60"/>
+      <c r="X157" s="60"/>
+      <c r="Y157" s="60"/>
+      <c r="Z157" s="64"/>
+      <c r="AA157" s="64"/>
+      <c r="AB157" s="60"/>
+      <c r="AC157" s="61"/>
+      <c r="AD157" s="60"/>
+      <c r="AE157" s="60"/>
+      <c r="AF157" s="60"/>
+      <c r="AG157" s="60"/>
+      <c r="AH157" s="60"/>
+      <c r="AI157" s="60"/>
       <c r="AJ157" s="33"/>
     </row>
-    <row r="158" ht="15.6" customHeight="1">
-      <c r="A158" s="64"/>
+    <row r="158" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A158" s="65"/>
       <c r="B158" s="45"/>
       <c r="C158" s="45"/>
       <c r="D158" s="45"/>
-      <c r="E158" s="64"/>
+      <c r="E158" s="65"/>
       <c r="F158" s="44"/>
       <c r="G158" s="44"/>
       <c r="H158" s="45"/>
@@ -8903,12 +8830,12 @@
       <c r="L158" s="45"/>
       <c r="M158" s="45"/>
       <c r="N158" s="45"/>
-      <c r="O158" s="65"/>
+      <c r="O158" s="66"/>
       <c r="P158" s="44"/>
       <c r="Q158" s="45"/>
       <c r="R158" s="45"/>
       <c r="S158" s="45"/>
-      <c r="T158" s="66"/>
+      <c r="T158" s="67"/>
       <c r="U158" s="45"/>
       <c r="V158" s="45"/>
       <c r="W158" s="45"/>
@@ -8926,50 +8853,50 @@
       <c r="AI158" s="45"/>
       <c r="AJ158" s="33"/>
     </row>
-    <row r="159" ht="15.6" customHeight="1">
-      <c r="A159" s="58"/>
-      <c r="B159" s="59"/>
-      <c r="C159" s="59"/>
-      <c r="D159" s="59"/>
-      <c r="E159" s="58"/>
-      <c r="F159" s="60"/>
-      <c r="G159" s="60"/>
-      <c r="H159" s="59"/>
-      <c r="I159" s="59"/>
-      <c r="J159" s="59"/>
-      <c r="K159" s="59"/>
-      <c r="L159" s="59"/>
-      <c r="M159" s="59"/>
-      <c r="N159" s="59"/>
-      <c r="O159" s="61"/>
-      <c r="P159" s="60"/>
-      <c r="Q159" s="59"/>
-      <c r="R159" s="59"/>
-      <c r="S159" s="59"/>
-      <c r="T159" s="62"/>
-      <c r="U159" s="59"/>
-      <c r="V159" s="59"/>
-      <c r="W159" s="59"/>
-      <c r="X159" s="59"/>
-      <c r="Y159" s="59"/>
-      <c r="Z159" s="63"/>
-      <c r="AA159" s="63"/>
-      <c r="AB159" s="59"/>
-      <c r="AC159" s="60"/>
-      <c r="AD159" s="59"/>
-      <c r="AE159" s="59"/>
-      <c r="AF159" s="59"/>
-      <c r="AG159" s="59"/>
-      <c r="AH159" s="59"/>
-      <c r="AI159" s="59"/>
+    <row r="159" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A159" s="59"/>
+      <c r="B159" s="60"/>
+      <c r="C159" s="60"/>
+      <c r="D159" s="60"/>
+      <c r="E159" s="59"/>
+      <c r="F159" s="61"/>
+      <c r="G159" s="61"/>
+      <c r="H159" s="60"/>
+      <c r="I159" s="60"/>
+      <c r="J159" s="60"/>
+      <c r="K159" s="60"/>
+      <c r="L159" s="60"/>
+      <c r="M159" s="60"/>
+      <c r="N159" s="60"/>
+      <c r="O159" s="62"/>
+      <c r="P159" s="61"/>
+      <c r="Q159" s="60"/>
+      <c r="R159" s="60"/>
+      <c r="S159" s="60"/>
+      <c r="T159" s="63"/>
+      <c r="U159" s="60"/>
+      <c r="V159" s="60"/>
+      <c r="W159" s="60"/>
+      <c r="X159" s="60"/>
+      <c r="Y159" s="60"/>
+      <c r="Z159" s="64"/>
+      <c r="AA159" s="64"/>
+      <c r="AB159" s="60"/>
+      <c r="AC159" s="61"/>
+      <c r="AD159" s="60"/>
+      <c r="AE159" s="60"/>
+      <c r="AF159" s="60"/>
+      <c r="AG159" s="60"/>
+      <c r="AH159" s="60"/>
+      <c r="AI159" s="60"/>
       <c r="AJ159" s="33"/>
     </row>
-    <row r="160" ht="15.6" customHeight="1">
-      <c r="A160" s="64"/>
+    <row r="160" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A160" s="65"/>
       <c r="B160" s="45"/>
       <c r="C160" s="45"/>
       <c r="D160" s="45"/>
-      <c r="E160" s="64"/>
+      <c r="E160" s="65"/>
       <c r="F160" s="44"/>
       <c r="G160" s="44"/>
       <c r="H160" s="45"/>
@@ -8979,12 +8906,12 @@
       <c r="L160" s="45"/>
       <c r="M160" s="45"/>
       <c r="N160" s="45"/>
-      <c r="O160" s="65"/>
+      <c r="O160" s="66"/>
       <c r="P160" s="44"/>
       <c r="Q160" s="45"/>
       <c r="R160" s="45"/>
       <c r="S160" s="45"/>
-      <c r="T160" s="66"/>
+      <c r="T160" s="67"/>
       <c r="U160" s="45"/>
       <c r="V160" s="45"/>
       <c r="W160" s="45"/>
@@ -9002,50 +8929,50 @@
       <c r="AI160" s="45"/>
       <c r="AJ160" s="33"/>
     </row>
-    <row r="161" ht="15.6" customHeight="1">
-      <c r="A161" s="58"/>
-      <c r="B161" s="59"/>
-      <c r="C161" s="59"/>
-      <c r="D161" s="59"/>
-      <c r="E161" s="58"/>
-      <c r="F161" s="60"/>
-      <c r="G161" s="60"/>
-      <c r="H161" s="59"/>
-      <c r="I161" s="59"/>
-      <c r="J161" s="59"/>
-      <c r="K161" s="59"/>
-      <c r="L161" s="59"/>
-      <c r="M161" s="59"/>
-      <c r="N161" s="59"/>
-      <c r="O161" s="61"/>
-      <c r="P161" s="60"/>
-      <c r="Q161" s="59"/>
-      <c r="R161" s="59"/>
-      <c r="S161" s="59"/>
-      <c r="T161" s="62"/>
-      <c r="U161" s="59"/>
-      <c r="V161" s="59"/>
-      <c r="W161" s="59"/>
-      <c r="X161" s="59"/>
-      <c r="Y161" s="59"/>
-      <c r="Z161" s="63"/>
-      <c r="AA161" s="63"/>
-      <c r="AB161" s="59"/>
-      <c r="AC161" s="60"/>
-      <c r="AD161" s="59"/>
-      <c r="AE161" s="59"/>
-      <c r="AF161" s="59"/>
-      <c r="AG161" s="59"/>
-      <c r="AH161" s="59"/>
-      <c r="AI161" s="59"/>
+    <row r="161" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A161" s="59"/>
+      <c r="B161" s="60"/>
+      <c r="C161" s="60"/>
+      <c r="D161" s="60"/>
+      <c r="E161" s="59"/>
+      <c r="F161" s="61"/>
+      <c r="G161" s="61"/>
+      <c r="H161" s="60"/>
+      <c r="I161" s="60"/>
+      <c r="J161" s="60"/>
+      <c r="K161" s="60"/>
+      <c r="L161" s="60"/>
+      <c r="M161" s="60"/>
+      <c r="N161" s="60"/>
+      <c r="O161" s="62"/>
+      <c r="P161" s="61"/>
+      <c r="Q161" s="60"/>
+      <c r="R161" s="60"/>
+      <c r="S161" s="60"/>
+      <c r="T161" s="63"/>
+      <c r="U161" s="60"/>
+      <c r="V161" s="60"/>
+      <c r="W161" s="60"/>
+      <c r="X161" s="60"/>
+      <c r="Y161" s="60"/>
+      <c r="Z161" s="64"/>
+      <c r="AA161" s="64"/>
+      <c r="AB161" s="60"/>
+      <c r="AC161" s="61"/>
+      <c r="AD161" s="60"/>
+      <c r="AE161" s="60"/>
+      <c r="AF161" s="60"/>
+      <c r="AG161" s="60"/>
+      <c r="AH161" s="60"/>
+      <c r="AI161" s="60"/>
       <c r="AJ161" s="33"/>
     </row>
-    <row r="162" ht="15.6" customHeight="1">
-      <c r="A162" s="64"/>
+    <row r="162" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A162" s="65"/>
       <c r="B162" s="45"/>
       <c r="C162" s="45"/>
       <c r="D162" s="45"/>
-      <c r="E162" s="64"/>
+      <c r="E162" s="65"/>
       <c r="F162" s="44"/>
       <c r="G162" s="44"/>
       <c r="H162" s="45"/>
@@ -9055,12 +8982,12 @@
       <c r="L162" s="45"/>
       <c r="M162" s="45"/>
       <c r="N162" s="45"/>
-      <c r="O162" s="65"/>
+      <c r="O162" s="66"/>
       <c r="P162" s="44"/>
       <c r="Q162" s="45"/>
       <c r="R162" s="45"/>
       <c r="S162" s="45"/>
-      <c r="T162" s="66"/>
+      <c r="T162" s="67"/>
       <c r="U162" s="45"/>
       <c r="V162" s="45"/>
       <c r="W162" s="45"/>
@@ -9078,50 +9005,50 @@
       <c r="AI162" s="45"/>
       <c r="AJ162" s="33"/>
     </row>
-    <row r="163" ht="15.6" customHeight="1">
-      <c r="A163" s="58"/>
-      <c r="B163" s="59"/>
-      <c r="C163" s="59"/>
-      <c r="D163" s="59"/>
-      <c r="E163" s="58"/>
-      <c r="F163" s="60"/>
-      <c r="G163" s="60"/>
-      <c r="H163" s="59"/>
-      <c r="I163" s="59"/>
-      <c r="J163" s="59"/>
-      <c r="K163" s="59"/>
-      <c r="L163" s="59"/>
-      <c r="M163" s="59"/>
-      <c r="N163" s="59"/>
-      <c r="O163" s="61"/>
-      <c r="P163" s="60"/>
-      <c r="Q163" s="59"/>
-      <c r="R163" s="59"/>
-      <c r="S163" s="59"/>
-      <c r="T163" s="62"/>
-      <c r="U163" s="59"/>
-      <c r="V163" s="59"/>
-      <c r="W163" s="59"/>
-      <c r="X163" s="59"/>
-      <c r="Y163" s="59"/>
-      <c r="Z163" s="63"/>
-      <c r="AA163" s="63"/>
-      <c r="AB163" s="59"/>
-      <c r="AC163" s="60"/>
-      <c r="AD163" s="59"/>
-      <c r="AE163" s="59"/>
-      <c r="AF163" s="59"/>
-      <c r="AG163" s="59"/>
-      <c r="AH163" s="59"/>
-      <c r="AI163" s="59"/>
+    <row r="163" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A163" s="59"/>
+      <c r="B163" s="60"/>
+      <c r="C163" s="60"/>
+      <c r="D163" s="60"/>
+      <c r="E163" s="59"/>
+      <c r="F163" s="61"/>
+      <c r="G163" s="61"/>
+      <c r="H163" s="60"/>
+      <c r="I163" s="60"/>
+      <c r="J163" s="60"/>
+      <c r="K163" s="60"/>
+      <c r="L163" s="60"/>
+      <c r="M163" s="60"/>
+      <c r="N163" s="60"/>
+      <c r="O163" s="62"/>
+      <c r="P163" s="61"/>
+      <c r="Q163" s="60"/>
+      <c r="R163" s="60"/>
+      <c r="S163" s="60"/>
+      <c r="T163" s="63"/>
+      <c r="U163" s="60"/>
+      <c r="V163" s="60"/>
+      <c r="W163" s="60"/>
+      <c r="X163" s="60"/>
+      <c r="Y163" s="60"/>
+      <c r="Z163" s="64"/>
+      <c r="AA163" s="64"/>
+      <c r="AB163" s="60"/>
+      <c r="AC163" s="61"/>
+      <c r="AD163" s="60"/>
+      <c r="AE163" s="60"/>
+      <c r="AF163" s="60"/>
+      <c r="AG163" s="60"/>
+      <c r="AH163" s="60"/>
+      <c r="AI163" s="60"/>
       <c r="AJ163" s="33"/>
     </row>
-    <row r="164" ht="15.6" customHeight="1">
-      <c r="A164" s="64"/>
+    <row r="164" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A164" s="65"/>
       <c r="B164" s="45"/>
       <c r="C164" s="45"/>
       <c r="D164" s="45"/>
-      <c r="E164" s="64"/>
+      <c r="E164" s="65"/>
       <c r="F164" s="44"/>
       <c r="G164" s="44"/>
       <c r="H164" s="45"/>
@@ -9131,12 +9058,12 @@
       <c r="L164" s="45"/>
       <c r="M164" s="45"/>
       <c r="N164" s="45"/>
-      <c r="O164" s="65"/>
+      <c r="O164" s="66"/>
       <c r="P164" s="44"/>
       <c r="Q164" s="45"/>
       <c r="R164" s="45"/>
       <c r="S164" s="45"/>
-      <c r="T164" s="66"/>
+      <c r="T164" s="67"/>
       <c r="U164" s="45"/>
       <c r="V164" s="45"/>
       <c r="W164" s="45"/>
@@ -9154,50 +9081,50 @@
       <c r="AI164" s="45"/>
       <c r="AJ164" s="33"/>
     </row>
-    <row r="165" ht="15.6" customHeight="1">
-      <c r="A165" s="58"/>
-      <c r="B165" s="59"/>
-      <c r="C165" s="59"/>
-      <c r="D165" s="59"/>
-      <c r="E165" s="58"/>
-      <c r="F165" s="60"/>
-      <c r="G165" s="60"/>
-      <c r="H165" s="59"/>
-      <c r="I165" s="59"/>
-      <c r="J165" s="59"/>
-      <c r="K165" s="59"/>
-      <c r="L165" s="59"/>
-      <c r="M165" s="59"/>
-      <c r="N165" s="59"/>
-      <c r="O165" s="61"/>
-      <c r="P165" s="60"/>
-      <c r="Q165" s="59"/>
-      <c r="R165" s="59"/>
-      <c r="S165" s="59"/>
-      <c r="T165" s="62"/>
-      <c r="U165" s="59"/>
-      <c r="V165" s="59"/>
-      <c r="W165" s="59"/>
-      <c r="X165" s="59"/>
-      <c r="Y165" s="59"/>
-      <c r="Z165" s="63"/>
-      <c r="AA165" s="63"/>
-      <c r="AB165" s="59"/>
-      <c r="AC165" s="60"/>
-      <c r="AD165" s="59"/>
-      <c r="AE165" s="59"/>
-      <c r="AF165" s="59"/>
-      <c r="AG165" s="59"/>
-      <c r="AH165" s="59"/>
-      <c r="AI165" s="59"/>
+    <row r="165" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A165" s="59"/>
+      <c r="B165" s="60"/>
+      <c r="C165" s="60"/>
+      <c r="D165" s="60"/>
+      <c r="E165" s="59"/>
+      <c r="F165" s="61"/>
+      <c r="G165" s="61"/>
+      <c r="H165" s="60"/>
+      <c r="I165" s="60"/>
+      <c r="J165" s="60"/>
+      <c r="K165" s="60"/>
+      <c r="L165" s="60"/>
+      <c r="M165" s="60"/>
+      <c r="N165" s="60"/>
+      <c r="O165" s="62"/>
+      <c r="P165" s="61"/>
+      <c r="Q165" s="60"/>
+      <c r="R165" s="60"/>
+      <c r="S165" s="60"/>
+      <c r="T165" s="63"/>
+      <c r="U165" s="60"/>
+      <c r="V165" s="60"/>
+      <c r="W165" s="60"/>
+      <c r="X165" s="60"/>
+      <c r="Y165" s="60"/>
+      <c r="Z165" s="64"/>
+      <c r="AA165" s="64"/>
+      <c r="AB165" s="60"/>
+      <c r="AC165" s="61"/>
+      <c r="AD165" s="60"/>
+      <c r="AE165" s="60"/>
+      <c r="AF165" s="60"/>
+      <c r="AG165" s="60"/>
+      <c r="AH165" s="60"/>
+      <c r="AI165" s="60"/>
       <c r="AJ165" s="33"/>
     </row>
-    <row r="166" ht="15.6" customHeight="1">
-      <c r="A166" s="64"/>
+    <row r="166" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A166" s="65"/>
       <c r="B166" s="45"/>
       <c r="C166" s="45"/>
       <c r="D166" s="45"/>
-      <c r="E166" s="64"/>
+      <c r="E166" s="65"/>
       <c r="F166" s="44"/>
       <c r="G166" s="44"/>
       <c r="H166" s="45"/>
@@ -9207,12 +9134,12 @@
       <c r="L166" s="45"/>
       <c r="M166" s="45"/>
       <c r="N166" s="45"/>
-      <c r="O166" s="65"/>
+      <c r="O166" s="66"/>
       <c r="P166" s="44"/>
       <c r="Q166" s="45"/>
       <c r="R166" s="45"/>
       <c r="S166" s="45"/>
-      <c r="T166" s="66"/>
+      <c r="T166" s="67"/>
       <c r="U166" s="45"/>
       <c r="V166" s="45"/>
       <c r="W166" s="45"/>
@@ -9230,50 +9157,50 @@
       <c r="AI166" s="45"/>
       <c r="AJ166" s="33"/>
     </row>
-    <row r="167" ht="15.6" customHeight="1">
-      <c r="A167" s="58"/>
-      <c r="B167" s="59"/>
-      <c r="C167" s="59"/>
-      <c r="D167" s="59"/>
-      <c r="E167" s="58"/>
-      <c r="F167" s="60"/>
-      <c r="G167" s="60"/>
-      <c r="H167" s="59"/>
-      <c r="I167" s="59"/>
-      <c r="J167" s="59"/>
-      <c r="K167" s="59"/>
-      <c r="L167" s="59"/>
-      <c r="M167" s="59"/>
-      <c r="N167" s="59"/>
-      <c r="O167" s="61"/>
-      <c r="P167" s="60"/>
-      <c r="Q167" s="59"/>
-      <c r="R167" s="59"/>
-      <c r="S167" s="59"/>
-      <c r="T167" s="62"/>
-      <c r="U167" s="59"/>
-      <c r="V167" s="59"/>
-      <c r="W167" s="59"/>
-      <c r="X167" s="59"/>
-      <c r="Y167" s="59"/>
-      <c r="Z167" s="63"/>
-      <c r="AA167" s="63"/>
-      <c r="AB167" s="59"/>
-      <c r="AC167" s="60"/>
-      <c r="AD167" s="59"/>
-      <c r="AE167" s="59"/>
-      <c r="AF167" s="59"/>
-      <c r="AG167" s="59"/>
-      <c r="AH167" s="59"/>
-      <c r="AI167" s="59"/>
+    <row r="167" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A167" s="59"/>
+      <c r="B167" s="60"/>
+      <c r="C167" s="60"/>
+      <c r="D167" s="60"/>
+      <c r="E167" s="59"/>
+      <c r="F167" s="61"/>
+      <c r="G167" s="61"/>
+      <c r="H167" s="60"/>
+      <c r="I167" s="60"/>
+      <c r="J167" s="60"/>
+      <c r="K167" s="60"/>
+      <c r="L167" s="60"/>
+      <c r="M167" s="60"/>
+      <c r="N167" s="60"/>
+      <c r="O167" s="62"/>
+      <c r="P167" s="61"/>
+      <c r="Q167" s="60"/>
+      <c r="R167" s="60"/>
+      <c r="S167" s="60"/>
+      <c r="T167" s="63"/>
+      <c r="U167" s="60"/>
+      <c r="V167" s="60"/>
+      <c r="W167" s="60"/>
+      <c r="X167" s="60"/>
+      <c r="Y167" s="60"/>
+      <c r="Z167" s="64"/>
+      <c r="AA167" s="64"/>
+      <c r="AB167" s="60"/>
+      <c r="AC167" s="61"/>
+      <c r="AD167" s="60"/>
+      <c r="AE167" s="60"/>
+      <c r="AF167" s="60"/>
+      <c r="AG167" s="60"/>
+      <c r="AH167" s="60"/>
+      <c r="AI167" s="60"/>
       <c r="AJ167" s="33"/>
     </row>
-    <row r="168" ht="15.6" customHeight="1">
-      <c r="A168" s="64"/>
+    <row r="168" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A168" s="65"/>
       <c r="B168" s="45"/>
       <c r="C168" s="45"/>
       <c r="D168" s="45"/>
-      <c r="E168" s="64"/>
+      <c r="E168" s="65"/>
       <c r="F168" s="44"/>
       <c r="G168" s="44"/>
       <c r="H168" s="45"/>
@@ -9283,12 +9210,12 @@
       <c r="L168" s="45"/>
       <c r="M168" s="45"/>
       <c r="N168" s="45"/>
-      <c r="O168" s="65"/>
+      <c r="O168" s="66"/>
       <c r="P168" s="44"/>
       <c r="Q168" s="45"/>
       <c r="R168" s="45"/>
       <c r="S168" s="45"/>
-      <c r="T168" s="66"/>
+      <c r="T168" s="67"/>
       <c r="U168" s="45"/>
       <c r="V168" s="45"/>
       <c r="W168" s="45"/>
@@ -9306,50 +9233,50 @@
       <c r="AI168" s="45"/>
       <c r="AJ168" s="33"/>
     </row>
-    <row r="169" ht="15.6" customHeight="1">
-      <c r="A169" s="58"/>
-      <c r="B169" s="59"/>
-      <c r="C169" s="59"/>
-      <c r="D169" s="59"/>
-      <c r="E169" s="58"/>
-      <c r="F169" s="60"/>
-      <c r="G169" s="60"/>
-      <c r="H169" s="59"/>
-      <c r="I169" s="59"/>
-      <c r="J169" s="59"/>
-      <c r="K169" s="59"/>
-      <c r="L169" s="59"/>
-      <c r="M169" s="59"/>
-      <c r="N169" s="59"/>
-      <c r="O169" s="61"/>
-      <c r="P169" s="60"/>
-      <c r="Q169" s="59"/>
-      <c r="R169" s="59"/>
-      <c r="S169" s="59"/>
-      <c r="T169" s="62"/>
-      <c r="U169" s="59"/>
-      <c r="V169" s="59"/>
-      <c r="W169" s="59"/>
-      <c r="X169" s="59"/>
-      <c r="Y169" s="59"/>
-      <c r="Z169" s="63"/>
-      <c r="AA169" s="63"/>
-      <c r="AB169" s="59"/>
-      <c r="AC169" s="60"/>
-      <c r="AD169" s="59"/>
-      <c r="AE169" s="59"/>
-      <c r="AF169" s="59"/>
-      <c r="AG169" s="59"/>
-      <c r="AH169" s="59"/>
-      <c r="AI169" s="59"/>
+    <row r="169" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A169" s="59"/>
+      <c r="B169" s="60"/>
+      <c r="C169" s="60"/>
+      <c r="D169" s="60"/>
+      <c r="E169" s="59"/>
+      <c r="F169" s="61"/>
+      <c r="G169" s="61"/>
+      <c r="H169" s="60"/>
+      <c r="I169" s="60"/>
+      <c r="J169" s="60"/>
+      <c r="K169" s="60"/>
+      <c r="L169" s="60"/>
+      <c r="M169" s="60"/>
+      <c r="N169" s="60"/>
+      <c r="O169" s="62"/>
+      <c r="P169" s="61"/>
+      <c r="Q169" s="60"/>
+      <c r="R169" s="60"/>
+      <c r="S169" s="60"/>
+      <c r="T169" s="63"/>
+      <c r="U169" s="60"/>
+      <c r="V169" s="60"/>
+      <c r="W169" s="60"/>
+      <c r="X169" s="60"/>
+      <c r="Y169" s="60"/>
+      <c r="Z169" s="64"/>
+      <c r="AA169" s="64"/>
+      <c r="AB169" s="60"/>
+      <c r="AC169" s="61"/>
+      <c r="AD169" s="60"/>
+      <c r="AE169" s="60"/>
+      <c r="AF169" s="60"/>
+      <c r="AG169" s="60"/>
+      <c r="AH169" s="60"/>
+      <c r="AI169" s="60"/>
       <c r="AJ169" s="33"/>
     </row>
-    <row r="170" ht="15.6" customHeight="1">
-      <c r="A170" s="64"/>
+    <row r="170" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A170" s="65"/>
       <c r="B170" s="45"/>
       <c r="C170" s="45"/>
       <c r="D170" s="45"/>
-      <c r="E170" s="64"/>
+      <c r="E170" s="65"/>
       <c r="F170" s="44"/>
       <c r="G170" s="44"/>
       <c r="H170" s="45"/>
@@ -9359,12 +9286,12 @@
       <c r="L170" s="45"/>
       <c r="M170" s="45"/>
       <c r="N170" s="45"/>
-      <c r="O170" s="65"/>
+      <c r="O170" s="66"/>
       <c r="P170" s="44"/>
       <c r="Q170" s="45"/>
       <c r="R170" s="45"/>
       <c r="S170" s="45"/>
-      <c r="T170" s="66"/>
+      <c r="T170" s="67"/>
       <c r="U170" s="45"/>
       <c r="V170" s="45"/>
       <c r="W170" s="45"/>
@@ -9382,50 +9309,50 @@
       <c r="AI170" s="45"/>
       <c r="AJ170" s="33"/>
     </row>
-    <row r="171" ht="15.6" customHeight="1">
-      <c r="A171" s="58"/>
-      <c r="B171" s="59"/>
-      <c r="C171" s="59"/>
-      <c r="D171" s="59"/>
-      <c r="E171" s="58"/>
-      <c r="F171" s="60"/>
-      <c r="G171" s="60"/>
-      <c r="H171" s="59"/>
-      <c r="I171" s="59"/>
-      <c r="J171" s="59"/>
-      <c r="K171" s="59"/>
-      <c r="L171" s="59"/>
-      <c r="M171" s="59"/>
-      <c r="N171" s="59"/>
-      <c r="O171" s="61"/>
-      <c r="P171" s="60"/>
-      <c r="Q171" s="59"/>
-      <c r="R171" s="59"/>
-      <c r="S171" s="59"/>
-      <c r="T171" s="62"/>
-      <c r="U171" s="59"/>
-      <c r="V171" s="59"/>
-      <c r="W171" s="59"/>
-      <c r="X171" s="59"/>
-      <c r="Y171" s="59"/>
-      <c r="Z171" s="63"/>
-      <c r="AA171" s="63"/>
-      <c r="AB171" s="59"/>
-      <c r="AC171" s="60"/>
-      <c r="AD171" s="59"/>
-      <c r="AE171" s="59"/>
-      <c r="AF171" s="59"/>
-      <c r="AG171" s="59"/>
-      <c r="AH171" s="59"/>
-      <c r="AI171" s="59"/>
+    <row r="171" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A171" s="59"/>
+      <c r="B171" s="60"/>
+      <c r="C171" s="60"/>
+      <c r="D171" s="60"/>
+      <c r="E171" s="59"/>
+      <c r="F171" s="61"/>
+      <c r="G171" s="61"/>
+      <c r="H171" s="60"/>
+      <c r="I171" s="60"/>
+      <c r="J171" s="60"/>
+      <c r="K171" s="60"/>
+      <c r="L171" s="60"/>
+      <c r="M171" s="60"/>
+      <c r="N171" s="60"/>
+      <c r="O171" s="62"/>
+      <c r="P171" s="61"/>
+      <c r="Q171" s="60"/>
+      <c r="R171" s="60"/>
+      <c r="S171" s="60"/>
+      <c r="T171" s="63"/>
+      <c r="U171" s="60"/>
+      <c r="V171" s="60"/>
+      <c r="W171" s="60"/>
+      <c r="X171" s="60"/>
+      <c r="Y171" s="60"/>
+      <c r="Z171" s="64"/>
+      <c r="AA171" s="64"/>
+      <c r="AB171" s="60"/>
+      <c r="AC171" s="61"/>
+      <c r="AD171" s="60"/>
+      <c r="AE171" s="60"/>
+      <c r="AF171" s="60"/>
+      <c r="AG171" s="60"/>
+      <c r="AH171" s="60"/>
+      <c r="AI171" s="60"/>
       <c r="AJ171" s="33"/>
     </row>
-    <row r="172" ht="15.6" customHeight="1">
-      <c r="A172" s="64"/>
+    <row r="172" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A172" s="65"/>
       <c r="B172" s="45"/>
       <c r="C172" s="45"/>
       <c r="D172" s="45"/>
-      <c r="E172" s="64"/>
+      <c r="E172" s="65"/>
       <c r="F172" s="44"/>
       <c r="G172" s="44"/>
       <c r="H172" s="45"/>
@@ -9435,12 +9362,12 @@
       <c r="L172" s="45"/>
       <c r="M172" s="45"/>
       <c r="N172" s="45"/>
-      <c r="O172" s="65"/>
+      <c r="O172" s="66"/>
       <c r="P172" s="44"/>
       <c r="Q172" s="45"/>
       <c r="R172" s="45"/>
       <c r="S172" s="45"/>
-      <c r="T172" s="66"/>
+      <c r="T172" s="67"/>
       <c r="U172" s="45"/>
       <c r="V172" s="45"/>
       <c r="W172" s="45"/>
@@ -9458,50 +9385,50 @@
       <c r="AI172" s="45"/>
       <c r="AJ172" s="33"/>
     </row>
-    <row r="173" ht="15.6" customHeight="1">
-      <c r="A173" s="58"/>
-      <c r="B173" s="59"/>
-      <c r="C173" s="59"/>
-      <c r="D173" s="59"/>
-      <c r="E173" s="58"/>
-      <c r="F173" s="60"/>
-      <c r="G173" s="60"/>
-      <c r="H173" s="59"/>
-      <c r="I173" s="59"/>
-      <c r="J173" s="59"/>
-      <c r="K173" s="59"/>
-      <c r="L173" s="59"/>
-      <c r="M173" s="59"/>
-      <c r="N173" s="59"/>
-      <c r="O173" s="61"/>
-      <c r="P173" s="60"/>
-      <c r="Q173" s="59"/>
-      <c r="R173" s="59"/>
-      <c r="S173" s="59"/>
-      <c r="T173" s="62"/>
-      <c r="U173" s="59"/>
-      <c r="V173" s="59"/>
-      <c r="W173" s="59"/>
-      <c r="X173" s="59"/>
-      <c r="Y173" s="59"/>
-      <c r="Z173" s="63"/>
-      <c r="AA173" s="63"/>
-      <c r="AB173" s="59"/>
-      <c r="AC173" s="60"/>
-      <c r="AD173" s="59"/>
-      <c r="AE173" s="59"/>
-      <c r="AF173" s="59"/>
-      <c r="AG173" s="59"/>
-      <c r="AH173" s="59"/>
-      <c r="AI173" s="59"/>
+    <row r="173" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A173" s="59"/>
+      <c r="B173" s="60"/>
+      <c r="C173" s="60"/>
+      <c r="D173" s="60"/>
+      <c r="E173" s="59"/>
+      <c r="F173" s="61"/>
+      <c r="G173" s="61"/>
+      <c r="H173" s="60"/>
+      <c r="I173" s="60"/>
+      <c r="J173" s="60"/>
+      <c r="K173" s="60"/>
+      <c r="L173" s="60"/>
+      <c r="M173" s="60"/>
+      <c r="N173" s="60"/>
+      <c r="O173" s="62"/>
+      <c r="P173" s="61"/>
+      <c r="Q173" s="60"/>
+      <c r="R173" s="60"/>
+      <c r="S173" s="60"/>
+      <c r="T173" s="63"/>
+      <c r="U173" s="60"/>
+      <c r="V173" s="60"/>
+      <c r="W173" s="60"/>
+      <c r="X173" s="60"/>
+      <c r="Y173" s="60"/>
+      <c r="Z173" s="64"/>
+      <c r="AA173" s="64"/>
+      <c r="AB173" s="60"/>
+      <c r="AC173" s="61"/>
+      <c r="AD173" s="60"/>
+      <c r="AE173" s="60"/>
+      <c r="AF173" s="60"/>
+      <c r="AG173" s="60"/>
+      <c r="AH173" s="60"/>
+      <c r="AI173" s="60"/>
       <c r="AJ173" s="33"/>
     </row>
-    <row r="174" ht="15.6" customHeight="1">
-      <c r="A174" s="64"/>
+    <row r="174" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A174" s="65"/>
       <c r="B174" s="45"/>
       <c r="C174" s="45"/>
       <c r="D174" s="45"/>
-      <c r="E174" s="64"/>
+      <c r="E174" s="65"/>
       <c r="F174" s="44"/>
       <c r="G174" s="44"/>
       <c r="H174" s="45"/>
@@ -9511,12 +9438,12 @@
       <c r="L174" s="45"/>
       <c r="M174" s="45"/>
       <c r="N174" s="45"/>
-      <c r="O174" s="65"/>
+      <c r="O174" s="66"/>
       <c r="P174" s="44"/>
       <c r="Q174" s="45"/>
       <c r="R174" s="45"/>
       <c r="S174" s="45"/>
-      <c r="T174" s="66"/>
+      <c r="T174" s="67"/>
       <c r="U174" s="45"/>
       <c r="V174" s="45"/>
       <c r="W174" s="45"/>
@@ -9534,50 +9461,50 @@
       <c r="AI174" s="45"/>
       <c r="AJ174" s="33"/>
     </row>
-    <row r="175" ht="15.6" customHeight="1">
-      <c r="A175" s="58"/>
-      <c r="B175" s="59"/>
-      <c r="C175" s="59"/>
-      <c r="D175" s="59"/>
-      <c r="E175" s="58"/>
-      <c r="F175" s="60"/>
-      <c r="G175" s="60"/>
-      <c r="H175" s="59"/>
-      <c r="I175" s="59"/>
-      <c r="J175" s="59"/>
-      <c r="K175" s="59"/>
-      <c r="L175" s="59"/>
-      <c r="M175" s="59"/>
-      <c r="N175" s="59"/>
-      <c r="O175" s="61"/>
-      <c r="P175" s="60"/>
-      <c r="Q175" s="59"/>
-      <c r="R175" s="59"/>
-      <c r="S175" s="59"/>
-      <c r="T175" s="62"/>
-      <c r="U175" s="59"/>
-      <c r="V175" s="59"/>
-      <c r="W175" s="59"/>
-      <c r="X175" s="59"/>
-      <c r="Y175" s="59"/>
-      <c r="Z175" s="63"/>
-      <c r="AA175" s="63"/>
-      <c r="AB175" s="59"/>
-      <c r="AC175" s="60"/>
-      <c r="AD175" s="59"/>
-      <c r="AE175" s="59"/>
-      <c r="AF175" s="59"/>
-      <c r="AG175" s="59"/>
-      <c r="AH175" s="59"/>
-      <c r="AI175" s="59"/>
+    <row r="175" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A175" s="59"/>
+      <c r="B175" s="60"/>
+      <c r="C175" s="60"/>
+      <c r="D175" s="60"/>
+      <c r="E175" s="59"/>
+      <c r="F175" s="61"/>
+      <c r="G175" s="61"/>
+      <c r="H175" s="60"/>
+      <c r="I175" s="60"/>
+      <c r="J175" s="60"/>
+      <c r="K175" s="60"/>
+      <c r="L175" s="60"/>
+      <c r="M175" s="60"/>
+      <c r="N175" s="60"/>
+      <c r="O175" s="62"/>
+      <c r="P175" s="61"/>
+      <c r="Q175" s="60"/>
+      <c r="R175" s="60"/>
+      <c r="S175" s="60"/>
+      <c r="T175" s="63"/>
+      <c r="U175" s="60"/>
+      <c r="V175" s="60"/>
+      <c r="W175" s="60"/>
+      <c r="X175" s="60"/>
+      <c r="Y175" s="60"/>
+      <c r="Z175" s="64"/>
+      <c r="AA175" s="64"/>
+      <c r="AB175" s="60"/>
+      <c r="AC175" s="61"/>
+      <c r="AD175" s="60"/>
+      <c r="AE175" s="60"/>
+      <c r="AF175" s="60"/>
+      <c r="AG175" s="60"/>
+      <c r="AH175" s="60"/>
+      <c r="AI175" s="60"/>
       <c r="AJ175" s="33"/>
     </row>
-    <row r="176" ht="15.6" customHeight="1">
-      <c r="A176" s="64"/>
+    <row r="176" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A176" s="65"/>
       <c r="B176" s="45"/>
       <c r="C176" s="45"/>
       <c r="D176" s="45"/>
-      <c r="E176" s="64"/>
+      <c r="E176" s="65"/>
       <c r="F176" s="44"/>
       <c r="G176" s="44"/>
       <c r="H176" s="45"/>
@@ -9587,12 +9514,12 @@
       <c r="L176" s="45"/>
       <c r="M176" s="45"/>
       <c r="N176" s="45"/>
-      <c r="O176" s="65"/>
+      <c r="O176" s="66"/>
       <c r="P176" s="44"/>
       <c r="Q176" s="45"/>
       <c r="R176" s="45"/>
       <c r="S176" s="45"/>
-      <c r="T176" s="66"/>
+      <c r="T176" s="67"/>
       <c r="U176" s="45"/>
       <c r="V176" s="45"/>
       <c r="W176" s="45"/>
@@ -9610,50 +9537,50 @@
       <c r="AI176" s="45"/>
       <c r="AJ176" s="33"/>
     </row>
-    <row r="177" ht="15.6" customHeight="1">
-      <c r="A177" s="58"/>
-      <c r="B177" s="59"/>
-      <c r="C177" s="59"/>
-      <c r="D177" s="59"/>
-      <c r="E177" s="58"/>
-      <c r="F177" s="60"/>
-      <c r="G177" s="60"/>
-      <c r="H177" s="59"/>
-      <c r="I177" s="59"/>
-      <c r="J177" s="59"/>
-      <c r="K177" s="59"/>
-      <c r="L177" s="59"/>
-      <c r="M177" s="59"/>
-      <c r="N177" s="59"/>
-      <c r="O177" s="61"/>
-      <c r="P177" s="60"/>
-      <c r="Q177" s="59"/>
-      <c r="R177" s="59"/>
-      <c r="S177" s="59"/>
-      <c r="T177" s="62"/>
-      <c r="U177" s="59"/>
-      <c r="V177" s="59"/>
-      <c r="W177" s="59"/>
-      <c r="X177" s="59"/>
-      <c r="Y177" s="59"/>
-      <c r="Z177" s="63"/>
-      <c r="AA177" s="63"/>
-      <c r="AB177" s="59"/>
-      <c r="AC177" s="60"/>
-      <c r="AD177" s="59"/>
-      <c r="AE177" s="59"/>
-      <c r="AF177" s="59"/>
-      <c r="AG177" s="59"/>
-      <c r="AH177" s="59"/>
-      <c r="AI177" s="59"/>
+    <row r="177" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A177" s="59"/>
+      <c r="B177" s="60"/>
+      <c r="C177" s="60"/>
+      <c r="D177" s="60"/>
+      <c r="E177" s="59"/>
+      <c r="F177" s="61"/>
+      <c r="G177" s="61"/>
+      <c r="H177" s="60"/>
+      <c r="I177" s="60"/>
+      <c r="J177" s="60"/>
+      <c r="K177" s="60"/>
+      <c r="L177" s="60"/>
+      <c r="M177" s="60"/>
+      <c r="N177" s="60"/>
+      <c r="O177" s="62"/>
+      <c r="P177" s="61"/>
+      <c r="Q177" s="60"/>
+      <c r="R177" s="60"/>
+      <c r="S177" s="60"/>
+      <c r="T177" s="63"/>
+      <c r="U177" s="60"/>
+      <c r="V177" s="60"/>
+      <c r="W177" s="60"/>
+      <c r="X177" s="60"/>
+      <c r="Y177" s="60"/>
+      <c r="Z177" s="64"/>
+      <c r="AA177" s="64"/>
+      <c r="AB177" s="60"/>
+      <c r="AC177" s="61"/>
+      <c r="AD177" s="60"/>
+      <c r="AE177" s="60"/>
+      <c r="AF177" s="60"/>
+      <c r="AG177" s="60"/>
+      <c r="AH177" s="60"/>
+      <c r="AI177" s="60"/>
       <c r="AJ177" s="33"/>
     </row>
-    <row r="178" ht="15.6" customHeight="1">
-      <c r="A178" s="64"/>
+    <row r="178" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A178" s="65"/>
       <c r="B178" s="45"/>
       <c r="C178" s="45"/>
       <c r="D178" s="45"/>
-      <c r="E178" s="64"/>
+      <c r="E178" s="65"/>
       <c r="F178" s="44"/>
       <c r="G178" s="44"/>
       <c r="H178" s="45"/>
@@ -9663,12 +9590,12 @@
       <c r="L178" s="45"/>
       <c r="M178" s="45"/>
       <c r="N178" s="45"/>
-      <c r="O178" s="65"/>
+      <c r="O178" s="66"/>
       <c r="P178" s="44"/>
       <c r="Q178" s="45"/>
       <c r="R178" s="45"/>
       <c r="S178" s="45"/>
-      <c r="T178" s="66"/>
+      <c r="T178" s="67"/>
       <c r="U178" s="45"/>
       <c r="V178" s="45"/>
       <c r="W178" s="45"/>
@@ -9686,50 +9613,50 @@
       <c r="AI178" s="45"/>
       <c r="AJ178" s="33"/>
     </row>
-    <row r="179" ht="15.6" customHeight="1">
-      <c r="A179" s="58"/>
-      <c r="B179" s="59"/>
-      <c r="C179" s="59"/>
-      <c r="D179" s="59"/>
-      <c r="E179" s="58"/>
-      <c r="F179" s="60"/>
-      <c r="G179" s="60"/>
-      <c r="H179" s="59"/>
-      <c r="I179" s="59"/>
-      <c r="J179" s="59"/>
-      <c r="K179" s="59"/>
-      <c r="L179" s="59"/>
-      <c r="M179" s="59"/>
-      <c r="N179" s="59"/>
-      <c r="O179" s="61"/>
-      <c r="P179" s="60"/>
-      <c r="Q179" s="59"/>
-      <c r="R179" s="59"/>
-      <c r="S179" s="59"/>
-      <c r="T179" s="62"/>
-      <c r="U179" s="59"/>
-      <c r="V179" s="59"/>
-      <c r="W179" s="59"/>
-      <c r="X179" s="59"/>
-      <c r="Y179" s="59"/>
-      <c r="Z179" s="63"/>
-      <c r="AA179" s="63"/>
-      <c r="AB179" s="59"/>
-      <c r="AC179" s="60"/>
-      <c r="AD179" s="59"/>
-      <c r="AE179" s="59"/>
-      <c r="AF179" s="59"/>
-      <c r="AG179" s="59"/>
-      <c r="AH179" s="59"/>
-      <c r="AI179" s="59"/>
+    <row r="179" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A179" s="59"/>
+      <c r="B179" s="60"/>
+      <c r="C179" s="60"/>
+      <c r="D179" s="60"/>
+      <c r="E179" s="59"/>
+      <c r="F179" s="61"/>
+      <c r="G179" s="61"/>
+      <c r="H179" s="60"/>
+      <c r="I179" s="60"/>
+      <c r="J179" s="60"/>
+      <c r="K179" s="60"/>
+      <c r="L179" s="60"/>
+      <c r="M179" s="60"/>
+      <c r="N179" s="60"/>
+      <c r="O179" s="62"/>
+      <c r="P179" s="61"/>
+      <c r="Q179" s="60"/>
+      <c r="R179" s="60"/>
+      <c r="S179" s="60"/>
+      <c r="T179" s="63"/>
+      <c r="U179" s="60"/>
+      <c r="V179" s="60"/>
+      <c r="W179" s="60"/>
+      <c r="X179" s="60"/>
+      <c r="Y179" s="60"/>
+      <c r="Z179" s="64"/>
+      <c r="AA179" s="64"/>
+      <c r="AB179" s="60"/>
+      <c r="AC179" s="61"/>
+      <c r="AD179" s="60"/>
+      <c r="AE179" s="60"/>
+      <c r="AF179" s="60"/>
+      <c r="AG179" s="60"/>
+      <c r="AH179" s="60"/>
+      <c r="AI179" s="60"/>
       <c r="AJ179" s="33"/>
     </row>
-    <row r="180" ht="15.6" customHeight="1">
-      <c r="A180" s="64"/>
+    <row r="180" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A180" s="65"/>
       <c r="B180" s="45"/>
       <c r="C180" s="45"/>
       <c r="D180" s="45"/>
-      <c r="E180" s="64"/>
+      <c r="E180" s="65"/>
       <c r="F180" s="44"/>
       <c r="G180" s="44"/>
       <c r="H180" s="45"/>
@@ -9739,12 +9666,12 @@
       <c r="L180" s="45"/>
       <c r="M180" s="45"/>
       <c r="N180" s="45"/>
-      <c r="O180" s="65"/>
+      <c r="O180" s="66"/>
       <c r="P180" s="44"/>
       <c r="Q180" s="45"/>
       <c r="R180" s="45"/>
       <c r="S180" s="45"/>
-      <c r="T180" s="66"/>
+      <c r="T180" s="67"/>
       <c r="U180" s="45"/>
       <c r="V180" s="45"/>
       <c r="W180" s="45"/>
@@ -9762,50 +9689,50 @@
       <c r="AI180" s="45"/>
       <c r="AJ180" s="33"/>
     </row>
-    <row r="181" ht="15.6" customHeight="1">
-      <c r="A181" s="58"/>
-      <c r="B181" s="59"/>
-      <c r="C181" s="59"/>
-      <c r="D181" s="59"/>
-      <c r="E181" s="58"/>
-      <c r="F181" s="60"/>
-      <c r="G181" s="60"/>
-      <c r="H181" s="59"/>
-      <c r="I181" s="59"/>
-      <c r="J181" s="59"/>
-      <c r="K181" s="59"/>
-      <c r="L181" s="59"/>
-      <c r="M181" s="59"/>
-      <c r="N181" s="59"/>
-      <c r="O181" s="61"/>
-      <c r="P181" s="60"/>
-      <c r="Q181" s="59"/>
-      <c r="R181" s="59"/>
-      <c r="S181" s="59"/>
-      <c r="T181" s="62"/>
-      <c r="U181" s="59"/>
-      <c r="V181" s="59"/>
-      <c r="W181" s="59"/>
-      <c r="X181" s="59"/>
-      <c r="Y181" s="59"/>
-      <c r="Z181" s="63"/>
-      <c r="AA181" s="63"/>
-      <c r="AB181" s="59"/>
-      <c r="AC181" s="60"/>
-      <c r="AD181" s="59"/>
-      <c r="AE181" s="59"/>
-      <c r="AF181" s="59"/>
-      <c r="AG181" s="59"/>
-      <c r="AH181" s="59"/>
-      <c r="AI181" s="59"/>
+    <row r="181" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A181" s="59"/>
+      <c r="B181" s="60"/>
+      <c r="C181" s="60"/>
+      <c r="D181" s="60"/>
+      <c r="E181" s="59"/>
+      <c r="F181" s="61"/>
+      <c r="G181" s="61"/>
+      <c r="H181" s="60"/>
+      <c r="I181" s="60"/>
+      <c r="J181" s="60"/>
+      <c r="K181" s="60"/>
+      <c r="L181" s="60"/>
+      <c r="M181" s="60"/>
+      <c r="N181" s="60"/>
+      <c r="O181" s="62"/>
+      <c r="P181" s="61"/>
+      <c r="Q181" s="60"/>
+      <c r="R181" s="60"/>
+      <c r="S181" s="60"/>
+      <c r="T181" s="63"/>
+      <c r="U181" s="60"/>
+      <c r="V181" s="60"/>
+      <c r="W181" s="60"/>
+      <c r="X181" s="60"/>
+      <c r="Y181" s="60"/>
+      <c r="Z181" s="64"/>
+      <c r="AA181" s="64"/>
+      <c r="AB181" s="60"/>
+      <c r="AC181" s="61"/>
+      <c r="AD181" s="60"/>
+      <c r="AE181" s="60"/>
+      <c r="AF181" s="60"/>
+      <c r="AG181" s="60"/>
+      <c r="AH181" s="60"/>
+      <c r="AI181" s="60"/>
       <c r="AJ181" s="33"/>
     </row>
-    <row r="182" ht="15.6" customHeight="1">
-      <c r="A182" s="64"/>
+    <row r="182" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A182" s="65"/>
       <c r="B182" s="45"/>
       <c r="C182" s="45"/>
       <c r="D182" s="45"/>
-      <c r="E182" s="64"/>
+      <c r="E182" s="65"/>
       <c r="F182" s="44"/>
       <c r="G182" s="44"/>
       <c r="H182" s="45"/>
@@ -9815,12 +9742,12 @@
       <c r="L182" s="45"/>
       <c r="M182" s="45"/>
       <c r="N182" s="45"/>
-      <c r="O182" s="65"/>
+      <c r="O182" s="66"/>
       <c r="P182" s="44"/>
       <c r="Q182" s="45"/>
       <c r="R182" s="45"/>
       <c r="S182" s="45"/>
-      <c r="T182" s="66"/>
+      <c r="T182" s="67"/>
       <c r="U182" s="45"/>
       <c r="V182" s="45"/>
       <c r="W182" s="45"/>
@@ -9838,50 +9765,50 @@
       <c r="AI182" s="45"/>
       <c r="AJ182" s="33"/>
     </row>
-    <row r="183" ht="15.6" customHeight="1">
-      <c r="A183" s="58"/>
-      <c r="B183" s="59"/>
-      <c r="C183" s="59"/>
-      <c r="D183" s="59"/>
-      <c r="E183" s="58"/>
-      <c r="F183" s="60"/>
-      <c r="G183" s="60"/>
-      <c r="H183" s="59"/>
-      <c r="I183" s="59"/>
-      <c r="J183" s="59"/>
-      <c r="K183" s="59"/>
-      <c r="L183" s="59"/>
-      <c r="M183" s="59"/>
-      <c r="N183" s="59"/>
-      <c r="O183" s="61"/>
-      <c r="P183" s="60"/>
-      <c r="Q183" s="59"/>
-      <c r="R183" s="59"/>
-      <c r="S183" s="59"/>
-      <c r="T183" s="62"/>
-      <c r="U183" s="59"/>
-      <c r="V183" s="59"/>
-      <c r="W183" s="59"/>
-      <c r="X183" s="59"/>
-      <c r="Y183" s="59"/>
-      <c r="Z183" s="63"/>
-      <c r="AA183" s="63"/>
-      <c r="AB183" s="59"/>
-      <c r="AC183" s="60"/>
-      <c r="AD183" s="59"/>
-      <c r="AE183" s="59"/>
-      <c r="AF183" s="59"/>
-      <c r="AG183" s="59"/>
-      <c r="AH183" s="59"/>
-      <c r="AI183" s="59"/>
+    <row r="183" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A183" s="59"/>
+      <c r="B183" s="60"/>
+      <c r="C183" s="60"/>
+      <c r="D183" s="60"/>
+      <c r="E183" s="59"/>
+      <c r="F183" s="61"/>
+      <c r="G183" s="61"/>
+      <c r="H183" s="60"/>
+      <c r="I183" s="60"/>
+      <c r="J183" s="60"/>
+      <c r="K183" s="60"/>
+      <c r="L183" s="60"/>
+      <c r="M183" s="60"/>
+      <c r="N183" s="60"/>
+      <c r="O183" s="62"/>
+      <c r="P183" s="61"/>
+      <c r="Q183" s="60"/>
+      <c r="R183" s="60"/>
+      <c r="S183" s="60"/>
+      <c r="T183" s="63"/>
+      <c r="U183" s="60"/>
+      <c r="V183" s="60"/>
+      <c r="W183" s="60"/>
+      <c r="X183" s="60"/>
+      <c r="Y183" s="60"/>
+      <c r="Z183" s="64"/>
+      <c r="AA183" s="64"/>
+      <c r="AB183" s="60"/>
+      <c r="AC183" s="61"/>
+      <c r="AD183" s="60"/>
+      <c r="AE183" s="60"/>
+      <c r="AF183" s="60"/>
+      <c r="AG183" s="60"/>
+      <c r="AH183" s="60"/>
+      <c r="AI183" s="60"/>
       <c r="AJ183" s="33"/>
     </row>
-    <row r="184" ht="15.6" customHeight="1">
-      <c r="A184" s="64"/>
+    <row r="184" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A184" s="65"/>
       <c r="B184" s="45"/>
       <c r="C184" s="45"/>
       <c r="D184" s="45"/>
-      <c r="E184" s="64"/>
+      <c r="E184" s="65"/>
       <c r="F184" s="44"/>
       <c r="G184" s="44"/>
       <c r="H184" s="45"/>
@@ -9891,12 +9818,12 @@
       <c r="L184" s="45"/>
       <c r="M184" s="45"/>
       <c r="N184" s="45"/>
-      <c r="O184" s="65"/>
+      <c r="O184" s="66"/>
       <c r="P184" s="44"/>
       <c r="Q184" s="45"/>
       <c r="R184" s="45"/>
       <c r="S184" s="45"/>
-      <c r="T184" s="66"/>
+      <c r="T184" s="67"/>
       <c r="U184" s="45"/>
       <c r="V184" s="45"/>
       <c r="W184" s="45"/>
@@ -9914,50 +9841,50 @@
       <c r="AI184" s="45"/>
       <c r="AJ184" s="33"/>
     </row>
-    <row r="185" ht="15.6" customHeight="1">
-      <c r="A185" s="58"/>
-      <c r="B185" s="59"/>
-      <c r="C185" s="59"/>
-      <c r="D185" s="59"/>
-      <c r="E185" s="58"/>
-      <c r="F185" s="60"/>
-      <c r="G185" s="60"/>
-      <c r="H185" s="59"/>
-      <c r="I185" s="59"/>
-      <c r="J185" s="59"/>
-      <c r="K185" s="59"/>
-      <c r="L185" s="59"/>
-      <c r="M185" s="59"/>
-      <c r="N185" s="59"/>
-      <c r="O185" s="61"/>
-      <c r="P185" s="60"/>
-      <c r="Q185" s="59"/>
-      <c r="R185" s="59"/>
-      <c r="S185" s="59"/>
-      <c r="T185" s="62"/>
-      <c r="U185" s="59"/>
-      <c r="V185" s="59"/>
-      <c r="W185" s="59"/>
-      <c r="X185" s="59"/>
-      <c r="Y185" s="59"/>
-      <c r="Z185" s="63"/>
-      <c r="AA185" s="63"/>
-      <c r="AB185" s="59"/>
-      <c r="AC185" s="60"/>
-      <c r="AD185" s="59"/>
-      <c r="AE185" s="59"/>
-      <c r="AF185" s="59"/>
-      <c r="AG185" s="59"/>
-      <c r="AH185" s="59"/>
-      <c r="AI185" s="59"/>
+    <row r="185" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A185" s="59"/>
+      <c r="B185" s="60"/>
+      <c r="C185" s="60"/>
+      <c r="D185" s="60"/>
+      <c r="E185" s="59"/>
+      <c r="F185" s="61"/>
+      <c r="G185" s="61"/>
+      <c r="H185" s="60"/>
+      <c r="I185" s="60"/>
+      <c r="J185" s="60"/>
+      <c r="K185" s="60"/>
+      <c r="L185" s="60"/>
+      <c r="M185" s="60"/>
+      <c r="N185" s="60"/>
+      <c r="O185" s="62"/>
+      <c r="P185" s="61"/>
+      <c r="Q185" s="60"/>
+      <c r="R185" s="60"/>
+      <c r="S185" s="60"/>
+      <c r="T185" s="63"/>
+      <c r="U185" s="60"/>
+      <c r="V185" s="60"/>
+      <c r="W185" s="60"/>
+      <c r="X185" s="60"/>
+      <c r="Y185" s="60"/>
+      <c r="Z185" s="64"/>
+      <c r="AA185" s="64"/>
+      <c r="AB185" s="60"/>
+      <c r="AC185" s="61"/>
+      <c r="AD185" s="60"/>
+      <c r="AE185" s="60"/>
+      <c r="AF185" s="60"/>
+      <c r="AG185" s="60"/>
+      <c r="AH185" s="60"/>
+      <c r="AI185" s="60"/>
       <c r="AJ185" s="33"/>
     </row>
-    <row r="186" ht="15.6" customHeight="1">
-      <c r="A186" s="64"/>
+    <row r="186" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A186" s="65"/>
       <c r="B186" s="45"/>
       <c r="C186" s="45"/>
       <c r="D186" s="45"/>
-      <c r="E186" s="64"/>
+      <c r="E186" s="65"/>
       <c r="F186" s="44"/>
       <c r="G186" s="44"/>
       <c r="H186" s="45"/>
@@ -9967,12 +9894,12 @@
       <c r="L186" s="45"/>
       <c r="M186" s="45"/>
       <c r="N186" s="45"/>
-      <c r="O186" s="65"/>
+      <c r="O186" s="66"/>
       <c r="P186" s="44"/>
       <c r="Q186" s="45"/>
       <c r="R186" s="45"/>
       <c r="S186" s="45"/>
-      <c r="T186" s="66"/>
+      <c r="T186" s="67"/>
       <c r="U186" s="45"/>
       <c r="V186" s="45"/>
       <c r="W186" s="45"/>
@@ -9990,50 +9917,50 @@
       <c r="AI186" s="45"/>
       <c r="AJ186" s="33"/>
     </row>
-    <row r="187" ht="15.6" customHeight="1">
-      <c r="A187" s="58"/>
-      <c r="B187" s="59"/>
-      <c r="C187" s="59"/>
-      <c r="D187" s="59"/>
-      <c r="E187" s="58"/>
-      <c r="F187" s="60"/>
-      <c r="G187" s="60"/>
-      <c r="H187" s="59"/>
-      <c r="I187" s="59"/>
-      <c r="J187" s="59"/>
-      <c r="K187" s="59"/>
-      <c r="L187" s="59"/>
-      <c r="M187" s="59"/>
-      <c r="N187" s="59"/>
-      <c r="O187" s="61"/>
-      <c r="P187" s="60"/>
-      <c r="Q187" s="59"/>
-      <c r="R187" s="59"/>
-      <c r="S187" s="59"/>
-      <c r="T187" s="62"/>
-      <c r="U187" s="59"/>
-      <c r="V187" s="59"/>
-      <c r="W187" s="59"/>
-      <c r="X187" s="59"/>
-      <c r="Y187" s="59"/>
-      <c r="Z187" s="63"/>
-      <c r="AA187" s="63"/>
-      <c r="AB187" s="59"/>
-      <c r="AC187" s="60"/>
-      <c r="AD187" s="59"/>
-      <c r="AE187" s="59"/>
-      <c r="AF187" s="59"/>
-      <c r="AG187" s="59"/>
-      <c r="AH187" s="59"/>
-      <c r="AI187" s="59"/>
+    <row r="187" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A187" s="59"/>
+      <c r="B187" s="60"/>
+      <c r="C187" s="60"/>
+      <c r="D187" s="60"/>
+      <c r="E187" s="59"/>
+      <c r="F187" s="61"/>
+      <c r="G187" s="61"/>
+      <c r="H187" s="60"/>
+      <c r="I187" s="60"/>
+      <c r="J187" s="60"/>
+      <c r="K187" s="60"/>
+      <c r="L187" s="60"/>
+      <c r="M187" s="60"/>
+      <c r="N187" s="60"/>
+      <c r="O187" s="62"/>
+      <c r="P187" s="61"/>
+      <c r="Q187" s="60"/>
+      <c r="R187" s="60"/>
+      <c r="S187" s="60"/>
+      <c r="T187" s="63"/>
+      <c r="U187" s="60"/>
+      <c r="V187" s="60"/>
+      <c r="W187" s="60"/>
+      <c r="X187" s="60"/>
+      <c r="Y187" s="60"/>
+      <c r="Z187" s="64"/>
+      <c r="AA187" s="64"/>
+      <c r="AB187" s="60"/>
+      <c r="AC187" s="61"/>
+      <c r="AD187" s="60"/>
+      <c r="AE187" s="60"/>
+      <c r="AF187" s="60"/>
+      <c r="AG187" s="60"/>
+      <c r="AH187" s="60"/>
+      <c r="AI187" s="60"/>
       <c r="AJ187" s="33"/>
     </row>
-    <row r="188" ht="15.6" customHeight="1">
-      <c r="A188" s="64"/>
+    <row r="188" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A188" s="65"/>
       <c r="B188" s="45"/>
       <c r="C188" s="45"/>
       <c r="D188" s="45"/>
-      <c r="E188" s="64"/>
+      <c r="E188" s="65"/>
       <c r="F188" s="44"/>
       <c r="G188" s="44"/>
       <c r="H188" s="45"/>
@@ -10043,12 +9970,12 @@
       <c r="L188" s="45"/>
       <c r="M188" s="45"/>
       <c r="N188" s="45"/>
-      <c r="O188" s="65"/>
+      <c r="O188" s="66"/>
       <c r="P188" s="44"/>
       <c r="Q188" s="45"/>
       <c r="R188" s="45"/>
       <c r="S188" s="45"/>
-      <c r="T188" s="66"/>
+      <c r="T188" s="67"/>
       <c r="U188" s="45"/>
       <c r="V188" s="45"/>
       <c r="W188" s="45"/>
@@ -10066,50 +9993,50 @@
       <c r="AI188" s="45"/>
       <c r="AJ188" s="33"/>
     </row>
-    <row r="189" ht="15.6" customHeight="1">
-      <c r="A189" s="58"/>
-      <c r="B189" s="59"/>
-      <c r="C189" s="59"/>
-      <c r="D189" s="59"/>
-      <c r="E189" s="58"/>
-      <c r="F189" s="60"/>
-      <c r="G189" s="60"/>
-      <c r="H189" s="59"/>
-      <c r="I189" s="59"/>
-      <c r="J189" s="59"/>
-      <c r="K189" s="59"/>
-      <c r="L189" s="59"/>
-      <c r="M189" s="59"/>
-      <c r="N189" s="59"/>
-      <c r="O189" s="61"/>
-      <c r="P189" s="60"/>
-      <c r="Q189" s="59"/>
-      <c r="R189" s="59"/>
-      <c r="S189" s="59"/>
-      <c r="T189" s="62"/>
-      <c r="U189" s="59"/>
-      <c r="V189" s="59"/>
-      <c r="W189" s="59"/>
-      <c r="X189" s="59"/>
-      <c r="Y189" s="59"/>
-      <c r="Z189" s="63"/>
-      <c r="AA189" s="63"/>
-      <c r="AB189" s="59"/>
-      <c r="AC189" s="60"/>
-      <c r="AD189" s="59"/>
-      <c r="AE189" s="59"/>
-      <c r="AF189" s="59"/>
-      <c r="AG189" s="59"/>
-      <c r="AH189" s="59"/>
-      <c r="AI189" s="59"/>
+    <row r="189" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A189" s="59"/>
+      <c r="B189" s="60"/>
+      <c r="C189" s="60"/>
+      <c r="D189" s="60"/>
+      <c r="E189" s="59"/>
+      <c r="F189" s="61"/>
+      <c r="G189" s="61"/>
+      <c r="H189" s="60"/>
+      <c r="I189" s="60"/>
+      <c r="J189" s="60"/>
+      <c r="K189" s="60"/>
+      <c r="L189" s="60"/>
+      <c r="M189" s="60"/>
+      <c r="N189" s="60"/>
+      <c r="O189" s="62"/>
+      <c r="P189" s="61"/>
+      <c r="Q189" s="60"/>
+      <c r="R189" s="60"/>
+      <c r="S189" s="60"/>
+      <c r="T189" s="63"/>
+      <c r="U189" s="60"/>
+      <c r="V189" s="60"/>
+      <c r="W189" s="60"/>
+      <c r="X189" s="60"/>
+      <c r="Y189" s="60"/>
+      <c r="Z189" s="64"/>
+      <c r="AA189" s="64"/>
+      <c r="AB189" s="60"/>
+      <c r="AC189" s="61"/>
+      <c r="AD189" s="60"/>
+      <c r="AE189" s="60"/>
+      <c r="AF189" s="60"/>
+      <c r="AG189" s="60"/>
+      <c r="AH189" s="60"/>
+      <c r="AI189" s="60"/>
       <c r="AJ189" s="33"/>
     </row>
-    <row r="190" ht="15.6" customHeight="1">
-      <c r="A190" s="64"/>
+    <row r="190" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A190" s="65"/>
       <c r="B190" s="45"/>
       <c r="C190" s="45"/>
       <c r="D190" s="45"/>
-      <c r="E190" s="64"/>
+      <c r="E190" s="65"/>
       <c r="F190" s="44"/>
       <c r="G190" s="44"/>
       <c r="H190" s="45"/>
@@ -10119,12 +10046,12 @@
       <c r="L190" s="45"/>
       <c r="M190" s="45"/>
       <c r="N190" s="45"/>
-      <c r="O190" s="65"/>
+      <c r="O190" s="66"/>
       <c r="P190" s="44"/>
       <c r="Q190" s="45"/>
       <c r="R190" s="45"/>
       <c r="S190" s="45"/>
-      <c r="T190" s="66"/>
+      <c r="T190" s="67"/>
       <c r="U190" s="45"/>
       <c r="V190" s="45"/>
       <c r="W190" s="45"/>
@@ -10142,50 +10069,50 @@
       <c r="AI190" s="45"/>
       <c r="AJ190" s="33"/>
     </row>
-    <row r="191" ht="15.6" customHeight="1">
-      <c r="A191" s="58"/>
-      <c r="B191" s="59"/>
-      <c r="C191" s="59"/>
-      <c r="D191" s="59"/>
-      <c r="E191" s="58"/>
-      <c r="F191" s="60"/>
-      <c r="G191" s="60"/>
-      <c r="H191" s="59"/>
-      <c r="I191" s="59"/>
-      <c r="J191" s="59"/>
-      <c r="K191" s="59"/>
-      <c r="L191" s="59"/>
-      <c r="M191" s="59"/>
-      <c r="N191" s="59"/>
-      <c r="O191" s="61"/>
-      <c r="P191" s="60"/>
-      <c r="Q191" s="59"/>
-      <c r="R191" s="59"/>
-      <c r="S191" s="59"/>
-      <c r="T191" s="62"/>
-      <c r="U191" s="59"/>
-      <c r="V191" s="59"/>
-      <c r="W191" s="59"/>
-      <c r="X191" s="59"/>
-      <c r="Y191" s="59"/>
-      <c r="Z191" s="63"/>
-      <c r="AA191" s="63"/>
-      <c r="AB191" s="59"/>
-      <c r="AC191" s="60"/>
-      <c r="AD191" s="59"/>
-      <c r="AE191" s="59"/>
-      <c r="AF191" s="59"/>
-      <c r="AG191" s="59"/>
-      <c r="AH191" s="59"/>
-      <c r="AI191" s="59"/>
+    <row r="191" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A191" s="59"/>
+      <c r="B191" s="60"/>
+      <c r="C191" s="60"/>
+      <c r="D191" s="60"/>
+      <c r="E191" s="59"/>
+      <c r="F191" s="61"/>
+      <c r="G191" s="61"/>
+      <c r="H191" s="60"/>
+      <c r="I191" s="60"/>
+      <c r="J191" s="60"/>
+      <c r="K191" s="60"/>
+      <c r="L191" s="60"/>
+      <c r="M191" s="60"/>
+      <c r="N191" s="60"/>
+      <c r="O191" s="62"/>
+      <c r="P191" s="61"/>
+      <c r="Q191" s="60"/>
+      <c r="R191" s="60"/>
+      <c r="S191" s="60"/>
+      <c r="T191" s="63"/>
+      <c r="U191" s="60"/>
+      <c r="V191" s="60"/>
+      <c r="W191" s="60"/>
+      <c r="X191" s="60"/>
+      <c r="Y191" s="60"/>
+      <c r="Z191" s="64"/>
+      <c r="AA191" s="64"/>
+      <c r="AB191" s="60"/>
+      <c r="AC191" s="61"/>
+      <c r="AD191" s="60"/>
+      <c r="AE191" s="60"/>
+      <c r="AF191" s="60"/>
+      <c r="AG191" s="60"/>
+      <c r="AH191" s="60"/>
+      <c r="AI191" s="60"/>
       <c r="AJ191" s="33"/>
     </row>
-    <row r="192" ht="15.6" customHeight="1">
-      <c r="A192" s="64"/>
+    <row r="192" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A192" s="65"/>
       <c r="B192" s="45"/>
       <c r="C192" s="45"/>
       <c r="D192" s="45"/>
-      <c r="E192" s="64"/>
+      <c r="E192" s="65"/>
       <c r="F192" s="44"/>
       <c r="G192" s="44"/>
       <c r="H192" s="45"/>
@@ -10195,12 +10122,12 @@
       <c r="L192" s="45"/>
       <c r="M192" s="45"/>
       <c r="N192" s="45"/>
-      <c r="O192" s="65"/>
+      <c r="O192" s="66"/>
       <c r="P192" s="44"/>
       <c r="Q192" s="45"/>
       <c r="R192" s="45"/>
       <c r="S192" s="45"/>
-      <c r="T192" s="66"/>
+      <c r="T192" s="67"/>
       <c r="U192" s="45"/>
       <c r="V192" s="45"/>
       <c r="W192" s="45"/>
@@ -10218,50 +10145,50 @@
       <c r="AI192" s="45"/>
       <c r="AJ192" s="33"/>
     </row>
-    <row r="193" ht="15.6" customHeight="1">
-      <c r="A193" s="58"/>
-      <c r="B193" s="59"/>
-      <c r="C193" s="59"/>
-      <c r="D193" s="59"/>
-      <c r="E193" s="58"/>
-      <c r="F193" s="60"/>
-      <c r="G193" s="60"/>
-      <c r="H193" s="59"/>
-      <c r="I193" s="59"/>
-      <c r="J193" s="59"/>
-      <c r="K193" s="59"/>
-      <c r="L193" s="59"/>
-      <c r="M193" s="59"/>
-      <c r="N193" s="59"/>
-      <c r="O193" s="61"/>
-      <c r="P193" s="60"/>
-      <c r="Q193" s="59"/>
-      <c r="R193" s="59"/>
-      <c r="S193" s="59"/>
-      <c r="T193" s="62"/>
-      <c r="U193" s="59"/>
-      <c r="V193" s="59"/>
-      <c r="W193" s="59"/>
-      <c r="X193" s="59"/>
-      <c r="Y193" s="59"/>
-      <c r="Z193" s="63"/>
-      <c r="AA193" s="63"/>
-      <c r="AB193" s="59"/>
-      <c r="AC193" s="60"/>
-      <c r="AD193" s="59"/>
-      <c r="AE193" s="59"/>
-      <c r="AF193" s="59"/>
-      <c r="AG193" s="59"/>
-      <c r="AH193" s="59"/>
-      <c r="AI193" s="59"/>
+    <row r="193" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A193" s="59"/>
+      <c r="B193" s="60"/>
+      <c r="C193" s="60"/>
+      <c r="D193" s="60"/>
+      <c r="E193" s="59"/>
+      <c r="F193" s="61"/>
+      <c r="G193" s="61"/>
+      <c r="H193" s="60"/>
+      <c r="I193" s="60"/>
+      <c r="J193" s="60"/>
+      <c r="K193" s="60"/>
+      <c r="L193" s="60"/>
+      <c r="M193" s="60"/>
+      <c r="N193" s="60"/>
+      <c r="O193" s="62"/>
+      <c r="P193" s="61"/>
+      <c r="Q193" s="60"/>
+      <c r="R193" s="60"/>
+      <c r="S193" s="60"/>
+      <c r="T193" s="63"/>
+      <c r="U193" s="60"/>
+      <c r="V193" s="60"/>
+      <c r="W193" s="60"/>
+      <c r="X193" s="60"/>
+      <c r="Y193" s="60"/>
+      <c r="Z193" s="64"/>
+      <c r="AA193" s="64"/>
+      <c r="AB193" s="60"/>
+      <c r="AC193" s="61"/>
+      <c r="AD193" s="60"/>
+      <c r="AE193" s="60"/>
+      <c r="AF193" s="60"/>
+      <c r="AG193" s="60"/>
+      <c r="AH193" s="60"/>
+      <c r="AI193" s="60"/>
       <c r="AJ193" s="33"/>
     </row>
-    <row r="194" ht="15.6" customHeight="1">
-      <c r="A194" s="64"/>
+    <row r="194" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A194" s="65"/>
       <c r="B194" s="45"/>
       <c r="C194" s="45"/>
       <c r="D194" s="45"/>
-      <c r="E194" s="64"/>
+      <c r="E194" s="65"/>
       <c r="F194" s="44"/>
       <c r="G194" s="44"/>
       <c r="H194" s="45"/>
@@ -10271,12 +10198,12 @@
       <c r="L194" s="45"/>
       <c r="M194" s="45"/>
       <c r="N194" s="45"/>
-      <c r="O194" s="65"/>
+      <c r="O194" s="66"/>
       <c r="P194" s="44"/>
       <c r="Q194" s="45"/>
       <c r="R194" s="45"/>
       <c r="S194" s="45"/>
-      <c r="T194" s="66"/>
+      <c r="T194" s="67"/>
       <c r="U194" s="45"/>
       <c r="V194" s="45"/>
       <c r="W194" s="45"/>
@@ -10294,42 +10221,42 @@
       <c r="AI194" s="45"/>
       <c r="AJ194" s="33"/>
     </row>
-    <row r="195" ht="15.6" customHeight="1">
-      <c r="A195" s="58"/>
-      <c r="B195" s="59"/>
-      <c r="C195" s="59"/>
-      <c r="D195" s="59"/>
-      <c r="E195" s="58"/>
-      <c r="F195" s="60"/>
-      <c r="G195" s="60"/>
-      <c r="H195" s="59"/>
-      <c r="I195" s="59"/>
-      <c r="J195" s="59"/>
-      <c r="K195" s="59"/>
-      <c r="L195" s="59"/>
-      <c r="M195" s="59"/>
-      <c r="N195" s="59"/>
-      <c r="O195" s="61"/>
-      <c r="P195" s="60"/>
-      <c r="Q195" s="59"/>
-      <c r="R195" s="59"/>
-      <c r="S195" s="59"/>
-      <c r="T195" s="62"/>
-      <c r="U195" s="59"/>
-      <c r="V195" s="59"/>
-      <c r="W195" s="59"/>
-      <c r="X195" s="59"/>
-      <c r="Y195" s="59"/>
-      <c r="Z195" s="63"/>
-      <c r="AA195" s="63"/>
-      <c r="AB195" s="59"/>
-      <c r="AC195" s="60"/>
-      <c r="AD195" s="59"/>
-      <c r="AE195" s="59"/>
-      <c r="AF195" s="59"/>
-      <c r="AG195" s="59"/>
-      <c r="AH195" s="59"/>
-      <c r="AI195" s="59"/>
+    <row r="195" ht="15.6" customHeight="1" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A195" s="59"/>
+      <c r="B195" s="60"/>
+      <c r="C195" s="60"/>
+      <c r="D195" s="60"/>
+      <c r="E195" s="59"/>
+      <c r="F195" s="61"/>
+      <c r="G195" s="61"/>
+      <c r="H195" s="60"/>
+      <c r="I195" s="60"/>
+      <c r="J195" s="60"/>
+      <c r="K195" s="60"/>
+      <c r="L195" s="60"/>
+      <c r="M195" s="60"/>
+      <c r="N195" s="60"/>
+      <c r="O195" s="62"/>
+      <c r="P195" s="61"/>
+      <c r="Q195" s="60"/>
+      <c r="R195" s="60"/>
+      <c r="S195" s="60"/>
+      <c r="T195" s="63"/>
+      <c r="U195" s="60"/>
+      <c r="V195" s="60"/>
+      <c r="W195" s="60"/>
+      <c r="X195" s="60"/>
+      <c r="Y195" s="60"/>
+      <c r="Z195" s="64"/>
+      <c r="AA195" s="64"/>
+      <c r="AB195" s="60"/>
+      <c r="AC195" s="61"/>
+      <c r="AD195" s="60"/>
+      <c r="AE195" s="60"/>
+      <c r="AF195" s="60"/>
+      <c r="AG195" s="60"/>
+      <c r="AH195" s="60"/>
+      <c r="AI195" s="60"/>
       <c r="AJ195" s="33"/>
     </row>
   </sheetData>
@@ -10337,22 +10264,34 @@
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="I1:O1"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4 O103:O195">
-      <formula1>"Pas de participation citoyenne,Information,Consultation,Concertation,Co-construction"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X4 X103:X195">
-      <formula1>"À venir,À discuter,En cours,Réalisé,En retard,En pause,Bloqué "</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y4 Y103:Y195">
-      <formula1>"Élevé,Moyen,Bas"</formula1>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB10:AB195">
+      <formula1>"VRAI,FAUX"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB4:AB195">
       <formula1>"VRAI,FAUX"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O103:O195">
+      <formula1>"Pas de participation citoyenne,Information,Consultation,Concertation,Co-construction"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O4">
+      <formula1>"Pas de participation citoyenne,Information,Consultation,Concertation,Co-construction"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X103:X195">
+      <formula1>"À venir,À discuter,En cours,Réalisé,En retard,En pause,Bloqué "</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X4">
+      <formula1>"À venir,À discuter,En cours,Réalisé,En retard,En pause,Bloqué "</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y103:Y195">
+      <formula1>"Élevé,Moyen,Bas"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y4">
+      <formula1>"Élevé,Moyen,Bas"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
@@ -10360,183 +10299,183 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="11.1667" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="11.1667"/>
   <cols>
-    <col min="1" max="1" width="42.6719" style="67" customWidth="1"/>
-    <col min="2" max="2" width="38.6719" style="67" customWidth="1"/>
-    <col min="3" max="3" width="23" style="67" customWidth="1"/>
-    <col min="4" max="4" width="25" style="67" customWidth="1"/>
-    <col min="5" max="5" width="29.6719" style="67" customWidth="1"/>
-    <col min="6" max="16384" width="11.1719" style="67" customWidth="1"/>
+    <col min="1" max="1" width="42.6719" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.6719" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29.6719" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="11.1719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1">
-      <c r="A1" t="s" s="68">
+    <row r="1" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="68" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="69" t="s">
         <v>72</v>
       </c>
-      <c r="B1" t="s" s="68">
-        <v>73</v>
-      </c>
-      <c r="C1" t="s" s="68">
-        <v>29</v>
-      </c>
-      <c r="D1" t="s" s="68">
-        <v>30</v>
-      </c>
-      <c r="E1" t="s" s="68">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" ht="19.5" customHeight="1">
-      <c r="A2" t="s" s="69">
-        <v>75</v>
-      </c>
-      <c r="B2" t="s" s="69">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s" s="69">
-        <v>70</v>
-      </c>
-      <c r="D2" t="s" s="69">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s" s="69">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" ht="19.5" customHeight="1">
-      <c r="A3" t="s" s="69">
+      <c r="E2" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="B3" t="s" s="69">
+    </row>
+    <row r="3" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="C3" t="s" s="69">
+      <c r="B3" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D3" t="s" s="69">
+      <c r="C3" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="E3" t="s" s="69">
+      <c r="D3" s="69" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" ht="19.5" customHeight="1">
-      <c r="A4" t="s" s="69">
+      <c r="E3" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B4" t="s" s="69">
+    </row>
+    <row r="4" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="C4" t="s" s="69">
+      <c r="B4" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="D4" t="s" s="69">
+      <c r="C4" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="E4" t="s" s="69">
+      <c r="D4" s="69" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="5" ht="19.5" customHeight="1">
-      <c r="A5" t="s" s="69">
+      <c r="E4" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="B5" t="s" s="69">
+    </row>
+    <row r="5" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="C5" t="s" s="69">
+      <c r="B5" s="69" t="s">
         <v>90</v>
       </c>
+      <c r="C5" s="69" t="s">
+        <v>91</v>
+      </c>
       <c r="D5" s="70"/>
-      <c r="E5" t="s" s="69">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" t="s" s="69">
+      <c r="E5" s="69" t="s">
         <v>92</v>
       </c>
-      <c r="B6" t="s" s="69">
+    </row>
+    <row r="6" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C6" t="s" s="69">
+      <c r="B6" s="69" t="s">
         <v>94</v>
       </c>
+      <c r="C6" s="69" t="s">
+        <v>95</v>
+      </c>
       <c r="D6" s="70"/>
-      <c r="E6" t="s" s="69">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" ht="19.5" customHeight="1">
-      <c r="A7" t="s" s="69">
-        <v>95</v>
-      </c>
-      <c r="B7" t="s" s="69">
+      <c r="E6" s="69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="C7" t="s" s="69">
+      <c r="B7" s="69" t="s">
         <v>97</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>98</v>
       </c>
       <c r="D7" s="70"/>
       <c r="E7" s="70"/>
     </row>
-    <row r="8" ht="19.5" customHeight="1">
-      <c r="A8" t="s" s="69">
-        <v>98</v>
-      </c>
-      <c r="B8" t="s" s="69">
+    <row r="8" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="C8" t="s" s="69">
+      <c r="B8" s="69" t="s">
         <v>100</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>101</v>
       </c>
       <c r="D8" s="70"/>
       <c r="E8" s="70"/>
     </row>
-    <row r="9" ht="19.5" customHeight="1">
-      <c r="A9" t="s" s="69">
-        <v>101</v>
-      </c>
-      <c r="B9" t="s" s="69">
+    <row r="9" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="C9" t="s" s="69">
+      <c r="B9" s="69" t="s">
         <v>103</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>104</v>
       </c>
       <c r="D9" s="70"/>
       <c r="E9" s="70"/>
     </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" t="s" s="69">
-        <v>104</v>
-      </c>
-      <c r="B10" t="s" s="69">
+    <row r="10" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="69" t="s">
         <v>105</v>
+      </c>
+      <c r="B10" s="69" t="s">
+        <v>106</v>
       </c>
       <c r="C10" s="70"/>
       <c r="D10" s="70"/>
       <c r="E10" s="70"/>
     </row>
-    <row r="11" ht="19.5" customHeight="1">
-      <c r="A11" t="s" s="69">
-        <v>106</v>
-      </c>
-      <c r="B11" t="s" s="69">
+    <row r="11" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="69" t="s">
         <v>107</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>108</v>
       </c>
       <c r="C11" s="70"/>
       <c r="D11" s="70"/>
       <c r="E11" s="70"/>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
-      <c r="A12" t="s" s="69">
-        <v>108</v>
-      </c>
-      <c r="B12" t="s" s="69">
+    <row r="12" ht="19.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="69" t="s">
         <v>109</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>110</v>
       </c>
       <c r="C12" s="70"/>
       <c r="D12" s="70"/>
@@ -10544,7 +10483,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="downThenOver"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
